--- a/Luban/Config/Datas/EnemyList.xlsx
+++ b/Luban/Config/Datas/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>74,70,88,1,2,3,4,5,6,43,61,64,72,74,70,88,1,2,3,4,5,6,43,61,64,72,74,70</t>
+          <t>74,70,88,1,2,3,4,5,6,43,61,64,72,74,70,88,1,2,3,4,5,6,43,61,64,72,74,70,129</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>第 10 波：28 只 / 13 种（间隔 18.0s / 0.40s）</t>
+          <t>第 10 波：29 只 / 14 种（间隔 18.0s / 0.40s）★含 Boss</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>74,70,88,80,1,2,3,4,5,6,7,43,61,64,72,74,70,88,80,1,2,3,4,5,6,7,43,61,64,72</t>
+          <t>74,70,88,80,1,2,3,4,5,6,7,43,61,64,72,74,70,88,80,1,2,3,4,5,6,7,43,61,64,72,129,130</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>第 11 波：30 只 / 15 种（间隔 20.0s / 0.37s）</t>
+          <t>第 11 波：32 只 / 17 种（间隔 20.0s / 0.37s）★含 Boss</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>70,88,80,77,1,2,3,4,5,6,7,43,61,64,72,74,70,88,80,77,1,2,3,4,5,6,7,43,61,64,72,74</t>
+          <t>70,88,80,77,1,2,3,4,5,6,7,43,61,64,72,74,70,88,80,77,1,2,3,4,5,6,7,43,61,64,72,74,129,130,131,132</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>第 12 波：32 只 / 16 种（间隔 22.0s / 0.34s）</t>
+          <t>第 12 波：36 只 / 20 种（间隔 22.0s / 0.34s）★含 Boss</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/EnemyList.xlsx
+++ b/Luban/Config/Datas/EnemyList.xlsx
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="54.875" customWidth="1" style="2" min="3" max="3"/>
@@ -1158,18 +1158,18 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>2,1,2,1,2,1,2,1,2,1</t>
+          <t>99,89,86,16,122</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>620</v>
+        <v>560</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>第 1 波：10 只 / 2 种（间隔 0.0s / 0.62s）</t>
+          <t>第 1 波：5 只 / 目标血量 1400（单怪间隔 0.56s）</t>
         </is>
       </c>
     </row>
@@ -1179,18 +1179,18 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>1,2,1,2,1,2,1,2,1,2,1,2</t>
+          <t>103,84,1,121,100,88,80</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>595</v>
+        <v>552</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>第 2 波：12 只 / 2 种（间隔 2.0s / 0.59s）</t>
+          <t>第 2 波：7 只 / 目标血量 1541（单怪间隔 0.55s）</t>
         </is>
       </c>
     </row>
@@ -1200,18 +1200,18 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,1,2,3,1,2,3,1,2,3,1,2</t>
+          <t>88,80,23,19,101,5,87</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>第 3 波：14 只 / 3 种（间隔 4.0s / 0.57s）</t>
+          <t>第 3 波：7 只 / 目标血量 1697（单怪间隔 0.54s）</t>
         </is>
       </c>
     </row>
@@ -1221,18 +1221,18 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,43,1,2,3,43,1,2,3,43,1,2,3,43</t>
+          <t>5,87,30,83,85,98,4,17</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>第 4 波：16 只 / 4 种（间隔 6.0s / 0.55s）</t>
+          <t>第 4 波：8 只 / 目标血量 1868（单怪间隔 0.54s）</t>
         </is>
       </c>
     </row>
@@ -1242,18 +1242,18 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>61,1,2,3,4,43,61,1,2,3,4,43,61,1,2,3,4,43</t>
+          <t>98,4,17,82,81,97,79,2</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>第 5 波：18 只 / 6 种（间隔 8.0s / 0.52s）</t>
+          <t>第 5 波：8 只 / 目标血量 2057（单怪间隔 0.53s）</t>
         </is>
       </c>
     </row>
@@ -1263,18 +1263,18 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>64,1,2,3,4,43,61,64,1,2,3,4,43,61,64,1,2,3,4,43</t>
+          <t>97,79,2,102,90,8,24,99,89</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>第 6 波：20 只 / 7 种（间隔 10.0s / 0.49s）</t>
+          <t>第 6 波：9 只 / 目标血量 2265（单怪间隔 0.51s）</t>
         </is>
       </c>
     </row>
@@ -1284,18 +1284,18 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>64,72,1,2,3,4,5,43,61,64,72,1,2,3,4,5,43,61,64,72,1,2</t>
+          <t>8,24,99,89,86,16,122,103,84</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>12000</v>
+        <v>3000</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>第 7 波：22 只 / 9 种（间隔 12.0s / 0.47s）</t>
+          <t>第 7 波：9 只 / 目标血量 2494（单怪间隔 0.50s）</t>
         </is>
       </c>
     </row>
@@ -1305,18 +1305,18 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>72,74,1,2,3,4,5,43,61,64,72,74,1,2,3,4,5,43,61,64,72,74,1,2</t>
+          <t>16,122,103,84,1,121,100,88,80,23</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14000</v>
+        <v>3000</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>445</v>
+        <v>496</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>第 8 波：24 只 / 10 种（间隔 14.0s / 0.45s）</t>
+          <t>第 8 波：10 只 / 目标血量 2746（单怪间隔 0.50s）</t>
         </is>
       </c>
     </row>
@@ -1326,18 +1326,18 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>72,74,70,1,2,3,4,5,6,43,61,64,72,74,70,1,2,3,4,5,6,43,61,64,72,74</t>
+          <t>121,100,88,80,23,19,101,5,87,30,83,85</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>16000</v>
+        <v>3000</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>420</v>
+        <v>488</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>第 9 波：26 只 / 12 种（间隔 16.0s / 0.42s）</t>
+          <t>第 9 波：12 只 / 目标血量 3023（单怪间隔 0.49s）</t>
         </is>
       </c>
     </row>
@@ -1347,18 +1347,18 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>74,70,88,1,2,3,4,5,6,43,61,64,72,74,70,88,1,2,3,4,5,6,43,61,64,72,74,70,129</t>
+          <t>19,101,5,87,30,83,85,98,4,17,82,81,97</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>18000</v>
+        <v>3000</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>395</v>
+        <v>480</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>第 10 波：29 只 / 14 种（间隔 18.0s / 0.40s）★含 Boss</t>
+          <t>第 10 波：13 只 / 目标血量 3328（单怪间隔 0.48s）</t>
         </is>
       </c>
     </row>
@@ -1368,18 +1368,18 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>74,70,88,80,1,2,3,4,5,6,7,43,61,64,72,74,70,88,80,1,2,3,4,5,6,7,43,61,64,72,129,130</t>
+          <t>11,29,26,125,56,78,20,13</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>370</v>
+        <v>464</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>第 11 波：32 只 / 17 种（间隔 20.0s / 0.37s）★含 Boss</t>
+          <t>第 11 波：8 只 / 目标血量 3664（单怪间隔 0.46s）</t>
         </is>
       </c>
     </row>
@@ -1389,18 +1389,18 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>70,88,80,77,1,2,3,4,5,6,7,43,61,64,72,74,70,88,80,77,1,2,3,4,5,6,7,43,61,64,72,74,129,130,131,132</t>
+          <t>78,20,13,15,14,28,126,77,92,132</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>22000</v>
+        <v>3000</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>345</v>
+        <v>456</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>第 12 波：36 只 / 20 种（间隔 22.0s / 0.34s）★含 Boss</t>
+          <t>第 12 波：10 只 / 目标血量 4034（单怪间隔 0.46s）</t>
         </is>
       </c>
     </row>
@@ -1410,18 +1410,18 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>70,88,80,77,75,1,2,3,4,5,6,7,8,43,61,64,72,74,70,88,80,77,75,1,2,3,4,5,6,7,8,43,61,64</t>
+          <t>28,126,77,92,12,124,123,117,57</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>24000</v>
+        <v>3000</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>320</v>
+        <v>448</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>第 13 波：34 只 / 18 种（间隔 24.0s / 0.32s）</t>
+          <t>第 13 波：9 只 / 目标血量 4442（单怪间隔 0.45s）</t>
         </is>
       </c>
     </row>
@@ -1431,18 +1431,18 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>88,80,77,75,31,1,2,3,4,5,6,7,8,43,61,64,72,74,70,88,80,77,75,31,1,2,3,4,5,6,7,8,43,61,64,72</t>
+          <t>124,123,117,57,128,119,127,7,18,27,116,132</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>26000</v>
+        <v>3000</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>295</v>
+        <v>440</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>第 14 波：36 只 / 19 种（间隔 26.0s / 0.29s）</t>
+          <t>第 14 波：12 只 / 目标血量 4891（单怪间隔 0.44s）</t>
         </is>
       </c>
     </row>
@@ -1452,18 +1452,18 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>88,80,77,75,31,26,1,2,3,4,5,6,7,8,9,43,61,64,72,74,70,88,80,77,75,31,26,1,2,3,4,5,6,7,8,9,43,61</t>
+          <t>119,127,7,18,27,116,25,104,22,120,21,118</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>28000</v>
+        <v>3000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>270</v>
+        <v>432</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>第 15 波：38 只 / 21 种（间隔 28.0s / 0.27s）</t>
+          <t>第 15 波：12 只 / 目标血量 5385（单怪间隔 0.43s）</t>
         </is>
       </c>
     </row>
@@ -1532,6 +1532,531 @@
     </row>
     <row r="40">
       <c r="D40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>116,25,104,22,120,21,118,11,29,26,125,56,132</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <v>416</v>
+      </c>
+      <c r="F41" s="0" t="inlineStr">
+        <is>
+          <t>第 16 波：13 只 / 目标血量 5928（单怪间隔 0.42s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>21,118,11,29,26,125,56,78,20,13,15,14,28,126,77</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E42" s="0" t="n">
+        <v>408</v>
+      </c>
+      <c r="F42" s="0" t="inlineStr">
+        <is>
+          <t>第 17 波：15 只 / 目标血量 6527（单怪间隔 0.41s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>125,56,78,20,13,15,14,28,126,77,92,12,124,123,117,132</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E43" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="F43" s="0" t="inlineStr">
+        <is>
+          <t>第 18 波：16 只 / 目标血量 7186（单怪间隔 0.40s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>15,14,28,126,77,92,12,124,123,117,57,128,119,127,7,18,27</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E44" s="0" t="n">
+        <v>392</v>
+      </c>
+      <c r="F44" s="0" t="inlineStr">
+        <is>
+          <t>第 19 波：17 只 / 目标血量 7912（单怪间隔 0.39s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>92,12,124,123,117,57,128,119,127,7,18,27,116,25,104,22,120,21,132,129</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E45" s="0" t="n">
+        <v>384</v>
+      </c>
+      <c r="F45" s="0" t="inlineStr">
+        <is>
+          <t>第 20 波：20 只 / 目标血量 8711（单怪间隔 0.38s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>114,96,115,111,49,53,106,59,62,54,107</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <v>368</v>
+      </c>
+      <c r="F46" s="0" t="inlineStr">
+        <is>
+          <t>第 21 波：11 只 / 目标血量 9591（单怪间隔 0.37s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>53,106,59,62,54,107,112,113,46,45,51,50,132</t>
+        </is>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E47" s="0" t="n">
+        <v>360</v>
+      </c>
+      <c r="F47" s="0" t="inlineStr">
+        <is>
+          <t>第 22 波：13 只 / 目标血量 10560（单怪间隔 0.36s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>107,112,113,46,45,51,50,93,48,55,43,64,44</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E48" s="0" t="n">
+        <v>352</v>
+      </c>
+      <c r="F48" s="0" t="inlineStr">
+        <is>
+          <t>第 23 波：13 只 / 目标血量 11627（单怪间隔 0.35s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>51,50,93,48,55,43,64,44,109,91,108,42,95,52,132</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E49" s="0" t="n">
+        <v>344</v>
+      </c>
+      <c r="F49" s="0" t="inlineStr">
+        <is>
+          <t>第 24 波：15 只 / 目标血量 12801（单怪间隔 0.34s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>43,64,44,109,91,108,42,95,52,60,94,105,114,96,115,130</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E50" s="0" t="n">
+        <v>336</v>
+      </c>
+      <c r="F50" s="0" t="inlineStr">
+        <is>
+          <t>第 25 波：16 只 / 目标血量 14094（单怪间隔 0.34s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>108,42,95,52,60,94,105,114,96,115,111,49,53,106,59,62,54,132</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E51" s="0" t="n">
+        <v>320</v>
+      </c>
+      <c r="F51" s="0" t="inlineStr">
+        <is>
+          <t>第 26 波：18 只 / 目标血量 15517（单怪间隔 0.32s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>94,105,114,96,115,111,49,53,106,59,62,54,107,112,113,46,45,51,50</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E52" s="0" t="n">
+        <v>312</v>
+      </c>
+      <c r="F52" s="0" t="inlineStr">
+        <is>
+          <t>第 27 波：19 只 / 目标血量 17084（单怪间隔 0.31s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>111,49,53,106,59,62,54,107,112,113,46,45,51,50,93,48,55,43,64,44,132</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E53" s="0" t="n">
+        <v>304</v>
+      </c>
+      <c r="F53" s="0" t="inlineStr">
+        <is>
+          <t>第 28 波：21 只 / 目标血量 18810（单怪间隔 0.30s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>62,54,107,112,113,46,45,51,50,93,48,55,43,64,44,109,91,108,42,95,52,60,94</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E54" s="0" t="n">
+        <v>296</v>
+      </c>
+      <c r="F54" s="0" t="inlineStr">
+        <is>
+          <t>第 29 波：23 只 / 目标血量 20710（单怪间隔 0.30s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>46,45,51,50,93,48,55,43,64,44,109,91,108,42,95,52,60,94,105,114,96,115,111,49,53,132,131</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E55" s="0" t="n">
+        <v>288</v>
+      </c>
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t>第 30 波：27 只 / 目标血量 22801（单怪间隔 0.29s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>72,10,6,35,67,61,63,39,9,68</t>
+        </is>
+      </c>
+      <c r="D56" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E56" s="0" t="n">
+        <v>272</v>
+      </c>
+      <c r="F56" s="0" t="inlineStr">
+        <is>
+          <t>第 31 波：10 只 / 目标血量 25104（单怪间隔 0.27s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>61,63,39,9,68,41,75,32,70,65,58,38,132</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E57" s="0" t="n">
+        <v>264</v>
+      </c>
+      <c r="F57" s="0" t="inlineStr">
+        <is>
+          <t>第 32 波：13 只 / 目标血量 27640（单怪间隔 0.26s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>41,75,32,70,65,58,38,37,73,47,34,76,66</t>
+        </is>
+      </c>
+      <c r="D58" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E58" s="0" t="n">
+        <v>256</v>
+      </c>
+      <c r="F58" s="0" t="inlineStr">
+        <is>
+          <t>第 33 波：13 只 / 目标血量 30431（单怪间隔 0.26s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>58,38,37,73,47,34,76,66,74,40,36,31,69,110,132</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E59" s="0" t="n">
+        <v>248</v>
+      </c>
+      <c r="F59" s="0" t="inlineStr">
+        <is>
+          <t>第 34 波：15 只 / 目标血量 33505（单怪间隔 0.25s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,131</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E60" s="0" t="n">
+        <v>240</v>
+      </c>
+      <c r="F60" s="0" t="inlineStr">
+        <is>
+          <t>第 35 波：16 只 / 目标血量 36889（单怪间隔 0.24s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,132</t>
+        </is>
+      </c>
+      <c r="D61" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E61" s="0" t="n">
+        <v>224</v>
+      </c>
+      <c r="F61" s="0" t="inlineStr">
+        <is>
+          <t>第 36 波：18 只 / 目标血量 40615（单怪间隔 0.22s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65</t>
+        </is>
+      </c>
+      <c r="D62" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E62" s="0" t="n">
+        <v>216</v>
+      </c>
+      <c r="F62" s="0" t="inlineStr">
+        <is>
+          <t>第 37 波：17 只 / 目标血量 44717（单怪间隔 0.22s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,132</t>
+        </is>
+      </c>
+      <c r="D63" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E63" s="0" t="n">
+        <v>208</v>
+      </c>
+      <c r="F63" s="0" t="inlineStr">
+        <is>
+          <t>第 38 波：21 只 / 目标血量 49233（单怪间隔 0.21s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110</t>
+        </is>
+      </c>
+      <c r="D64" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E64" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F64" s="0" t="inlineStr">
+        <is>
+          <t>第 39 波：21 只 / 目标血量 54206（单怪间隔 0.20s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,132,131</t>
+        </is>
+      </c>
+      <c r="D65" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E65" s="0" t="n">
+        <v>192</v>
+      </c>
+      <c r="F65" s="0" t="inlineStr">
+        <is>
+          <t>第 40 波：26 只 / 目标血量 59681（单怪间隔 0.19s）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Luban/Config/Datas/EnemyList.xlsx
+++ b/Luban/Config/Datas/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="54.875" customWidth="1" style="2" min="3" max="3"/>
@@ -2055,6 +2055,741 @@
       <c r="F65" s="0" t="inlineStr">
         <is>
           <t>第 40 波：26 只 / 目标血量 59681（单怪间隔 0.19s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68</t>
+        </is>
+      </c>
+      <c r="D66" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E66" s="0" t="n">
+        <v>176</v>
+      </c>
+      <c r="F66" s="0" t="inlineStr">
+        <is>
+          <t>第 41 波：24 只 / 目标血量 60158（单怪间隔 0.18s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,132</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E67" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F67" s="0" t="inlineStr">
+        <is>
+          <t>第 42 波：25 只 / 目标血量 60640（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76</t>
+        </is>
+      </c>
+      <c r="D68" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E68" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F68" s="0" t="inlineStr">
+        <is>
+          <t>第 43 波：26 只 / 目标血量 61125（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,132</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E69" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F69" s="0" t="inlineStr">
+        <is>
+          <t>第 44 波：27 只 / 目标血量 61614（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,129</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E70" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F70" s="0" t="inlineStr">
+        <is>
+          <t>第 45 波：27 只 / 目标血量 62107（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t>75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,132</t>
+        </is>
+      </c>
+      <c r="D71" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E71" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F71" s="0" t="inlineStr">
+        <is>
+          <t>第 46 波：26 只 / 目标血量 62604（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68</t>
+        </is>
+      </c>
+      <c r="D72" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E72" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F72" s="0" t="inlineStr">
+        <is>
+          <t>第 47 波：26 只 / 目标血量 63104（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,132</t>
+        </is>
+      </c>
+      <c r="D73" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E73" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F73" s="0" t="inlineStr">
+        <is>
+          <t>第 48 波：27 只 / 目标血量 63609（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47</t>
+        </is>
+      </c>
+      <c r="D74" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E74" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F74" s="0" t="inlineStr">
+        <is>
+          <t>第 49 波：26 只 / 目标血量 64118（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,132,130</t>
+        </is>
+      </c>
+      <c r="D75" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E75" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F75" s="0" t="inlineStr">
+        <is>
+          <t>第 50 波：27 只 / 目标血量 64631（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33</t>
+        </is>
+      </c>
+      <c r="D76" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E76" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F76" s="0" t="inlineStr">
+        <is>
+          <t>第 51 波：27 只 / 目标血量 65148（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,132</t>
+        </is>
+      </c>
+      <c r="D77" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E77" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F77" s="0" t="inlineStr">
+        <is>
+          <t>第 52 波：27 只 / 目标血量 65669（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E78" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F78" s="0" t="inlineStr">
+        <is>
+          <t>第 53 波：28 只 / 目标血量 66195（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,132</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E79" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F79" s="0" t="inlineStr">
+        <is>
+          <t>第 54 波：29 只 / 目标血量 66724（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,131</t>
+        </is>
+      </c>
+      <c r="D80" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E80" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F80" s="0" t="inlineStr">
+        <is>
+          <t>第 55 波：30 只 / 目标血量 67258（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,132</t>
+        </is>
+      </c>
+      <c r="D81" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E81" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F81" s="0" t="inlineStr">
+        <is>
+          <t>第 56 波：28 只 / 目标血量 67796（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33</t>
+        </is>
+      </c>
+      <c r="D82" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E82" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F82" s="0" t="inlineStr">
+        <is>
+          <t>第 57 波：29 只 / 目标血量 68338（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,132</t>
+        </is>
+      </c>
+      <c r="D83" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E83" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F83" s="0" t="inlineStr">
+        <is>
+          <t>第 58 波：28 只 / 目标血量 68885（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="C84" s="0" t="inlineStr">
+        <is>
+          <t>32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39</t>
+        </is>
+      </c>
+      <c r="D84" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E84" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F84" s="0" t="inlineStr">
+        <is>
+          <t>第 59 波：28 只 / 目标血量 69436（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t>37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,132,129</t>
+        </is>
+      </c>
+      <c r="D85" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E85" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F85" s="0" t="inlineStr">
+        <is>
+          <t>第 60 波：31 只 / 目标血量 69992（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t>66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73</t>
+        </is>
+      </c>
+      <c r="D86" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E86" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F86" s="0" t="inlineStr">
+        <is>
+          <t>第 61 波：29 只 / 目标血量 70552（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,132</t>
+        </is>
+      </c>
+      <c r="D87" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E87" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F87" s="0" t="inlineStr">
+        <is>
+          <t>第 62 波：30 只 / 目标血量 71116（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t>72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69</t>
+        </is>
+      </c>
+      <c r="D88" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E88" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F88" s="0" t="inlineStr">
+        <is>
+          <t>第 63 波：28 只 / 目标血量 71685（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="C89" s="0" t="inlineStr">
+        <is>
+          <t>61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,132</t>
+        </is>
+      </c>
+      <c r="D89" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E89" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F89" s="0" t="inlineStr">
+        <is>
+          <t>第 64 波：31 只 / 目标血量 72258（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="C90" s="0" t="inlineStr">
+        <is>
+          <t>41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,130</t>
+        </is>
+      </c>
+      <c r="D90" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E90" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F90" s="0" t="inlineStr">
+        <is>
+          <t>第 65 波：32 只 / 目标血量 72837（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t>58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,132</t>
+        </is>
+      </c>
+      <c r="D91" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E91" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F91" s="0" t="inlineStr">
+        <is>
+          <t>第 66 波：32 只 / 目标血量 73419（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t>34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37</t>
+        </is>
+      </c>
+      <c r="D92" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E92" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F92" s="0" t="inlineStr">
+        <is>
+          <t>第 67 波：30 只 / 目标血量 74007（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t>36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,132</t>
+        </is>
+      </c>
+      <c r="D93" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E93" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F93" s="0" t="inlineStr">
+        <is>
+          <t>第 68 波：32 只 / 目标血量 74599（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69</t>
+        </is>
+      </c>
+      <c r="D94" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E94" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F94" s="0" t="inlineStr">
+        <is>
+          <t>第 69 波：30 只 / 目标血量 75195（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,132,131</t>
+        </is>
+      </c>
+      <c r="D95" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E95" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F95" s="0" t="inlineStr">
+        <is>
+          <t>第 70 波：32 只 / 目标血量 75797（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t>9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61</t>
+        </is>
+      </c>
+      <c r="D96" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E96" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F96" s="0" t="inlineStr">
+        <is>
+          <t>第 71 波：30 只 / 目标血量 76403（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="0" t="n">
+        <v>72</v>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,132</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E97" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F97" s="0" t="inlineStr">
+        <is>
+          <t>第 72 波：32 只 / 目标血量 77015（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E98" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F98" s="0" t="inlineStr">
+        <is>
+          <t>第 73 波：32 只 / 目标血量 77631（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,132</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E99" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F99" s="0" t="inlineStr">
+        <is>
+          <t>第 74 波：33 只 / 目标血量 78252（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,129</t>
+        </is>
+      </c>
+      <c r="D100" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E100" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="F100" s="0" t="inlineStr">
+        <is>
+          <t>第 75 波：33 只 / 目标血量 78878（单怪间隔 0.17s）</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/EnemyList.xlsx
+++ b/Luban/Config/Datas/EnemyList.xlsx
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="54.875" customWidth="1" style="2" min="3" max="3"/>
@@ -2790,6 +2790,531 @@
       <c r="F100" s="0" t="inlineStr">
         <is>
           <t>第 75 波：33 只 / 目标血量 78878（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>76</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,132</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E101" t="n">
+        <v>170</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>第 76 波：33 只 / 目标血量 79509（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>77</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E102" t="n">
+        <v>170</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>第 77 波：33 只 / 目标血量 80145（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>78</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,132</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E103" t="n">
+        <v>170</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>第 78 波：34 只 / 目标血量 80786（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>79</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E104" t="n">
+        <v>170</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>第 79 波：33 只 / 目标血量 81432（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>80</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,132,130</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E105" t="n">
+        <v>170</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>第 80 波：36 只 / 目标血量 82084（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>81</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E106" t="n">
+        <v>170</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>第 81 波：34 只 / 目标血量 82740（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>82</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,132</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E107" t="n">
+        <v>170</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>第 82 波：34 只 / 目标血量 83402（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>83</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E108" t="n">
+        <v>170</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>第 83 波：34 只 / 目标血量 84070（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>84</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,132</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E109" t="n">
+        <v>170</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>第 84 波：35 只 / 目标血量 84742（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>85</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,131</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E110" t="n">
+        <v>170</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>第 85 波：35 只 / 目标血量 85420（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>86</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,132</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E111" t="n">
+        <v>170</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>第 86 波：37 只 / 目标血量 86103（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>87</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E112" t="n">
+        <v>170</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>第 87 波：36 只 / 目标血量 86792（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>88</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,132</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E113" t="n">
+        <v>170</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>第 88 波：37 只 / 目标血量 87487（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>89</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E114" t="n">
+        <v>170</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>第 89 波：36 只 / 目标血量 88187（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>90</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,132,129</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E115" t="n">
+        <v>170</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>第 90 波：37 只 / 目标血量 88892（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>91</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E116" t="n">
+        <v>170</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>第 91 波：35 只 / 目标血量 89603（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>92</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,132</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E117" t="n">
+        <v>170</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>第 92 波：38 只 / 目标血量 90320（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>93</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E118" t="n">
+        <v>170</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>第 93 波：36 只 / 目标血量 91043（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>94</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,132</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E119" t="n">
+        <v>170</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>第 94 波：38 只 / 目标血量 91771（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>95</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,130</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E120" t="n">
+        <v>170</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>第 95 波：38 只 / 目标血量 92505（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>96</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,132</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E121" t="n">
+        <v>170</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>第 96 波：40 只 / 目标血量 93245（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>97</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E122" t="n">
+        <v>170</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>第 97 波：38 只 / 目标血量 93991（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>98</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,132</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E123" t="n">
+        <v>170</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>第 98 波：41 只 / 目标血量 94743（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>99</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E124" t="n">
+        <v>170</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>第 99 波：39 只 / 目标血量 95501（单怪间隔 0.17s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>100</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,132,131</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E125" t="n">
+        <v>170</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>第 100 波：42 只 / 目标血量 96265（单怪间隔 0.17s）</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/EnemyList.xlsx
+++ b/Luban/Config/Datas/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F425"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="54.875" customWidth="1" style="2" min="3" max="3"/>
@@ -1158,18 +1158,18 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>99,89,86,16,122</t>
+          <t>3100136,3100136,3100136,3100136,3100136,3100136,3100136,3100136</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>560</v>
+        <v>900</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>第 1 波：5 只 / 目标血量 1400（单怪间隔 0.56s）</t>
+          <t>L1 W1/20; N=8; EHP=240.000000; normal:17x8</t>
         </is>
       </c>
     </row>
@@ -1179,18 +1179,18 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>103,84,1,121,100,88,80</t>
+          <t>3102136,3102136,3102136,3102136,3102136,3102144,3102144,3102144,3102144</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>552</v>
+        <v>885</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>第 2 波：7 只 / 目标血量 1541（单怪间隔 0.55s）</t>
+          <t>L1 W2/20; N=9; EHP=307.260000; normal:17x5,normal:18x4</t>
         </is>
       </c>
     </row>
@@ -1200,18 +1200,18 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>88,80,23,19,101,5,87</t>
+          <t>3104136,3104673,3104136,3104673,3104136,3104136,3104144,3104144,3104144,3104144</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>544</v>
+        <v>870</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>第 3 波：7 只 / 目标血量 1697（单怪间隔 0.54s）</t>
+          <t>L1 W3/20; N=10; EHP=393.600000; normal:17x4,normal:18x4,swarm:84x2</t>
         </is>
       </c>
     </row>
@@ -1221,18 +1221,18 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>5,87,30,83,85,98,4,17</t>
+          <t>3106136,3106673,3106136,3106673,3106136,3106673,3106136,3106144,3106144,3106144,3106144</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>536</v>
+        <v>855</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>第 4 波：8 只 / 目标血量 1868（单怪间隔 0.54s）</t>
+          <t>L1 W4/20; N=11; EHP=502.260000; normal:17x4,normal:18x4,swarm:84x3</t>
         </is>
       </c>
     </row>
@@ -1242,18 +1242,18 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>98,4,17,82,81,97,79,2</t>
+          <t>3108136,3108673,3108668,3108136,3108673,3108136,3108673,3108136,3108144,3108144,3108144,3108144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>528</v>
+        <v>840</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>第 5 波：8 只 / 目标血量 2057（单怪间隔 0.53s）</t>
+          <t>L1 W5/20; N=12; EHP=712.857600; normal:17x4,normal:18x4,medium:83x1,swarm:84x3</t>
         </is>
       </c>
     </row>
@@ -1263,18 +1263,18 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>97,79,2,102,90,8,24,99,89</t>
+          <t>3110136,3110673,3110668,3110136,3110673,3110136,3110673,3110136,3110136,3110144,3110144,3110144,3110144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>512</v>
+        <v>825</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>第 6 波：9 只 / 目标血量 2265（单怪间隔 0.51s）</t>
+          <t>L1 W6/20; N=13; EHP=799.500000; normal:17x5,normal:18x4,medium:83x1,swarm:84x3</t>
         </is>
       </c>
     </row>
@@ -1284,18 +1284,18 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>8,24,99,89,86,16,122,103,84</t>
+          <t>3112136,3112673,3112107,3112668,3112136,3112673,3112668,3112136,3112673,3112136,3112144,3112144,3112144,3112144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>504</v>
+        <v>810</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>第 7 波：9 只 / 目标血量 2494（单怪间隔 0.50s）</t>
+          <t>L1 W7/20; N=14; EHP=994.560000; air:13x1,normal:17x4,normal:18x4,medium:83x2,swarm:84x3</t>
         </is>
       </c>
     </row>
@@ -1305,18 +1305,18 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>16,122,103,84,1,121,100,88,80,23</t>
+          <t>3114136,3114673,3114091,3114668,3114136,3114673,3114668,3114136,3114673,3114136,3114673,3114144,3114144,3114144,3114144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>496</v>
+        <v>795</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>第 8 波：10 只 / 目标血量 2746（单怪间隔 0.50s）</t>
+          <t>L1 W8/20; N=15; EHP=1224.900000; air:11x1,normal:17x4,normal:18x4,medium:83x2,swarm:84x4</t>
         </is>
       </c>
     </row>
@@ -1326,18 +1326,18 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>121,100,88,80,23,19,101,5,87,30,83,85</t>
+          <t>3116136,3116673,3116091,3116668,3116136,3116673,3116107,3116668,3116136,3116673,3116136,3116673,3116144,3116144,3116144,3116144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>488</v>
+        <v>780</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>第 9 波：12 只 / 目标血量 3023（单怪间隔 0.49s）</t>
+          <t>L1 W9/20; N=16; EHP=1493.760000; air:11x1,air:13x1,normal:17x4,normal:18x4,medium:83x2,swarm:84x4</t>
         </is>
       </c>
     </row>
@@ -1347,18 +1347,18 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>19,101,5,87,30,83,85,98,4,17,82,81,97</t>
+          <t>3118136,3118673,3118091,3118668,3118136,3118673,3118115,3118668,3118136,3118673,3118136,3118673,3118136,3118144,3118144,3118144,3118144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>480</v>
+        <v>765</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>第 10 波：13 只 / 目标血量 3328（单怪间隔 0.48s）</t>
+          <t>L1 W10/20; N=17; EHP=2020.905600; air:11x1,air:14x1,normal:17x5,normal:18x4,medium:83x2,swarm:84x4</t>
         </is>
       </c>
     </row>
@@ -1368,18 +1368,18 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>11,29,26,125,56,78,20,13</t>
+          <t>3120136,3120673,3120668,3120709,3120136,3120673,3120668,3120136,3120673,3120136,3120673,3120136,3120673,3120144,3120144,3120144,3120144,3120144</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>464</v>
+        <v>750</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>第 11 波：8 只 / 目标血量 3664（单怪间隔 0.46s）</t>
+          <t>L1 W11/20; N=18; EHP=2160.000000; normal:17x5,normal:18x5,medium:83x2,swarm:84x5,heavy:88x1</t>
         </is>
       </c>
     </row>
@@ -1389,18 +1389,18 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>78,20,13,15,14,28,126,77,92,132</t>
+          <t>3122136,3122673,3122107,3122668,3122709,3122136,3122673,3122668,3122136,3122673,3122136,3122673,3122136,3122673,3122144,3122144,3122144,3122144,3122144</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>456</v>
+        <v>735</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>第 12 波：10 只 / 目标血量 4034（单怪间隔 0.46s）</t>
+          <t>L1 W12/20; N=19; EHP=2563.860000; air:13x1,normal:17x5,normal:18x5,medium:83x2,swarm:84x5,heavy:88x1</t>
         </is>
       </c>
     </row>
@@ -1410,18 +1410,18 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>28,126,77,92,12,124,123,117,57</t>
+          <t>3124136,3124673,3124091,3124668,3124709,3124136,3124673,3124115,3124668,3124709,3124136,3124673,3124668,3124136,3124673,3124144,3124673,3124144,3124144,3124144</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>448</v>
+        <v>720</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>第 13 波：9 只 / 目标血量 4442（单怪间隔 0.45s）</t>
+          <t>L1 W13/20; N=20; EHP=3019.200000; air:11x1,air:14x1,normal:17x4,normal:18x4,medium:83x3,swarm:84x5,heavy:88x2</t>
         </is>
       </c>
     </row>
@@ -1431,18 +1431,18 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>124,123,117,57,128,119,127,7,18,27,116,132</t>
+          <t>3126136,3126673,3126107,3126668,3126709,3126136,3126673,3126115,3126668,3126709,3126136,3126673,3126668,3126136,3126673,3126136,3126673,3126144,3126144,3126144,3126144</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>440</v>
+        <v>705</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>第 14 波：12 只 / 目标血量 4891（单怪间隔 0.44s）</t>
+          <t>L1 W14/20; N=21; EHP=3529.260000; air:13x1,air:14x1,normal:17x5,normal:18x4,medium:83x3,swarm:84x5,heavy:88x2</t>
         </is>
       </c>
     </row>
@@ -1452,18 +1452,18 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>119,127,7,18,27,116,25,104,22,120,21,118</t>
+          <t>3128136,3128673,3128091,3128668,3128709,3128136,3128673,3128107,3128668,3128709,3128136,3128673,3128988,3128136,3128673,3128136,3128673,3128144,3128673,3128144,3128144,3128144</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>432</v>
+        <v>690</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>第 15 波：12 只 / 目标血量 5385（单怪间隔 0.43s）</t>
+          <t>L1 W15/20; N=22; EHP=4588.953600; air:11x1,air:13x1,normal:17x5,normal:18x4,medium:83x2,swarm:84x6,heavy:88x2,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -1539,18 +1539,18 @@
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>116,25,104,22,120,21,118,11,29,26,125,56,132</t>
+          <t>3130136,3130673,3130668,3130709,3130136,3130673,3130988,3130709,3130136,3130673,3130988,3130136,3130673,3130136,3130673,3130136,3130673,3130144,3130144,3130144,3130144,3130144,3130144</t>
         </is>
       </c>
       <c r="D41" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E41" s="0" t="n">
-        <v>416</v>
+        <v>675</v>
       </c>
       <c r="F41" s="0" t="inlineStr">
         <is>
-          <t>第 16 波：13 只 / 目标血量 5928（单怪间隔 0.42s）</t>
+          <t>L1 W16/20; N=23; EHP=4773.000000; normal:17x6,normal:18x6,medium:83x1,swarm:84x6,heavy:88x2,medium:123x2</t>
         </is>
       </c>
     </row>
@@ -1560,18 +1560,18 @@
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>21,118,11,29,26,125,56,78,20,13,15,14,28,126,77</t>
+          <t>3132136,3132673,3132107,3132668,3132709,3132136,3132673,3132115,3132668,3132709,3132136,3132673,3132988,3132136,3132673,3132136,3132673,3132136,3132673,3132144,3132144,3132144,3132144,3132144</t>
         </is>
       </c>
       <c r="D42" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="0" t="n">
-        <v>408</v>
+        <v>660</v>
       </c>
       <c r="F42" s="0" t="inlineStr">
         <is>
-          <t>第 17 波：15 只 / 目标血量 6527（单怪间隔 0.41s）</t>
+          <t>L1 W17/20; N=24; EHP=5420.160000; air:13x1,air:14x1,normal:17x6,normal:18x5,medium:83x2,swarm:84x6,heavy:88x2,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -1581,18 +1581,18 @@
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>125,56,78,20,13,15,14,28,126,77,92,12,124,123,117,132</t>
+          <t>3134136,3134673,3134091,3134668,3134709,3134136,3134673,3134107,3134988,3134709,3134136,3134673,3134115,3134988,3134136,3134673,3134136,3134673,3134144,3134673,3134144,3134673,3134144,3134144,3134144</t>
         </is>
       </c>
       <c r="D43" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E43" s="0" t="n">
-        <v>400</v>
+        <v>645</v>
       </c>
       <c r="F43" s="0" t="inlineStr">
         <is>
-          <t>第 18 波：16 只 / 目标血量 7186（单怪间隔 0.40s）</t>
+          <t>L1 W18/20; N=25; EHP=6181.500000; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x5,medium:83x1,swarm:84x7,heavy:88x2,medium:123x2</t>
         </is>
       </c>
     </row>
@@ -1602,18 +1602,18 @@
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>15,14,28,126,77,92,12,124,123,117,57,128,119,127,7,18,27</t>
+          <t>3136136,3136673,3136091,3136668,3136709,3136136,3136673,3136107,3136668,3136709,3136136,3136673,3136115,3136988,3136136,3136673,3136136,3136673,3136136,3136673,3136144,3136673,3136144,3136144,3136144,3136144</t>
         </is>
       </c>
       <c r="D44" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E44" s="0" t="n">
-        <v>392</v>
+        <v>630</v>
       </c>
       <c r="F44" s="0" t="inlineStr">
         <is>
-          <t>第 19 波：17 只 / 目标血量 7912（单怪间隔 0.39s）</t>
+          <t>L1 W19/20; N=26; EHP=7013.760000; air:11x1,air:13x1,air:14x1,normal:17x6,normal:18x5,medium:83x2,swarm:84x7,heavy:88x2,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -1623,18 +1623,18 @@
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>92,12,124,123,117,57,128,119,127,7,18,27,116,25,104,22,120,21,132,129</t>
+          <t>3138136,3138673,3138091,3138668,3138709,3138990,3138136,3138673,3138107,3138668,3138709,3138136,3138673,3138115,3138988,3138136,3138673,3138988,3138136,3138673,3138144,3138673,3138144,3138673,3138144,3138144,3138144</t>
         </is>
       </c>
       <c r="D45" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E45" s="0" t="n">
-        <v>384</v>
+        <v>615</v>
       </c>
       <c r="F45" s="0" t="inlineStr">
         <is>
-          <t>第 20 波：20 只 / 目标血量 8711（单怪间隔 0.38s）</t>
+          <t>L1 W20/20; N=27; EHP=9900.225000; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x5,medium:83x2,swarm:84x7,heavy:88x2,elite:123x1,medium:123x2</t>
         </is>
       </c>
     </row>
@@ -1644,18 +1644,18 @@
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>114,96,115,111,49,53,106,59,62,54,107</t>
+          <t>3140136,3140136,3140136,3140136,3140144,3140144,3140144,3140144,3140144</t>
         </is>
       </c>
       <c r="D46" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E46" s="0" t="n">
-        <v>368</v>
+        <v>895</v>
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t>第 21 波：11 只 / 目标血量 9591（单怪间隔 0.37s）</t>
+          <t>L2 W1/20; N=9; EHP=278.100000; normal:17x4,normal:18x5</t>
         </is>
       </c>
     </row>
@@ -1665,18 +1665,18 @@
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>53,106,59,62,54,107,112,113,46,45,51,50,132</t>
+          <t>3142136,3142136,3142136,3142136,3142136,3142144,3142144,3142144,3142144,3142144</t>
         </is>
       </c>
       <c r="D47" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E47" s="0" t="n">
-        <v>360</v>
+        <v>880</v>
       </c>
       <c r="F47" s="0" t="inlineStr">
         <is>
-          <t>第 22 波：13 只 / 目标血量 10560（单怪间隔 0.36s）</t>
+          <t>L2 W2/20; N=10; EHP=351.642000; normal:17x5,normal:18x5</t>
         </is>
       </c>
     </row>
@@ -1686,18 +1686,18 @@
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>107,112,113,46,45,51,50,93,48,55,43,64,44</t>
+          <t>3144136,3144673,3144136,3144673,3144136,3144673,3144136,3144144,3144144,3144144,3144144</t>
         </is>
       </c>
       <c r="D48" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E48" s="0" t="n">
-        <v>352</v>
+        <v>865</v>
       </c>
       <c r="F48" s="0" t="inlineStr">
         <is>
-          <t>第 23 波：13 只 / 目标血量 11627（单怪间隔 0.35s）</t>
+          <t>L2 W3/20; N=11; EHP=445.948800; normal:17x4,normal:18x4,swarm:84x3</t>
         </is>
       </c>
     </row>
@@ -1707,18 +1707,18 @@
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>51,50,93,48,55,43,64,44,109,91,108,42,95,52,132</t>
+          <t>3146136,3146673,3146136,3146673,3146136,3146673,3146136,3146144,3146144,3146144,3146144,3146144</t>
         </is>
       </c>
       <c r="D49" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E49" s="0" t="n">
-        <v>344</v>
+        <v>850</v>
       </c>
       <c r="F49" s="0" t="inlineStr">
         <is>
-          <t>第 24 波：15 只 / 目标血量 12801（单怪间隔 0.34s）</t>
+          <t>L2 W4/20; N=12; EHP=564.357600; normal:17x4,normal:18x5,swarm:84x3</t>
         </is>
       </c>
     </row>
@@ -1728,18 +1728,18 @@
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>43,64,44,109,91,108,42,95,52,60,94,105,114,96,115,130</t>
+          <t>3148136,3148673,3148988,3148136,3148673,3148136,3148673,3148136,3148144,3148144,3148144,3148144,3148144</t>
         </is>
       </c>
       <c r="D50" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E50" s="0" t="n">
-        <v>336</v>
+        <v>835</v>
       </c>
       <c r="F50" s="0" t="inlineStr">
         <is>
-          <t>第 25 波：16 只 / 目标血量 14094（单怪间隔 0.34s）</t>
+          <t>L2 W5/20; N=13; EHP=795.430272; normal:17x4,normal:18x5,swarm:84x3,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -1749,18 +1749,18 @@
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>108,42,95,52,60,94,105,114,96,115,111,49,53,106,59,62,54,132</t>
+          <t>3150136,3150673,3150107,3150668,3150136,3150673,3150988,3150136,3150673,3150136,3150144,3150144,3150144,3150144</t>
         </is>
       </c>
       <c r="D51" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E51" s="0" t="n">
-        <v>320</v>
+        <v>820</v>
       </c>
       <c r="F51" s="0" t="inlineStr">
         <is>
-          <t>第 26 波：18 只 / 目标血量 15517（单怪间隔 0.32s）</t>
+          <t>L2 W6/20; N=14; EHP=886.830000; air:13x1,normal:17x4,normal:18x4,medium:83x1,swarm:84x3,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -1770,18 +1770,18 @@
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>94,105,114,96,115,111,49,53,106,59,62,54,107,112,113,46,45,51,50</t>
+          <t>3152136,3152673,3152091,3152668,3152136,3152673,3152988,3152136,3152673,3152136,3152673,3152144,3152144,3152144,3152144</t>
         </is>
       </c>
       <c r="D52" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E52" s="0" t="n">
-        <v>312</v>
+        <v>805</v>
       </c>
       <c r="F52" s="0" t="inlineStr">
         <is>
-          <t>第 27 波：19 只 / 目标血量 17084（单怪间隔 0.31s）</t>
+          <t>L2 W7/20; N=15; EHP=1097.568000; air:11x1,normal:17x4,normal:18x4,medium:83x1,swarm:84x4,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -1791,18 +1791,18 @@
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>111,49,53,106,59,62,54,107,112,113,46,45,51,50,93,48,55,43,64,44,132</t>
+          <t>3154136,3154673,3154115,3154668,3154136,3154673,3154988,3154136,3154673,3154136,3154673,3154144,3154144,3154144,3154144,3154144</t>
         </is>
       </c>
       <c r="D53" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E53" s="0" t="n">
-        <v>304</v>
+        <v>790</v>
       </c>
       <c r="F53" s="0" t="inlineStr">
         <is>
-          <t>第 28 波：21 只 / 目标血量 18810（单怪间隔 0.30s）</t>
+          <t>L2 W8/20; N=16; EHP=1345.756800; air:14x1,normal:17x4,normal:18x5,medium:83x1,swarm:84x4,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -1812,18 +1812,18 @@
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>62,54,107,112,113,46,45,51,50,93,48,55,43,64,44,109,91,108,42,95,52,60,94</t>
+          <t>3156136,3156673,3156107,3156668,3156136,3156673,3156988,3156136,3156673,3156136,3156673,3156136,3156144,3156144,3156144,3156144,3156144</t>
         </is>
       </c>
       <c r="D54" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E54" s="0" t="n">
-        <v>296</v>
+        <v>775</v>
       </c>
       <c r="F54" s="0" t="inlineStr">
         <is>
-          <t>第 29 波：23 只 / 目标血量 20710（单怪间隔 0.30s）</t>
+          <t>L2 W9/20; N=17; EHP=1634.733600; air:13x1,normal:17x5,normal:18x5,medium:83x1,swarm:84x4,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -1833,18 +1833,18 @@
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>46,45,51,50,93,48,55,43,64,44,109,91,108,42,95,52,60,94,105,114,96,115,111,49,53,132,131</t>
+          <t>3158136,3158673,3158091,3158668,3158136,3158673,3158988,3158136,3158673,3158136,3158673,3158136,3158673,3158144,3158144,3158144,3158144,3158144</t>
         </is>
       </c>
       <c r="D55" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E55" s="0" t="n">
-        <v>288</v>
+        <v>760</v>
       </c>
       <c r="F55" s="0" t="inlineStr">
         <is>
-          <t>第 30 波：27 只 / 目标血量 22801（单怪间隔 0.29s）</t>
+          <t>L2 W10/20; N=18; EHP=2203.975872; air:11x1,normal:17x5,normal:18x5,medium:83x1,swarm:84x5,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -1854,18 +1854,18 @@
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>72,10,6,35,67,61,63,39,9,68</t>
+          <t>3160136,3160673,3160242,3160668,3160709,3160136,3160673,3160242,3160988,3160136,3160673,3160136,3160673,3160144,3160673,3160144,3160144,3160144,3160144</t>
         </is>
       </c>
       <c r="D56" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E56" s="0" t="n">
-        <v>272</v>
+        <v>745</v>
       </c>
       <c r="F56" s="0" t="inlineStr">
         <is>
-          <t>第 31 波：10 只 / 目标血量 25104（单怪间隔 0.27s）</t>
+          <t>L2 W11/20; N=19; EHP=2348.400000; normal:17x4,normal:18x5,fast:30x2,medium:83x1,swarm:84x5,heavy:88x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -1875,18 +1875,18 @@
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>61,63,39,9,68,41,75,32,70,65,58,38,132</t>
+          <t>3162136,3162673,3162242,3162091,3162668,3162709,3162136,3162673,3162242,3162107,3162668,3162709,3162136,3162673,3162988,3162144,3162673,3162144,3162673,3162144</t>
         </is>
       </c>
       <c r="D57" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E57" s="0" t="n">
-        <v>264</v>
+        <v>730</v>
       </c>
       <c r="F57" s="0" t="inlineStr">
         <is>
-          <t>第 32 波：13 只 / 目标血量 27640（单怪间隔 0.26s）</t>
+          <t>L2 W12/20; N=20; EHP=2779.764000; air:11x1,air:13x1,normal:17x3,normal:18x3,fast:30x2,medium:83x2,swarm:84x5,heavy:88x2,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -1896,18 +1896,18 @@
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>41,75,32,70,65,58,38,37,73,47,34,76,66</t>
+          <t>3164136,3164673,3164242,3164091,3164668,3164709,3164136,3164673,3164242,3164115,3164988,3164709,3164136,3164673,3164988,3164144,3164673,3164144,3164673,3164144,3164144</t>
         </is>
       </c>
       <c r="D58" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E58" s="0" t="n">
-        <v>256</v>
+        <v>715</v>
       </c>
       <c r="F58" s="0" t="inlineStr">
         <is>
-          <t>第 33 波：13 只 / 目标血量 30431（单怪间隔 0.26s）</t>
+          <t>L2 W13/20; N=21; EHP=3265.264800; air:11x1,air:14x1,normal:17x3,normal:18x4,fast:30x2,medium:83x1,swarm:84x5,heavy:88x2,medium:123x2</t>
         </is>
       </c>
     </row>
@@ -1917,18 +1917,18 @@
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>58,38,37,73,47,34,76,66,74,40,36,31,69,110,132</t>
+          <t>3166136,3166673,3166242,3166107,3166668,3166709,3166136,3166673,3166242,3166115,3166668,3166709,3166136,3166673,3166988,3166144,3166673,3166144,3166673,3166144,3166673,3166144</t>
         </is>
       </c>
       <c r="D59" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E59" s="0" t="n">
-        <v>248</v>
+        <v>700</v>
       </c>
       <c r="F59" s="0" t="inlineStr">
         <is>
-          <t>第 34 波：15 只 / 目标血量 33505（单怪间隔 0.25s）</t>
+          <t>L2 W14/20; N=22; EHP=3808.239600; air:13x1,air:14x1,normal:17x3,normal:18x4,fast:30x2,medium:83x2,swarm:84x6,heavy:88x2,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -1938,18 +1938,18 @@
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,131</t>
+          <t>3168136,3168673,3168242,3168091,3168668,3168709,3168136,3168673,3168242,3168107,3168868,3168709,3168136,3168673,3168988,3168136,3168673,3168144,3168673,3168144,3168673,3168144,3168144</t>
         </is>
       </c>
       <c r="D60" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E60" s="0" t="n">
-        <v>240</v>
+        <v>685</v>
       </c>
       <c r="F60" s="0" t="inlineStr">
         <is>
-          <t>第 35 波：16 只 / 目标血量 36889（单怪间隔 0.24s）</t>
+          <t>L2 W15/20; N=23; EHP=4941.468672; air:11x1,air:13x1,normal:17x4,normal:18x4,fast:30x2,medium:83x1,swarm:84x6,heavy:88x2,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -1959,18 +1959,18 @@
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,132</t>
+          <t>3170136,3170673,3170242,3170668,3170709,3170136,3170673,3170242,3170868,3170709,3170136,3170673,3170988,3170136,3170673,3170136,3170673,3170144,3170673,3170144,3170144,3170144,3170144,3170144</t>
         </is>
       </c>
       <c r="D61" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E61" s="0" t="n">
-        <v>224</v>
+        <v>670</v>
       </c>
       <c r="F61" s="0" t="inlineStr">
         <is>
-          <t>第 36 波：18 只 / 目标血量 40615（单怪间隔 0.22s）</t>
+          <t>L2 W16/20; N=24; EHP=5140.000000; normal:17x5,normal:18x6,fast:30x2,medium:83x1,swarm:84x6,heavy:88x2,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -1980,18 +1980,18 @@
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65</t>
+          <t>3172136,3172673,3172242,3172091,3172668,3172709,3172136,3172673,3172242,3172107,3172868,3172709,3172136,3172673,3172242,3172115,3172988,3172144,3172673,3172144,3172673,3172144,3172673,3172144,3172673</t>
         </is>
       </c>
       <c r="D62" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E62" s="0" t="n">
-        <v>216</v>
+        <v>655</v>
       </c>
       <c r="F62" s="0" t="inlineStr">
         <is>
-          <t>第 37 波：17 只 / 目标血量 44717（单怪间隔 0.22s）</t>
+          <t>L2 W17/20; N=25; EHP=5815.380000; air:11x1,air:13x1,air:14x1,normal:17x3,normal:18x4,fast:30x3,medium:83x1,swarm:84x7,heavy:88x2,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2001,18 +2001,18 @@
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,132</t>
+          <t>3174136,3174673,3174242,3174091,3174668,3174709,3174136,3174673,3174242,3174107,3174868,3174709,3174136,3174673,3174242,3174115,3174988,3174136,3174673,3174144,3174673,3174144,3174673,3174144,3174673,3174144</t>
         </is>
       </c>
       <c r="D63" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E63" s="0" t="n">
-        <v>208</v>
+        <v>640</v>
       </c>
       <c r="F63" s="0" t="inlineStr">
         <is>
-          <t>第 38 波：21 只 / 目标血量 49233（单怪间隔 0.21s）</t>
+          <t>L2 W18/20; N=26; EHP=6621.622800; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x3,medium:83x1,swarm:84x7,heavy:88x2,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2022,18 +2022,18 @@
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110</t>
+          <t>3176136,3176673,3176242,3176091,3176668,3176709,3176136,3176673,3176242,3176107,3176668,3176709,3176136,3176673,3176242,3176115,3176868,3176136,3176673,3176988,3176144,3176673,3176144,3176673,3176144,3176673,3176144</t>
         </is>
       </c>
       <c r="D64" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E64" s="0" t="n">
-        <v>200</v>
+        <v>625</v>
       </c>
       <c r="F64" s="0" t="inlineStr">
         <is>
-          <t>第 39 波：21 只 / 目标血量 54206（单怪间隔 0.20s）</t>
+          <t>L2 W19/20; N=27; EHP=7502.025600; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x3,medium:83x2,swarm:84x7,heavy:88x2,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2043,18 +2043,18 @@
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,132,131</t>
+          <t>3178136,3178673,3178242,3178091,3178668,3178709,3178990,3178136,3178673,3178242,3178107,3178868,3178709,3178136,3178673,3178242,3178115,3178988,3178136,3178673,3178988,3178144,3178673,3178144,3178673,3178144,3178673,3178144</t>
         </is>
       </c>
       <c r="D65" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E65" s="0" t="n">
-        <v>192</v>
+        <v>610</v>
       </c>
       <c r="F65" s="0" t="inlineStr">
         <is>
-          <t>第 40 波：26 只 / 目标血量 59681（单怪间隔 0.19s）</t>
+          <t>L2 W20/20; N=28; EHP=10574.907000; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x3,medium:83x1,swarm:84x7,heavy:88x2,medium:108x1,elite:123x1,medium:123x2</t>
         </is>
       </c>
     </row>
@@ -2064,18 +2064,18 @@
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68</t>
+          <t>3180136,3180136,3180136,3180136,3180136,3180144,3180144,3180144,3180144,3180144</t>
         </is>
       </c>
       <c r="D66" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E66" s="0" t="n">
-        <v>176</v>
+        <v>890</v>
       </c>
       <c r="F66" s="0" t="inlineStr">
         <is>
-          <t>第 41 波：24 只 / 目标血量 60158（单怪间隔 0.18s）</t>
+          <t>L3 W1/20; N=10; EHP=318.000000; normal:17x5,normal:18x5</t>
         </is>
       </c>
     </row>
@@ -2085,18 +2085,18 @@
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,132</t>
+          <t>3182136,3182136,3182136,3182136,3182136,3182136,3182144,3182144,3182144,3182144,3182144</t>
         </is>
       </c>
       <c r="D67" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E67" s="0" t="n">
-        <v>170</v>
+        <v>875</v>
       </c>
       <c r="F67" s="0" t="inlineStr">
         <is>
-          <t>第 42 波：25 只 / 目标血量 60640（单怪间隔 0.17s）</t>
+          <t>L3 W2/20; N=11; EHP=398.072400; normal:17x6,normal:18x5</t>
         </is>
       </c>
     </row>
@@ -2106,18 +2106,18 @@
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76</t>
+          <t>3184136,3184673,3184136,3184673,3184136,3184673,3184136,3184136,3184144,3184144,3184144,3184144</t>
         </is>
       </c>
       <c r="D68" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E68" s="0" t="n">
-        <v>170</v>
+        <v>860</v>
       </c>
       <c r="F68" s="0" t="inlineStr">
         <is>
-          <t>第 43 波：26 只 / 目标血量 61125（单怪间隔 0.17s）</t>
+          <t>L3 W3/20; N=12; EHP=500.659200; normal:17x5,normal:18x4,swarm:84x3</t>
         </is>
       </c>
     </row>
@@ -2127,18 +2127,18 @@
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,132</t>
+          <t>3186136,3186673,3186136,3186673,3186136,3186673,3186136,3186136,3186144,3186144,3186144,3186144,3186144</t>
         </is>
       </c>
       <c r="D69" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E69" s="0" t="n">
-        <v>170</v>
+        <v>845</v>
       </c>
       <c r="F69" s="0" t="inlineStr">
         <is>
-          <t>第 44 波：27 只 / 目标血量 61614（单怪间隔 0.17s）</t>
+          <t>L3 W4/20; N=13; EHP=629.194800; normal:17x5,normal:18x5,swarm:84x3</t>
         </is>
       </c>
     </row>
@@ -2148,18 +2148,18 @@
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,129</t>
+          <t>3188136,3188673,3188668,3188136,3188673,3188868,3188136,3188673,3188136,3188136,3188144,3188144,3188144,3188144</t>
         </is>
       </c>
       <c r="D70" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E70" s="0" t="n">
-        <v>170</v>
+        <v>830</v>
       </c>
       <c r="F70" s="0" t="inlineStr">
         <is>
-          <t>第 45 波：27 只 / 目标血量 62107（单怪间隔 0.17s）</t>
+          <t>L3 W5/20; N=14; EHP=881.567232; normal:17x5,normal:18x4,medium:83x1,swarm:84x3,medium:108x1</t>
         </is>
       </c>
     </row>
@@ -2169,18 +2169,18 @@
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,132</t>
+          <t>3190136,3190673,3190242,3190107,3190668,3190136,3190673,3190988,3190136,3190673,3190136,3190673,3190144,3190144,3190144</t>
         </is>
       </c>
       <c r="D71" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E71" s="0" t="n">
-        <v>170</v>
+        <v>815</v>
       </c>
       <c r="F71" s="0" t="inlineStr">
         <is>
-          <t>第 46 波：26 只 / 目标血量 62604（单怪间隔 0.17s）</t>
+          <t>L3 W6/20; N=15; EHP=977.850000; air:13x1,normal:17x4,normal:18x3,fast:30x1,medium:83x1,swarm:84x4,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2190,18 +2190,18 @@
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68</t>
+          <t>3192136,3192673,3192242,3192091,3192868,3192136,3192673,3192988,3192136,3192673,3192136,3192673,3192144,3192144,3192144,3192144</t>
         </is>
       </c>
       <c r="D72" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E72" s="0" t="n">
-        <v>170</v>
+        <v>800</v>
       </c>
       <c r="F72" s="0" t="inlineStr">
         <is>
-          <t>第 47 波：26 只 / 目标血量 63104（单怪间隔 0.17s）</t>
+          <t>L3 W7/20; N=16; EHP=1204.838400; air:11x1,normal:17x4,normal:18x4,fast:30x1,swarm:84x4,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2211,18 +2211,18 @@
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,132</t>
+          <t>3194136,3194673,3194242,3194115,3194668,3194136,3194673,3194242,3194868,3194136,3194673,3194136,3194673,3194144,3194144,3194144,3194144</t>
         </is>
       </c>
       <c r="D73" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E73" s="0" t="n">
-        <v>170</v>
+        <v>785</v>
       </c>
       <c r="F73" s="0" t="inlineStr">
         <is>
-          <t>第 48 波：27 只 / 目标血量 63609（单怪间隔 0.17s）</t>
+          <t>L3 W8/20; N=17; EHP=1471.513200; air:14x1,normal:17x4,normal:18x4,fast:30x2,medium:83x1,swarm:84x4,medium:108x1</t>
         </is>
       </c>
     </row>
@@ -2232,18 +2232,18 @@
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47</t>
+          <t>3196136,3196673,3196242,3196107,3196668,3196136,3196673,3196242,3196988,3196136,3196673,3196136,3196673,3196144,3196673,3196144,3196144,3196144</t>
         </is>
       </c>
       <c r="D74" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E74" s="0" t="n">
-        <v>170</v>
+        <v>770</v>
       </c>
       <c r="F74" s="0" t="inlineStr">
         <is>
-          <t>第 49 波：26 只 / 目标血量 64118（单怪间隔 0.17s）</t>
+          <t>L3 W9/20; N=18; EHP=1781.308800; air:13x1,normal:17x4,normal:18x4,fast:30x2,medium:83x1,swarm:84x5,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2253,18 +2253,18 @@
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,132,130</t>
+          <t>3198136,3198673,3198242,3198091,3198868,3198136,3198673,3198242,3198988,3198136,3198673,3198136,3198673,3198136,3198673,3198144,3198144,3198144,3198144</t>
         </is>
       </c>
       <c r="D75" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E75" s="0" t="n">
-        <v>170</v>
+        <v>755</v>
       </c>
       <c r="F75" s="0" t="inlineStr">
         <is>
-          <t>第 50 波：27 只 / 目标血量 64631（单怪间隔 0.17s）</t>
+          <t>L3 W10/20; N=19; EHP=2394.178752; air:11x1,normal:17x5,normal:18x4,fast:30x2,swarm:84x5,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2274,18 +2274,18 @@
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33</t>
+          <t>3200136,3200673,3200242,3200668,3200709,3200136,3200673,3200786,3200868,3200709,3200136,3200673,3200988,3200136,3200673,3200144,3200673,3200144,3200144,3200144</t>
         </is>
       </c>
       <c r="D76" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E76" s="0" t="n">
-        <v>170</v>
+        <v>740</v>
       </c>
       <c r="F76" s="0" t="inlineStr">
         <is>
-          <t>第 51 波：27 只 / 目标血量 65148（单怪间隔 0.17s）</t>
+          <t>L3 W11/20; N=20; EHP=2544.000000; normal:17x4,normal:18x4,fast:30x1,medium:83x1,swarm:84x5,heavy:88x2,fast:98x1,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2295,18 +2295,18 @@
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,132</t>
+          <t>3202136,3202673,3202242,3202091,3202668,3202709,3202136,3202673,3202786,3202107,3202868,3202709,3202136,3202673,3202988,3202136,3202673,3202144,3202673,3202144,3202144</t>
         </is>
       </c>
       <c r="D77" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E77" s="0" t="n">
-        <v>170</v>
+        <v>725</v>
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t>第 52 波：27 只 / 目标血量 65669（单怪间隔 0.17s）</t>
+          <t>L3 W12/20; N=21; EHP=3003.764400; air:11x1,air:13x1,normal:17x4,normal:18x3,fast:30x1,medium:83x1,swarm:84x5,heavy:88x2,fast:98x1,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2316,18 +2316,18 @@
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68</t>
+          <t>3204136,3204673,3204242,3204091,3204668,3204709,3204136,3204673,3204786,3204115,3204868,3204709,3204136,3204673,3204988,3204136,3204673,3204144,3204673,3204144,3204673,3204144</t>
         </is>
       </c>
       <c r="D78" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E78" s="0" t="n">
-        <v>170</v>
+        <v>710</v>
       </c>
       <c r="F78" s="0" t="inlineStr">
         <is>
-          <t>第 53 波：28 只 / 目标血量 66195（单怪间隔 0.17s）</t>
+          <t>L3 W13/20; N=22; EHP=3520.387200; air:11x1,air:14x1,normal:17x4,normal:18x3,fast:30x1,medium:83x1,swarm:84x6,heavy:88x2,fast:98x1,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2337,18 +2337,18 @@
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,132</t>
+          <t>3206136,3206673,3206242,3206107,3206668,3206709,3206136,3206673,3206786,3206115,3206868,3206709,3206136,3206673,3206988,3206136,3206673,3206144,3206673,3206144,3206673,3206144,3206144</t>
         </is>
       </c>
       <c r="D79" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E79" s="0" t="n">
-        <v>170</v>
+        <v>695</v>
       </c>
       <c r="F79" s="0" t="inlineStr">
         <is>
-          <t>第 54 波：29 只 / 目标血量 66724（单怪间隔 0.17s）</t>
+          <t>L3 W14/20; N=23; EHP=4097.302800; air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x1,medium:83x1,swarm:84x6,heavy:88x2,fast:98x1,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2358,18 +2358,18 @@
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,131</t>
+          <t>3208136,3208673,3208242,3208091,3208668,3208709,3208136,3208673,3208786,3208107,3208868,3208709,3208136,3208673,3208988,3208136,3208673,3208136,3208673,3208144,3208673,3208144,3208144,3208144</t>
         </is>
       </c>
       <c r="D80" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E80" s="0" t="n">
-        <v>170</v>
+        <v>680</v>
       </c>
       <c r="F80" s="0" t="inlineStr">
         <is>
-          <t>第 55 波：30 只 / 目标血量 67258（单怪间隔 0.17s）</t>
+          <t>L3 W15/20; N=24; EHP=5306.499072; air:11x1,air:13x1,normal:17x5,normal:18x4,fast:30x1,medium:83x1,swarm:84x6,heavy:88x2,fast:98x1,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2379,18 +2379,18 @@
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,132</t>
+          <t>3210136,3210673,3210242,3210668,3210709,3210136,3210673,3210786,3210868,3210709,3210136,3210673,3210786,3210988,3210136,3210673,3210136,3210673,3210144,3210673,3210144,3210673,3210144,3210144,3210144</t>
         </is>
       </c>
       <c r="D81" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E81" s="0" t="n">
-        <v>170</v>
+        <v>665</v>
       </c>
       <c r="F81" s="0" t="inlineStr">
         <is>
-          <t>第 56 波：28 只 / 目标血量 67796（单怪间隔 0.17s）</t>
+          <t>L3 W16/20; N=25; EHP=5519.000000; normal:17x5,normal:18x5,fast:30x1,medium:83x1,swarm:84x7,heavy:88x2,fast:98x2,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2400,18 +2400,18 @@
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33</t>
+          <t>3212136,3212673,3212242,3212091,3212668,3212709,3212136,3212673,3212242,3212107,3212868,3212709,3212136,3212673,3212786,3212115,3212988,3212136,3212673,3212144,3212673,3212144,3212673,3212144,3212673,3212144</t>
         </is>
       </c>
       <c r="D82" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E82" s="0" t="n">
-        <v>170</v>
+        <v>650</v>
       </c>
       <c r="F82" s="0" t="inlineStr">
         <is>
-          <t>第 57 波：29 只 / 目标血量 68338（单怪间隔 0.17s）</t>
+          <t>L3 W17/20; N=26; EHP=6224.150400; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x2,medium:83x1,swarm:84x7,heavy:88x2,fast:98x1,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2421,18 +2421,18 @@
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,132</t>
+          <t>3214136,3214673,3214242,3214091,3214668,3214709,3214136,3214673,3214786,3214107,3214668,3214709,3214136,3214673,3214786,3214115,3214868,3214136,3214673,3214988,3214144,3214673,3214144,3214673,3214144,3214673,3214144</t>
         </is>
       </c>
       <c r="D83" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E83" s="0" t="n">
-        <v>170</v>
+        <v>635</v>
       </c>
       <c r="F83" s="0" t="inlineStr">
         <is>
-          <t>第 58 波：28 只 / 目标血量 68885（单怪间隔 0.17s）</t>
+          <t>L3 W18/20; N=27; EHP=7076.581200; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x1,medium:83x2,swarm:84x7,heavy:88x2,fast:98x2,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2442,18 +2442,18 @@
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39</t>
+          <t>3216136,3216673,3216242,3216091,3216668,3216709,3216136,3216673,3216242,3216107,3216868,3216709,3216136,3216673,3216786,3216115,3216988,3216136,3216673,3216988,3216136,3216673,3216144,3216673,3216144,3216673,3216144,3216144</t>
         </is>
       </c>
       <c r="D84" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E84" s="0" t="n">
-        <v>170</v>
+        <v>620</v>
       </c>
       <c r="F84" s="0" t="inlineStr">
         <is>
-          <t>第 59 波：28 只 / 目标血量 69436（单怪间隔 0.17s）</t>
+          <t>L3 W19/20; N=28; EHP=8006.476800; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x4,fast:30x2,medium:83x1,swarm:84x7,heavy:88x2,fast:98x1,medium:108x1,medium:123x2</t>
         </is>
       </c>
     </row>
@@ -2463,18 +2463,18 @@
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,132,129</t>
+          <t>3218136,3218673,3218242,3218091,3218668,3218709,3218990,3218136,3218673,3218786,3218107,3218868,3218709,3218136,3218673,3218786,3218115,3218868,3218136,3218673,3218988,3218144,3218673,3218144,3218673,3218144,3218673,3218144,3218673</t>
         </is>
       </c>
       <c r="D85" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E85" s="0" t="n">
-        <v>170</v>
+        <v>605</v>
       </c>
       <c r="F85" s="0" t="inlineStr">
         <is>
-          <t>第 60 波：31 只 / 目标血量 69992（单怪间隔 0.17s）</t>
+          <t>L3 W20/20; N=29; EHP=11271.589500; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x1,medium:83x1,swarm:84x8,heavy:88x2,fast:98x2,medium:108x2,elite:123x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2484,18 +2484,18 @@
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73</t>
+          <t>3220136,3220136,3220136,3220136,3220136,3220144,3220144,3220144,3220144,3220144,3220144</t>
         </is>
       </c>
       <c r="D86" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E86" s="0" t="n">
-        <v>170</v>
+        <v>885</v>
       </c>
       <c r="F86" s="0" t="inlineStr">
         <is>
-          <t>第 61 波：29 只 / 目标血量 70552（单怪间隔 0.17s）</t>
+          <t>L4 W1/20; N=11; EHP=359.700000; normal:17x5,normal:18x6</t>
         </is>
       </c>
     </row>
@@ -2505,18 +2505,18 @@
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,132</t>
+          <t>3222136,3222136,3222136,3222136,3222136,3222136,3222144,3222144,3222144,3222144,3222144,3222144</t>
         </is>
       </c>
       <c r="D87" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E87" s="0" t="n">
-        <v>170</v>
+        <v>870</v>
       </c>
       <c r="F87" s="0" t="inlineStr">
         <is>
-          <t>第 62 波：30 只 / 目标血量 71116（单怪间隔 0.17s）</t>
+          <t>L4 W2/20; N=12; EHP=446.551200; normal:17x6,normal:18x6</t>
         </is>
       </c>
     </row>
@@ -2526,18 +2526,18 @@
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69</t>
+          <t>3224136,3224673,3224136,3224673,3224136,3224673,3224136,3224136,3224144,3224144,3224144,3224144,3224144</t>
         </is>
       </c>
       <c r="D88" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E88" s="0" t="n">
-        <v>170</v>
+        <v>855</v>
       </c>
       <c r="F88" s="0" t="inlineStr">
         <is>
-          <t>第 63 波：28 只 / 目标血量 71685（单怪间隔 0.17s）</t>
+          <t>L4 W3/20; N=13; EHP=557.731200; normal:17x5,normal:18x5,swarm:84x3</t>
         </is>
       </c>
     </row>
@@ -2547,18 +2547,18 @@
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,132</t>
+          <t>3226136,3226673,3226136,3226673,3226136,3226673,3226136,3226136,3226144,3226144,3226144,3226144,3226144,3226144</t>
         </is>
       </c>
       <c r="D89" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E89" s="0" t="n">
-        <v>170</v>
+        <v>840</v>
       </c>
       <c r="F89" s="0" t="inlineStr">
         <is>
-          <t>第 64 波：31 只 / 目标血量 72258（单怪间隔 0.17s）</t>
+          <t>L4 W4/20; N=14; EHP=696.771600; normal:17x5,normal:18x6,swarm:84x3</t>
         </is>
       </c>
     </row>
@@ -2568,18 +2568,18 @@
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,130</t>
+          <t>3228136,3228673,3228668,3228136,3228673,3228988,3228136,3228673,3228136,3228673,3228144,3228144,3228144,3228144,3228144</t>
         </is>
       </c>
       <c r="D90" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E90" s="0" t="n">
-        <v>170</v>
+        <v>825</v>
       </c>
       <c r="F90" s="0" t="inlineStr">
         <is>
-          <t>第 65 波：32 只 / 目标血量 72837（单怪间隔 0.17s）</t>
+          <t>L4 W5/20; N=15; EHP=971.268480; normal:17x4,normal:18x5,medium:83x1,swarm:84x4,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2589,18 +2589,18 @@
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,132</t>
+          <t>3230136,3230673,3230242,3230107,3230868,3230136,3230673,3230988,3230136,3230673,3230136,3230673,3230144,3230144,3230144,3230144</t>
         </is>
       </c>
       <c r="D91" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E91" s="0" t="n">
-        <v>170</v>
+        <v>810</v>
       </c>
       <c r="F91" s="0" t="inlineStr">
         <is>
-          <t>第 66 波：32 只 / 目标血量 73419（单怪间隔 0.17s）</t>
+          <t>L4 W6/20; N=16; EHP=1072.560000; air:13x1,normal:17x4,normal:18x4,fast:30x1,swarm:84x4,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2610,18 +2610,18 @@
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37</t>
+          <t>3232136,3232673,3232242,3232091,3232668,3232136,3232673,3232786,3232868,3232136,3232673,3232136,3232673,3232144,3232144,3232144,3232144</t>
         </is>
       </c>
       <c r="D92" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E92" s="0" t="n">
-        <v>170</v>
+        <v>795</v>
       </c>
       <c r="F92" s="0" t="inlineStr">
         <is>
-          <t>第 67 波：30 只 / 目标血量 74007（单怪间隔 0.17s）</t>
+          <t>L4 W7/20; N=17; EHP=1316.371200; air:11x1,normal:17x4,normal:18x4,fast:30x1,medium:83x1,swarm:84x4,fast:98x1,medium:108x1</t>
         </is>
       </c>
     </row>
@@ -2631,18 +2631,18 @@
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,132</t>
+          <t>3234136,3234673,3234242,3234115,3234668,3234136,3234673,3234786,3234988,3234136,3234673,3234136,3234673,3234144,3234673,3234144,3234144,3234144</t>
         </is>
       </c>
       <c r="D93" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E93" s="0" t="n">
-        <v>170</v>
+        <v>780</v>
       </c>
       <c r="F93" s="0" t="inlineStr">
         <is>
-          <t>第 68 波：32 只 / 目标血量 74599（单怪间隔 0.17s）</t>
+          <t>L4 W8/20; N=18; EHP=1602.169200; air:14x1,normal:17x4,normal:18x4,fast:30x1,medium:83x1,swarm:84x5,fast:98x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2652,18 +2652,18 @@
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69</t>
+          <t>3236136,3236673,3236242,3236107,3236868,3236136,3236673,3236786,3236988,3236136,3236673,3236136,3236673,3236144,3236673,3236144,3236144,3236144,3236144</t>
         </is>
       </c>
       <c r="D94" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E94" s="0" t="n">
-        <v>170</v>
+        <v>765</v>
       </c>
       <c r="F94" s="0" t="inlineStr">
         <is>
-          <t>第 69 波：30 只 / 目标血量 75195（单怪间隔 0.17s）</t>
+          <t>L4 W9/20; N=19; EHP=1933.485600; air:13x1,normal:17x4,normal:18x5,fast:30x1,swarm:84x5,fast:98x1,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2673,18 +2673,18 @@
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,132,131</t>
+          <t>3238136,3238673,3238242,3238091,3238668,3238136,3238673,3238786,3238868,3238136,3238673,3238988,3238136,3238673,3238144,3238673,3238144,3238144,3238144,3238144</t>
         </is>
       </c>
       <c r="D95" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E95" s="0" t="n">
-        <v>170</v>
+        <v>750</v>
       </c>
       <c r="F95" s="0" t="inlineStr">
         <is>
-          <t>第 70 波：32 只 / 目标血量 75797（单怪间隔 0.17s）</t>
+          <t>L4 W10/20; N=20; EHP=2591.514240; air:11x1,normal:17x4,normal:18x5,fast:30x1,medium:83x1,swarm:84x5,fast:98x1,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2694,18 +2694,18 @@
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61</t>
+          <t>3240136,3240673,3240242,3240668,3240645,3240136,3240673,3240786,3240868,3240709,3240136,3240673,3240988,3240136,3240673,3240144,3240673,3240144,3240144,3240144,3240144</t>
         </is>
       </c>
       <c r="D96" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E96" s="0" t="n">
-        <v>170</v>
+        <v>735</v>
       </c>
       <c r="F96" s="0" t="inlineStr">
         <is>
-          <t>第 71 波：30 只 / 目标血量 76403（单怪间隔 0.17s）</t>
+          <t>L4 W11/20; N=21; EHP=2746.800000; normal:17x4,normal:18x5,fast:30x1,heavy:80x1,medium:83x1,swarm:84x5,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2715,18 +2715,18 @@
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,132</t>
+          <t>3242136,3242673,3242242,3242091,3242668,3242645,3242136,3242673,3242786,3242107,3242868,3242709,3242136,3242673,3242988,3242144,3242673,3242144,3242673,3242144,3242673,3242144</t>
         </is>
       </c>
       <c r="D97" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E97" s="0" t="n">
-        <v>170</v>
+        <v>720</v>
       </c>
       <c r="F97" s="0" t="inlineStr">
         <is>
-          <t>第 72 波：32 只 / 目标血量 77015（单怪间隔 0.17s）</t>
+          <t>L4 W12/20; N=22; EHP=3235.861200; air:11x1,air:13x1,normal:17x3,normal:18x4,fast:30x1,heavy:80x1,medium:83x1,swarm:84x6,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2736,18 +2736,18 @@
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37</t>
+          <t>3244136,3244673,3244242,3244091,3244668,3244645,3244136,3244673,3244786,3244115,3244868,3244709,3244136,3244673,3244988,3244136,3244673,3244144,3244673,3244144,3244673,3244144,3244144</t>
         </is>
       </c>
       <c r="D98" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E98" s="0" t="n">
-        <v>170</v>
+        <v>705</v>
       </c>
       <c r="F98" s="0" t="inlineStr">
         <is>
-          <t>第 73 波：32 只 / 目标血量 77631（单怪间隔 0.17s）</t>
+          <t>L4 W13/20; N=23; EHP=3784.567200; air:11x1,air:14x1,normal:17x4,normal:18x4,fast:30x1,heavy:80x1,medium:83x1,swarm:84x6,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2757,18 +2757,18 @@
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,132</t>
+          <t>3246136,3246673,3246242,3246107,3246668,3246645,3246136,3246673,3246786,3246115,3246868,3246709,3246136,3246673,3246988,3246136,3246673,3246144,3246673,3246144,3246673,3246144,3246144,3246144</t>
         </is>
       </c>
       <c r="D99" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E99" s="0" t="n">
-        <v>170</v>
+        <v>690</v>
       </c>
       <c r="F99" s="0" t="inlineStr">
         <is>
-          <t>第 74 波：33 只 / 目标血量 78252（单怪间隔 0.17s）</t>
+          <t>L4 W14/20; N=24; EHP=4396.449600; air:13x1,air:14x1,normal:17x4,normal:18x5,fast:30x1,heavy:80x1,medium:83x1,swarm:84x6,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
         </is>
       </c>
     </row>
@@ -2778,543 +2778,6843 @@
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,129</t>
+          <t>3248136,3248673,3248242,3248091,3248668,3248645,3248136,3248673,3248786,3248107,3248868,3248693,3248136,3248673,3248786,3248115,3248988,3248144,3248673,3248144,3248673,3248144,3248673,3248144,3248673</t>
         </is>
       </c>
       <c r="D100" s="0" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E100" s="0" t="n">
+        <v>675</v>
+      </c>
+      <c r="F100" s="0" t="inlineStr">
+        <is>
+          <t>L4 W15/20; N=25; EHP=5684.044800; air:11x1,air:13x1,air:14x1,normal:17x3,normal:18x4,fast:30x1,heavy:80x1,medium:83x1,swarm:84x7,heavy:86x1,fast:98x2,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="0" t="n">
+        <v>76</v>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>3250136,3250673,3250242,3250668,3250693,3250136,3250673,3250242,3250868,3250709,3250136,3250673,3250786,3250988,3250136,3250673,3250136,3250673,3250144,3250673,3250144,3250673,3250144,3250144,3250144,3250144</t>
+        </is>
+      </c>
+      <c r="D101" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="0" t="n">
+        <v>660</v>
+      </c>
+      <c r="F101" s="0" t="inlineStr">
+        <is>
+          <t>L4 W16/20; N=26; EHP=5912.000000; normal:17x5,normal:18x6,fast:30x2,medium:83x1,swarm:84x7,heavy:86x1,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>3252136,3252673,3252242,3252091,3252668,3252645,3252136,3252673,3252786,3252107,3252668,3252709,3252136,3252673,3252786,3252115,3252868,3252136,3252673,3252988,3252144,3252673,3252144,3252673,3252144,3252673,3252144</t>
+        </is>
+      </c>
+      <c r="D102" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="0" t="n">
+        <v>645</v>
+      </c>
+      <c r="F102" s="0" t="inlineStr">
+        <is>
+          <t>L4 W17/20; N=27; EHP=6646.471200; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x1,heavy:80x1,medium:83x2,swarm:84x7,heavy:88x1,fast:98x2,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>3254136,3254673,3254242,3254091,3254668,3254645,3254136,3254673,3254242,3254107,3254868,3254693,3254136,3254673,3254786,3254115,3254988,3254136,3254673,3254988,3254144,3254673,3254144,3254673,3254144,3254673,3254144,3254144</t>
+        </is>
+      </c>
+      <c r="D103" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="0" t="n">
+        <v>630</v>
+      </c>
+      <c r="F103" s="0" t="inlineStr">
+        <is>
+          <t>L4 W18/20; N=28; EHP=7546.375200; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x5,fast:30x2,heavy:80x1,medium:83x1,swarm:84x7,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>3256136,3256673,3256242,3256091,3256668,3256693,3256136,3256673,3256786,3256107,3256868,3256709,3256136,3256673,3256786,3256115,3256868,3256136,3256673,3256988,3256144,3256673,3256144,3256673,3256144,3256673,3256144,3256673,3256144</t>
+        </is>
+      </c>
+      <c r="D104" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="0" t="n">
+        <v>615</v>
+      </c>
+      <c r="F104" s="0" t="inlineStr">
+        <is>
+          <t>L4 W19/20; N=29; EHP=8527.113600; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x5,fast:30x1,medium:83x1,swarm:84x8,heavy:86x1,heavy:88x1,fast:98x2,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t>3258136,3258673,3258242,3258091,3258668,3258645,3258990,3258136,3258673,3258242,3258107,3258668,3258693,3258136,3258673,3258786,3258115,3258868,3258709,3258136,3258673,3258988,3258144,3258673,3258144,3258673,3258144,3258673,3258144,3258673</t>
+        </is>
+      </c>
+      <c r="D105" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="F105" s="0" t="inlineStr">
+        <is>
+          <t>L4 W20/20; N=30; EHP=11990.272500; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x2,heavy:80x1,medium:83x2,swarm:84x8,heavy:86x1,heavy:88x1,fast:98x1,medium:108x1,elite:123x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="0" t="n">
+        <v>81</v>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t>3260136,3260136,3260136,3260136,3260136,3260136,3260144,3260144,3260144,3260144,3260144,3260144</t>
+        </is>
+      </c>
+      <c r="D106" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="0" t="n">
+        <v>880</v>
+      </c>
+      <c r="F106" s="0" t="inlineStr">
+        <is>
+          <t>L5 W1/20; N=12; EHP=403.200000; normal:17x6,normal:18x6</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t>3262136,3262136,3262136,3262136,3262136,3262136,3262136,3262144,3262144,3262144,3262144,3262144,3262144</t>
+        </is>
+      </c>
+      <c r="D107" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="0" t="n">
+        <v>865</v>
+      </c>
+      <c r="F107" s="0" t="inlineStr">
+        <is>
+          <t>L5 W2/20; N=13; EHP=497.078400; normal:17x7,normal:18x6</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t>3264136,3264673,3264136,3264673,3264136,3264673,3264136,3264136,3264136,3264144,3264144,3264144,3264144,3264144</t>
+        </is>
+      </c>
+      <c r="D108" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="0" t="n">
+        <v>850</v>
+      </c>
+      <c r="F108" s="0" t="inlineStr">
+        <is>
+          <t>L5 W3/20; N=14; EHP=617.164800; normal:17x6,normal:18x5,swarm:84x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t>3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266673,3266136,3266136,3266144,3266144,3266144,3266144,3266144</t>
+        </is>
+      </c>
+      <c r="D109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="0" t="n">
+        <v>835</v>
+      </c>
+      <c r="F109" s="0" t="inlineStr">
+        <is>
+          <t>L5 W4/20; N=15; EHP=767.088000; normal:17x6,normal:18x5,swarm:84x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t>3268136,3268673,3268868,3268136,3268673,3268988,3268136,3268673,3268136,3268673,3268136,3268144,3268144,3268144,3268144,3268144</t>
+        </is>
+      </c>
+      <c r="D110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="0" t="n">
+        <v>820</v>
+      </c>
+      <c r="F110" s="0" t="inlineStr">
+        <is>
+          <t>L5 W5/20; N=16; EHP=1064.534016; normal:17x5,normal:18x5,swarm:84x4,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t>3270136,3270673,3270242,3270107,3270668,3270136,3270673,3270786,3270868,3270136,3270673,3270136,3270673,3270144,3270144,3270144,3270144</t>
+        </is>
+      </c>
+      <c r="D111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="0" t="n">
+        <v>805</v>
+      </c>
+      <c r="F111" s="0" t="inlineStr">
+        <is>
+          <t>L5 W6/20; N=17; EHP=1170.960000; air:13x1,normal:17x4,normal:18x4,fast:30x1,medium:83x1,swarm:84x4,fast:98x1,medium:108x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t>3272136,3272673,3272242,3272091,3272668,3272136,3272673,3272786,3272988,3272136,3272673,3272136,3272673,3272144,3272673,3272144,3272144,3272144</t>
+        </is>
+      </c>
+      <c r="D112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="0" t="n">
+        <v>790</v>
+      </c>
+      <c r="F112" s="0" t="inlineStr">
+        <is>
+          <t>L5 W7/20; N=18; EHP=1432.166400; air:11x1,normal:17x4,normal:18x4,fast:30x1,medium:83x1,swarm:84x5,fast:98x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t>3274136,3274673,3274242,3274115,3274868,3274136,3274673,3274786,3274988,3274136,3274673,3274136,3274673,3274136,3274673,3274144,3274144,3274144,3274144</t>
+        </is>
+      </c>
+      <c r="D113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="0" t="n">
+        <v>775</v>
+      </c>
+      <c r="F113" s="0" t="inlineStr">
+        <is>
+          <t>L5 W8/20; N=19; EHP=1737.724800; air:14x1,normal:17x5,normal:18x4,fast:30x1,swarm:84x5,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>3276136,3276673,3276242,3276107,3276668,3276136,3276673,3276786,3276868,3276136,3276673,3276988,3276136,3276673,3276136,3276673,3276144,3276144,3276144,3276144</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="0" t="n">
+        <v>760</v>
+      </c>
+      <c r="F114" s="0" t="inlineStr">
+        <is>
+          <t>L5 W9/20; N=20; EHP=2091.264000; air:13x1,normal:17x5,normal:18x4,fast:30x1,medium:83x1,swarm:84x5,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>3278136,3278673,3278242,3278091,3278668,3278136,3278673,3278786,3278868,3278136,3278673,3278988,3278136,3278673,3278136,3278673,3278144,3278144,3278144,3278144,3278144</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="0" t="n">
+        <v>745</v>
+      </c>
+      <c r="F115" s="0" t="inlineStr">
+        <is>
+          <t>L5 W10/20; N=21; EHP=2795.982336; air:11x1,normal:17x5,normal:18x5,fast:30x1,medium:83x1,swarm:84x5,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="0" t="n">
+        <v>91</v>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>3280136,3280673,3280242,3280668,3280253,3280136,3280673,3280786,3280868,3280645,3280136,3280673,3280988,3280136,3280673,3280136,3280673,3280144,3280673,3280144,3280144,3280144</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="0" t="n">
+        <v>730</v>
+      </c>
+      <c r="F116" s="0" t="inlineStr">
+        <is>
+          <t>L5 W11/20; N=22; EHP=2956.800000; normal:17x5,normal:18x4,fast:30x1,heavy:31x1,heavy:80x1,medium:83x1,swarm:84x6,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="0" t="n">
+        <v>92</v>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>3282136,3282673,3282242,3282091,3282668,3282645,3282136,3282673,3282786,3282107,3282868,3282693,3282136,3282673,3282988,3282136,3282673,3282144,3282673,3282144,3282673,3282144,3282144</t>
+        </is>
+      </c>
+      <c r="D117" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="0" t="n">
+        <v>715</v>
+      </c>
+      <c r="F117" s="0" t="inlineStr">
+        <is>
+          <t>L5 W12/20; N=23; EHP=3476.054400; air:11x1,air:13x1,normal:17x4,normal:18x4,fast:30x1,heavy:80x1,medium:83x1,swarm:84x6,heavy:86x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="0" t="n">
+        <v>93</v>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t>3284136,3284673,3284242,3284091,3284668,3284253,3284136,3284673,3284786,3284115,3284868,3284693,3284136,3284673,3284988,3284136,3284673,3284136,3284673,3284144,3284673,3284144,3284144,3284144</t>
+        </is>
+      </c>
+      <c r="D118" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="0" t="n">
+        <v>700</v>
+      </c>
+      <c r="F118" s="0" t="inlineStr">
+        <is>
+          <t>L5 W13/20; N=24; EHP=4057.804800; air:11x1,air:14x1,normal:17x5,normal:18x4,fast:30x1,heavy:31x1,medium:83x1,swarm:84x6,heavy:86x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>3286136,3286673,3286242,3286091,3286668,3286253,3286136,3286673,3286786,3286107,3286868,3286709,3286136,3286673,3286786,3286115,3286988,3286136,3286673,3286144,3286673,3286144,3286673,3286144,3286673</t>
+        </is>
+      </c>
+      <c r="D119" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="0" t="n">
+        <v>685</v>
+      </c>
+      <c r="F119" s="0" t="inlineStr">
+        <is>
+          <t>L5 W14/20; N=25; EHP=4705.680000; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x3,fast:30x1,heavy:31x1,medium:83x1,swarm:84x7,heavy:88x1,fast:98x2,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>3288136,3288673,3288242,3288091,3288668,3288645,3288254,3288136,3288673,3288242,3288107,3288868,3288709,3288136,3288673,3288786,3288115,3288988,3288136,3288673,3288144,3288673,3288144,3288673,3288144,3288673</t>
+        </is>
+      </c>
+      <c r="D120" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="0" t="n">
+        <v>670</v>
+      </c>
+      <c r="F120" s="0" t="inlineStr">
+        <is>
+          <t>L5 W15/20; N=26; EHP=6074.105856; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x3,fast:30x2,elite:31x1,heavy:80x1,medium:83x1,swarm:84x7,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t>3290136,3290673,3290242,3290668,3290645,3290136,3290673,3290786,3290668,3290693,3290136,3290673,3290786,3290868,3290136,3290673,3290988,3290136,3290673,3290136,3290673,3290144,3290673,3290144,3290144,3290144,3290144</t>
+        </is>
+      </c>
+      <c r="D121" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="0" t="n">
+        <v>655</v>
+      </c>
+      <c r="F121" s="0" t="inlineStr">
+        <is>
+          <t>L5 W16/20; N=27; EHP=6318.000000; normal:17x6,normal:18x5,fast:30x1,heavy:80x1,medium:83x2,swarm:84x7,heavy:86x1,fast:98x2,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="0" t="n">
+        <v>97</v>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>3292136,3292673,3292242,3292091,3292668,3292253,3292136,3292673,3292242,3292107,3292868,3292693,3292136,3292673,3292786,3292115,3292988,3292136,3292673,3292988,3292136,3292673,3292144,3292673,3292144,3292673,3292144,3292144</t>
+        </is>
+      </c>
+      <c r="D122" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="0" t="n">
+        <v>640</v>
+      </c>
+      <c r="F122" s="0" t="inlineStr">
+        <is>
+          <t>L5 W17/20; N=28; EHP=7082.342400; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x4,fast:30x2,heavy:31x1,medium:83x1,swarm:84x7,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>3294136,3294673,3294242,3294091,3294668,3294253,3294136,3294673,3294786,3294107,3294868,3294709,3294136,3294673,3294786,3294115,3294868,3294136,3294673,3294988,3294136,3294673,3294144,3294673,3294144,3294673,3294144,3294673,3294144</t>
+        </is>
+      </c>
+      <c r="D123" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="0" t="n">
+        <v>625</v>
+      </c>
+      <c r="F123" s="0" t="inlineStr">
+        <is>
+          <t>L5 W18/20; N=29; EHP=8031.004800; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x4,fast:30x1,heavy:31x1,medium:83x1,swarm:84x8,heavy:88x1,fast:98x2,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="0" t="n">
+        <v>99</v>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t>3296136,3296673,3296242,3296091,3296668,3296645,3296136,3296673,3296242,3296107,3296668,3296693,3296136,3296673,3296786,3296115,3296868,3296709,3296136,3296673,3296988,3296136,3296673,3296144,3296673,3296144,3296673,3296144,3296673,3296144</t>
+        </is>
+      </c>
+      <c r="D124" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="0" t="n">
+        <v>610</v>
+      </c>
+      <c r="F124" s="0" t="inlineStr">
+        <is>
+          <t>L5 W19/20; N=30; EHP=9063.936000; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x4,fast:30x2,heavy:80x1,medium:83x2,swarm:84x8,heavy:86x1,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t>3298136,3298673,3298242,3298091,3298668,3298253,3298990,3298136,3298673,3298786,3298107,3298868,3298645,3298136,3298673,3298786,3298115,3298988,3298693,3298136,3298673,3298988,3298136,3298673,3298144,3298673,3298144,3298673,3298144,3298673,3298144</t>
+        </is>
+      </c>
+      <c r="D125" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="0" t="n">
+        <v>595</v>
+      </c>
+      <c r="F125" s="0" t="inlineStr">
+        <is>
+          <t>L5 W20/20; N=31; EHP=12730.956000; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x4,fast:30x1,heavy:31x1,heavy:80x1,medium:83x1,swarm:84x8,heavy:86x1,fast:98x2,medium:108x1,elite:123x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t>3300136,3300136,3300136,3300136,3300136,3300136,3300144,3300144,3300144,3300144,3300144,3300144,3300144</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="0" t="n">
+        <v>875</v>
+      </c>
+      <c r="F126" s="0" t="inlineStr">
+        <is>
+          <t>L6 W1/20; N=13; EHP=448.500000; normal:17x6,normal:18x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="0" t="n">
+        <v>102</v>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t>3302136,3302136,3302136,3302136,3302136,3302136,3302136,3302144,3302144,3302144,3302144,3302144,3302144,3302144</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="0" t="n">
+        <v>860</v>
+      </c>
+      <c r="F127" s="0" t="inlineStr">
+        <is>
+          <t>L6 W2/20; N=14; EHP=549.654000; normal:17x7,normal:18x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304673,3304136,3304144,3304144,3304144,3304144,3304144,3304144</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="0" t="n">
+        <v>845</v>
+      </c>
+      <c r="F128" s="0" t="inlineStr">
+        <is>
+          <t>L6 W3/20; N=15; EHP=678.960000; normal:17x5,normal:18x6,swarm:84x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="C129" s="0" t="inlineStr">
+        <is>
+          <t>3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306673,3306136,3306136,3306144,3306144,3306144,3306144,3306144,3306144</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="0" t="n">
+        <v>830</v>
+      </c>
+      <c r="F129" s="0" t="inlineStr">
+        <is>
+          <t>L6 W4/20; N=16; EHP=840.144000; normal:17x6,normal:18x6,swarm:84x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="0" t="n">
+        <v>105</v>
+      </c>
+      <c r="C130" s="0" t="inlineStr">
+        <is>
+          <t>3308136,3308673,3308668,3308136,3308673,3308868,3308136,3308673,3308136,3308673,3308136,3308144,3308144,3308144,3308144,3308144,3308144</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="0" t="n">
+        <v>815</v>
+      </c>
+      <c r="F130" s="0" t="inlineStr">
+        <is>
+          <t>L6 W5/20; N=17; EHP=1161.363840; normal:17x5,normal:18x6,medium:83x1,swarm:84x4,medium:108x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="0" t="n">
+        <v>106</v>
+      </c>
+      <c r="C131" s="0" t="inlineStr">
+        <is>
+          <t>3310136,3310673,3310242,3310107,3310668,3310136,3310673,3310786,3310988,3310136,3310673,3310136,3310673,3310144,3310673,3310144,3310144,3310144</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="F131" s="0" t="inlineStr">
+        <is>
+          <t>L6 W6/20; N=18; EHP=1273.050000; air:13x1,normal:17x4,normal:18x4,fast:30x1,medium:83x1,swarm:84x5,fast:98x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="0" t="n">
+        <v>107</v>
+      </c>
+      <c r="C132" s="0" t="inlineStr">
+        <is>
+          <t>3312136,3312673,3312242,3312091,3312868,3312136,3312673,3312786,3312988,3312136,3312673,3312136,3312673,3312144,3312673,3312144,3312144,3312144,3312144</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="0" t="n">
+        <v>785</v>
+      </c>
+      <c r="F132" s="0" t="inlineStr">
+        <is>
+          <t>L6 W7/20; N=19; EHP=1552.224000; air:11x1,normal:17x4,normal:18x5,fast:30x1,swarm:84x5,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="0" t="n">
+        <v>108</v>
+      </c>
+      <c r="C133" s="0" t="inlineStr">
+        <is>
+          <t>3314136,3314673,3314242,3314115,3314668,3314136,3314673,3314786,3314868,3314136,3314673,3314988,3314136,3314673,3314144,3314673,3314144,3314144,3314144,3314144</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="0" t="n">
+        <v>770</v>
+      </c>
+      <c r="F133" s="0" t="inlineStr">
+        <is>
+          <t>L6 W8/20; N=20; EHP=1878.180000; air:14x1,normal:17x4,normal:18x5,fast:30x1,medium:83x1,swarm:84x5,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="0" t="n">
+        <v>109</v>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t>3316136,3316673,3316242,3316107,3316668,3316136,3316673,3316786,3316868,3316136,3316673,3316988,3316136,3316673,3316136,3316673,3316144,3316144,3316144,3316144,3316144</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="0" t="n">
+        <v>755</v>
+      </c>
+      <c r="F134" s="0" t="inlineStr">
+        <is>
+          <t>L6 W9/20; N=21; EHP=2254.644000; air:13x1,normal:17x5,normal:18x5,fast:30x1,medium:83x1,swarm:84x5,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="0" t="n">
+        <v>110</v>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t>3318136,3318673,3318242,3318091,3318668,3318136,3318673,3318786,3318868,3318136,3318673,3318988,3318136,3318673,3318136,3318673,3318144,3318673,3318144,3318144,3318144,3318144</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="0" t="n">
+        <v>740</v>
+      </c>
+      <c r="F135" s="0" t="inlineStr">
+        <is>
+          <t>L6 W10/20; N=22; EHP=3007.583040; air:11x1,normal:17x5,normal:18x5,fast:30x1,medium:83x1,swarm:84x6,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="0" t="n">
+        <v>111</v>
+      </c>
+      <c r="C136" s="0" t="inlineStr">
+        <is>
+          <t>3320136,3320673,3320242,3320668,3320253,3320136,3320673,3320786,3320868,3320325,3320136,3320673,3320988,3320136,3320673,3320136,3320673,3320144,3320673,3320144,3320144,3320144,3320144</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="0" t="n">
+        <v>725</v>
+      </c>
+      <c r="F136" s="0" t="inlineStr">
+        <is>
+          <t>L6 W11/20; N=23; EHP=3174.000000; normal:17x5,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,medium:83x1,swarm:84x6,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="0" t="n">
+        <v>112</v>
+      </c>
+      <c r="C137" s="0" t="inlineStr">
+        <is>
+          <t>3322136,3322673,3322242,3322091,3322668,3322253,3322136,3322673,3322786,3322107,3322868,3322325,3322136,3322673,3322988,3322136,3322673,3322144,3322673,3322144,3322673,3322144,3322144,3322144</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="0" t="n">
+        <v>710</v>
+      </c>
+      <c r="F137" s="0" t="inlineStr">
+        <is>
+          <t>L6 W12/20; N=24; EHP=3724.344000; air:11x1,air:13x1,normal:17x4,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,medium:83x1,swarm:84x6,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="0" t="n">
+        <v>113</v>
+      </c>
+      <c r="C138" s="0" t="inlineStr">
+        <is>
+          <t>3324136,3324673,3324242,3324091,3324668,3324325,3324136,3324673,3324786,3324107,3324868,3324709,3324136,3324673,3324786,3324115,3324988,3324144,3324673,3324144,3324673,3324144,3324673,3324144,3324673</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="0" t="n">
+        <v>695</v>
+      </c>
+      <c r="F138" s="0" t="inlineStr">
+        <is>
+          <t>L6 W13/20; N=25; EHP=4340.100000; air:11x1,air:13x1,air:14x1,normal:17x3,normal:18x4,fast:30x1,heavy:40x1,medium:83x1,swarm:84x7,heavy:88x1,fast:98x2,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="0" t="n">
+        <v>114</v>
+      </c>
+      <c r="C139" s="0" t="inlineStr">
+        <is>
+          <t>3326136,3326673,3326242,3326091,3326668,3326645,3326136,3326673,3326242,3326107,3326868,3326709,3326136,3326673,3326786,3326115,3326988,3326136,3326673,3326144,3326673,3326144,3326673,3326144,3326673,3326144</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="0" t="n">
+        <v>680</v>
+      </c>
+      <c r="F139" s="0" t="inlineStr">
+        <is>
+          <t>L6 W14/20; N=26; EHP=5024.994000; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x2,heavy:80x1,medium:83x1,swarm:84x7,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="0" t="n">
+        <v>115</v>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t>3328136,3328673,3328242,3328091,3328668,3328645,3328326,3328136,3328673,3328786,3328107,3328668,3328693,3328136,3328673,3328786,3328115,3328868,3328144,3328673,3328988,3328144,3328673,3328144,3328673,3328144,3328673</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="0" t="n">
+        <v>665</v>
+      </c>
+      <c r="F140" s="0" t="inlineStr">
+        <is>
+          <t>L6 W15/20; N=27; EHP=6476.682240; air:11x1,air:13x1,air:14x1,normal:17x3,normal:18x4,fast:30x1,elite:40x1,heavy:80x1,medium:83x2,swarm:84x7,heavy:86x1,fast:98x2,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="0" t="n">
+        <v>116</v>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t>3330136,3330673,3330242,3330668,3330253,3330136,3330673,3330242,3330868,3330693,3330136,3330673,3330786,3330988,3330136,3330673,3330988,3330136,3330673,3330136,3330673,3330144,3330673,3330144,3330144,3330144,3330144,3330144</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="0" t="n">
+        <v>650</v>
+      </c>
+      <c r="F141" s="0" t="inlineStr">
+        <is>
+          <t>L6 W16/20; N=28; EHP=6736.000000; normal:17x6,normal:18x6,fast:30x2,heavy:31x1,medium:83x1,swarm:84x7,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="0" t="n">
+        <v>117</v>
+      </c>
+      <c r="C142" s="0" t="inlineStr">
+        <is>
+          <t>3332136,3332673,3332242,3332091,3332668,3332253,3332136,3332673,3332786,3332107,3332868,3332325,3332136,3332673,3332786,3332115,3332868,3332136,3332673,3332988,3332144,3332673,3332144,3332673,3332144,3332673,3332144,3332673,3332144</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="0" t="n">
+        <v>635</v>
+      </c>
+      <c r="F142" s="0" t="inlineStr">
+        <is>
+          <t>L6 W17/20; N=29; EHP=7531.764000; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,medium:83x1,swarm:84x8,fast:98x2,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="0" t="n">
+        <v>118</v>
+      </c>
+      <c r="C143" s="0" t="inlineStr">
+        <is>
+          <t>3334136,3334673,3334242,3334091,3334668,3334325,3334136,3334673,3334242,3334107,3334668,3334645,3334136,3334673,3334786,3334115,3334868,3334709,3334136,3334673,3334988,3334144,3334673,3334144,3334673,3334144,3334673,3334144,3334673,3334144</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="0" t="n">
+        <v>620</v>
+      </c>
+      <c r="F143" s="0" t="inlineStr">
+        <is>
+          <t>L6 W18/20; N=30; EHP=8530.470000; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x5,fast:30x2,heavy:40x1,heavy:80x1,medium:83x2,swarm:84x8,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="0" t="n">
+        <v>119</v>
+      </c>
+      <c r="C144" s="0" t="inlineStr">
+        <is>
+          <t>3336136,3336673,3336242,3336091,3336668,3336645,3336136,3336673,3336786,3336107,3336868,3336693,3336136,3336673,3336786,3336115,3336988,3336709,3336136,3336673,3336988,3336136,3336673,3336144,3336673,3336144,3336673,3336144,3336673,3336144,3336144</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="0" t="n">
+        <v>605</v>
+      </c>
+      <c r="F144" s="0" t="inlineStr">
+        <is>
+          <t>L6 W19/20; N=31; EHP=9616.944000; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x5,fast:30x1,heavy:80x1,medium:83x1,swarm:84x8,heavy:86x1,heavy:88x1,fast:98x2,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="C145" s="0" t="inlineStr">
+        <is>
+          <t>3338136,3338673,3338242,3338091,3338668,3338253,3338990,3338136,3338673,3338242,3338107,3338868,3338645,3338136,3338673,3338786,3338115,3338868,3338693,3338136,3338673,3338988,3338136,3338673,3338144,3338673,3338144,3338673,3338144,3338673,3338144,3338144</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="0" t="n">
+        <v>590</v>
+      </c>
+      <c r="F145" s="0" t="inlineStr">
+        <is>
+          <t>L6 W20/20; N=32; EHP=13493.640000; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x5,fast:30x2,heavy:31x1,heavy:80x1,medium:83x1,swarm:84x8,heavy:86x1,fast:98x1,medium:108x2,elite:123x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="0" t="n">
+        <v>121</v>
+      </c>
+      <c r="C146" s="0" t="inlineStr">
+        <is>
+          <t>3340136,3340136,3340136,3340136,3340136,3340136,3340136,3340144,3340144,3340144,3340144,3340144,3340144,3340144</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="0" t="n">
+        <v>870</v>
+      </c>
+      <c r="F146" s="0" t="inlineStr">
+        <is>
+          <t>L7 W1/20; N=14; EHP=495.600000; normal:17x7,normal:18x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="0" t="n">
+        <v>122</v>
+      </c>
+      <c r="C147" s="0" t="inlineStr">
+        <is>
+          <t>3342136,3342136,3342136,3342136,3342136,3342136,3342136,3342136,3342144,3342144,3342144,3342144,3342144,3342144,3342144</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" s="0" t="n">
+        <v>855</v>
+      </c>
+      <c r="F147" s="0" t="inlineStr">
+        <is>
+          <t>L7 W2/20; N=15; EHP=604.278000; normal:17x8,normal:18x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="0" t="n">
+        <v>123</v>
+      </c>
+      <c r="C148" s="0" t="inlineStr">
+        <is>
+          <t>3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344673,3344136,3344136,3344144,3344144,3344144,3344144,3344144,3344144</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" s="0" t="n">
+        <v>840</v>
+      </c>
+      <c r="F148" s="0" t="inlineStr">
+        <is>
+          <t>L7 W3/20; N=16; EHP=743.116800; normal:17x6,normal:18x6,swarm:84x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="0" t="n">
+        <v>124</v>
+      </c>
+      <c r="C149" s="0" t="inlineStr">
+        <is>
+          <t>3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346673,3346136,3346136,3346136,3346144,3346144,3346144,3346144,3346144,3346144</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" s="0" t="n">
+        <v>825</v>
+      </c>
+      <c r="F149" s="0" t="inlineStr">
+        <is>
+          <t>L7 W4/20; N=17; EHP=915.939600; normal:17x7,normal:18x6,swarm:84x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="C150" s="0" t="inlineStr">
+        <is>
+          <t>3348136,3348673,3348668,3348136,3348673,3348988,3348136,3348673,3348136,3348673,3348136,3348673,3348136,3348144,3348144,3348144,3348144,3348144</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="0" t="n">
+        <v>810</v>
+      </c>
+      <c r="F150" s="0" t="inlineStr">
+        <is>
+          <t>L7 W5/20; N=18; EHP=1261.757952; normal:17x6,normal:18x5,medium:83x1,swarm:84x5,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="0" t="n">
+        <v>126</v>
+      </c>
+      <c r="C151" s="0" t="inlineStr">
+        <is>
+          <t>3350136,3350673,3350242,3350107,3350868,3350136,3350673,3350786,3350988,3350136,3350673,3350136,3350673,3350136,3350673,3350144,3350144,3350144,3350144</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" s="0" t="n">
+        <v>795</v>
+      </c>
+      <c r="F151" s="0" t="inlineStr">
+        <is>
+          <t>L7 W6/20; N=19; EHP=1378.830000; air:13x1,normal:17x5,normal:18x4,fast:30x1,swarm:84x5,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="0" t="n">
+        <v>127</v>
+      </c>
+      <c r="C152" s="0" t="inlineStr">
+        <is>
+          <t>3352136,3352673,3352242,3352091,3352668,3352136,3352673,3352786,3352868,3352136,3352673,3352988,3352136,3352673,3352136,3352673,3352144,3352144,3352144,3352144</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="0" t="n">
+        <v>780</v>
+      </c>
+      <c r="F152" s="0" t="inlineStr">
+        <is>
+          <t>L7 W7/20; N=20; EHP=1676.544000; air:11x1,normal:17x5,normal:18x4,fast:30x1,medium:83x1,swarm:84x5,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="0" t="n">
+        <v>128</v>
+      </c>
+      <c r="C153" s="0" t="inlineStr">
+        <is>
+          <t>3354136,3354673,3354242,3354115,3354668,3354136,3354673,3354786,3354868,3354136,3354673,3354988,3354136,3354673,3354136,3354673,3354144,3354144,3354144,3354144,3354144</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="0" t="n">
+        <v>765</v>
+      </c>
+      <c r="F153" s="0" t="inlineStr">
+        <is>
+          <t>L7 W8/20; N=21; EHP=2023.534800; air:14x1,normal:17x5,normal:18x5,fast:30x1,medium:83x1,swarm:84x5,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="0" t="n">
+        <v>129</v>
+      </c>
+      <c r="C154" s="0" t="inlineStr">
+        <is>
+          <t>3356136,3356673,3356242,3356107,3356668,3356136,3356673,3356786,3356868,3356136,3356673,3356988,3356136,3356673,3356136,3356673,3356144,3356673,3356144,3356144,3356144,3356144</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" s="0" t="n">
+        <v>750</v>
+      </c>
+      <c r="F154" s="0" t="inlineStr">
+        <is>
+          <t>L7 W9/20; N=22; EHP=2423.625600; air:13x1,normal:17x5,normal:18x5,fast:30x1,medium:83x1,swarm:84x6,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" s="0" t="n">
+        <v>130</v>
+      </c>
+      <c r="C155" s="0" t="inlineStr">
+        <is>
+          <t>3358136,3358673,3358242,3358091,3358668,3358136,3358673,3358786,3358868,3358136,3358673,3358988,3358136,3358673,3358136,3358673,3358136,3358673,3358144,3358144,3358144,3358144,3358144</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" s="0" t="n">
+        <v>735</v>
+      </c>
+      <c r="F155" s="0" t="inlineStr">
+        <is>
+          <t>L7 W10/20; N=23; EHP=3226.316352; air:11x1,normal:17x6,normal:18x5,fast:30x1,medium:83x1,swarm:84x6,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="0" t="n">
+        <v>131</v>
+      </c>
+      <c r="C156" s="0" t="inlineStr">
+        <is>
+          <t>3360136,3360673,3360466,3360668,3360253,3360136,3360673,3360786,3360868,3360325,3360136,3360673,3360988,3360136,3360673,3360136,3360673,3360136,3360673,3360144,3360144,3360144,3360144,3360144</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" s="0" t="n">
+        <v>720</v>
+      </c>
+      <c r="F156" s="0" t="inlineStr">
+        <is>
+          <t>L7 W11/20; N=24; EHP=3398.400000; normal:17x6,normal:18x5,heavy:31x1,heavy:40x1,fast:58x1,medium:83x1,swarm:84x6,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="0" t="n">
+        <v>132</v>
+      </c>
+      <c r="C157" s="0" t="inlineStr">
+        <is>
+          <t>3362136,3362673,3362242,3362091,3362668,3362325,3362136,3362673,3362466,3362107,3362868,3362709,3362136,3362673,3362786,3362115,3362988,3362136,3362673,3362144,3362673,3362144,3362673,3362144,3362673</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" s="0" t="n">
+        <v>705</v>
+      </c>
+      <c r="F157" s="0" t="inlineStr">
+        <is>
+          <t>L7 W12/20; N=25; EHP=3980.730000; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x3,fast:30x1,heavy:40x1,fast:58x1,medium:83x1,swarm:84x7,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="0" t="n">
+        <v>133</v>
+      </c>
+      <c r="C158" s="0" t="inlineStr">
+        <is>
+          <t>3364136,3364673,3364242,3364091,3364668,3364645,3364136,3364673,3364466,3364107,3364868,3364709,3364136,3364673,3364786,3364115,3364988,3364136,3364673,3364144,3364673,3364144,3364673,3364144,3364673,3364144</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" s="0" t="n">
+        <v>690</v>
+      </c>
+      <c r="F158" s="0" t="inlineStr">
+        <is>
+          <t>L7 W13/20; N=26; EHP=4631.452800; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x1,fast:58x1,heavy:80x1,medium:83x1,swarm:84x7,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="0" t="n">
+        <v>134</v>
+      </c>
+      <c r="C159" s="0" t="inlineStr">
+        <is>
+          <t>3366136,3366673,3366242,3366091,3366668,3366645,3366136,3366673,3366466,3366107,3366668,3366693,3366136,3366673,3366786,3366115,3366868,3366136,3366673,3366988,3366144,3366673,3366144,3366673,3366144,3366673,3366144</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" s="0" t="n">
+        <v>675</v>
+      </c>
+      <c r="F159" s="0" t="inlineStr">
+        <is>
+          <t>L7 W14/20; N=27; EHP=5354.391600; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x1,fast:58x1,heavy:80x1,medium:83x2,swarm:84x7,heavy:86x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="0" t="n">
+        <v>135</v>
+      </c>
+      <c r="C160" s="0" t="inlineStr">
+        <is>
+          <t>3368136,3368673,3368242,3368091,3368668,3368253,3368326,3368136,3368673,3368466,3368107,3368868,3368693,3368136,3368673,3368786,3368115,3368988,3368136,3368673,3368988,3368144,3368673,3368144,3368673,3368144,3368673,3368144</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" s="0" t="n">
+        <v>660</v>
+      </c>
+      <c r="F160" s="0" t="inlineStr">
+        <is>
+          <t>L7 W15/20; N=28; EHP=6891.773952; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x1,heavy:31x1,elite:40x1,fast:58x1,medium:83x1,swarm:84x7,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="0" t="n">
+        <v>136</v>
+      </c>
+      <c r="C161" s="0" t="inlineStr">
+        <is>
+          <t>3370136,3370673,3370242,3370668,3370253,3370136,3370673,3370466,3370868,3370325,3370136,3370673,3370786,3370868,3370136,3370673,3370988,3370136,3370673,3370136,3370673,3370144,3370673,3370144,3370673,3370144,3370144,3370144,3370144</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="0" t="n">
+        <v>645</v>
+      </c>
+      <c r="F161" s="0" t="inlineStr">
+        <is>
+          <t>L7 W16/20; N=29; EHP=7168.000000; normal:17x6,normal:18x6,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,medium:83x1,swarm:84x8,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="0" t="n">
+        <v>137</v>
+      </c>
+      <c r="C162" s="0" t="inlineStr">
+        <is>
+          <t>3372136,3372673,3372242,3372091,3372668,3372325,3372136,3372673,3372466,3372107,3372668,3372645,3372136,3372673,3372786,3372115,3372868,3372709,3372136,3372673,3372988,3372136,3372673,3372144,3372673,3372144,3372673,3372144,3372673,3372144</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" s="0" t="n">
+        <v>630</v>
+      </c>
+      <c r="F162" s="0" t="inlineStr">
+        <is>
+          <t>L7 W17/20; N=30; EHP=7994.736000; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x4,fast:30x1,heavy:40x1,fast:58x1,heavy:80x1,medium:83x2,swarm:84x8,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="0" t="n">
+        <v>138</v>
+      </c>
+      <c r="C163" s="0" t="inlineStr">
+        <is>
+          <t>3374136,3374673,3374242,3374091,3374668,3374645,3374136,3374673,3374466,3374107,3374868,3374693,3374136,3374673,3374786,3374115,3374988,3374709,3374136,3374673,3374988,3374136,3374673,3374144,3374673,3374144,3374673,3374144,3374673,3374144,3374144</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="0" t="n">
+        <v>615</v>
+      </c>
+      <c r="F163" s="0" t="inlineStr">
+        <is>
+          <t>L7 W18/20; N=31; EHP=9044.770800; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x5,fast:30x1,fast:58x1,heavy:80x1,medium:83x1,swarm:84x8,heavy:86x1,heavy:88x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" s="0" t="n">
+        <v>139</v>
+      </c>
+      <c r="C164" s="0" t="inlineStr">
+        <is>
+          <t>3376136,3376673,3376242,3376091,3376668,3376253,3376136,3376673,3376466,3376107,3376868,3376645,3376136,3376673,3376786,3376115,3376868,3376693,3376136,3376673,3376988,3376136,3376673,3376136,3376673,3376144,3376673,3376144,3376673,3376144,3376144,3376144</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="F164" s="0" t="inlineStr">
+        <is>
+          <t>L7 W19/20; N=32; EHP=10186.137600; air:11x1,air:13x1,air:14x1,normal:17x6,normal:18x5,fast:30x1,heavy:31x1,fast:58x1,heavy:80x1,medium:83x1,swarm:84x8,heavy:86x1,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="C165" s="0" t="inlineStr">
+        <is>
+          <t>3378136,3378673,3378242,3378091,3378668,3378253,3378990,3378136,3378673,3378466,3378107,3378668,3378325,3378136,3378673,3378786,3378115,3378868,3378693,3378136,3378673,3378988,3378136,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144,3378673,3378144</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="0" t="n">
+        <v>585</v>
+      </c>
+      <c r="F165" s="0" t="inlineStr">
+        <is>
+          <t>L7 W20/20; N=33; EHP=14278.324500; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,medium:83x2,swarm:84x9,heavy:86x1,fast:98x1,medium:108x1,elite:123x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" s="0" t="n">
+        <v>141</v>
+      </c>
+      <c r="C166" s="0" t="inlineStr">
+        <is>
+          <t>3380136,3380136,3380136,3380136,3380136,3380136,3380136,3380144,3380144,3380144,3380144,3380144,3380144,3380144,3380144</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" s="0" t="n">
+        <v>865</v>
+      </c>
+      <c r="F166" s="0" t="inlineStr">
+        <is>
+          <t>L8 W1/20; N=15; EHP=544.500000; normal:17x7,normal:18x8</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" s="0" t="n">
+        <v>142</v>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t>3382136,3382136,3382136,3382136,3382136,3382136,3382136,3382136,3382144,3382144,3382144,3382144,3382144,3382144,3382144,3382144</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="0" t="n">
+        <v>850</v>
+      </c>
+      <c r="F167" s="0" t="inlineStr">
+        <is>
+          <t>L8 W2/20; N=16; EHP=660.950400; normal:17x8,normal:18x8</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" s="0" t="n">
+        <v>143</v>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t>3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384136,3384144,3384144,3384144,3384144,3384144,3384144,3384144</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" s="0" t="n">
+        <v>835</v>
+      </c>
+      <c r="F168" s="0" t="inlineStr">
+        <is>
+          <t>L8 W3/20; N=17; EHP=809.635200; normal:17x6,normal:18x7,swarm:84x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" s="0" t="n">
+        <v>144</v>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386144,3386144,3386144,3386144,3386144,3386144,3386144</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" s="0" t="n">
+        <v>820</v>
+      </c>
+      <c r="F169" s="0" t="inlineStr">
+        <is>
+          <t>L8 W4/20; N=18; EHP=994.474800; normal:17x6,normal:18x7,swarm:84x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" s="0" t="n">
+        <v>145</v>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>3388136,3388673,3388868,3388136,3388673,3388988,3388136,3388673,3388136,3388673,3388136,3388673,3388136,3388144,3388144,3388144,3388144,3388144,3388144</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" s="0" t="n">
+        <v>805</v>
+      </c>
+      <c r="F170" s="0" t="inlineStr">
+        <is>
+          <t>L8 W5/20; N=19; EHP=1365.716352; normal:17x6,normal:18x6,swarm:84x5,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="0" t="n">
+        <v>146</v>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t>3390136,3390673,3390242,3390107,3390668,3390136,3390673,3390466,3390868,3390136,3390673,3390988,3390136,3390673,3390144,3390673,3390144,3390144,3390144,3390144</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" s="0" t="n">
+        <v>790</v>
+      </c>
+      <c r="F171" s="0" t="inlineStr">
+        <is>
+          <t>L8 W6/20; N=20; EHP=1488.300000; air:13x1,normal:17x4,normal:18x5,fast:30x1,fast:58x1,medium:83x1,swarm:84x5,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="0" t="n">
+        <v>147</v>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t>3392136,3392673,3392242,3392091,3392668,3392136,3392673,3392786,3392868,3392136,3392673,3392988,3392136,3392673,3392136,3392673,3392144,3392144,3392144,3392144,3392144</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" s="0" t="n">
+        <v>775</v>
+      </c>
+      <c r="F172" s="0" t="inlineStr">
+        <is>
+          <t>L8 W7/20; N=21; EHP=1805.126400; air:11x1,normal:17x5,normal:18x5,fast:30x1,medium:83x1,swarm:84x5,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="0" t="n">
+        <v>148</v>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t>3394136,3394673,3394466,3394115,3394668,3394136,3394673,3394786,3394868,3394136,3394673,3394988,3394136,3394673,3394136,3394673,3394144,3394673,3394144,3394144,3394144,3394144</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" s="0" t="n">
+        <v>760</v>
+      </c>
+      <c r="F173" s="0" t="inlineStr">
+        <is>
+          <t>L8 W8/20; N=22; EHP=2173.789200; air:14x1,normal:17x5,normal:18x5,fast:58x1,medium:83x1,swarm:84x6,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" s="0" t="n">
+        <v>149</v>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t>3396136,3396673,3396242,3396107,3396668,3396136,3396673,3396466,3396868,3396136,3396673,3396988,3396136,3396673,3396136,3396673,3396144,3396673,3396144,3396144,3396144,3396144,3396144</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" s="0" t="n">
+        <v>745</v>
+      </c>
+      <c r="F174" s="0" t="inlineStr">
+        <is>
+          <t>L8 W9/20; N=23; EHP=2598.208800; air:13x1,normal:17x5,normal:18x6,fast:30x1,fast:58x1,medium:83x1,swarm:84x6,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t>3398136,3398673,3398242,3398091,3398668,3398136,3398673,3398786,3398868,3398136,3398673,3398988,3398136,3398673,3398136,3398673,3398136,3398673,3398144,3398144,3398144,3398144,3398144,3398144</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" s="0" t="n">
+        <v>730</v>
+      </c>
+      <c r="F175" s="0" t="inlineStr">
+        <is>
+          <t>L8 W10/20; N=24; EHP=3452.182272; air:11x1,normal:17x6,normal:18x6,fast:30x1,medium:83x1,swarm:84x6,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" s="0" t="n">
+        <v>151</v>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t>3400136,3400673,3400242,3400668,3400693,3400136,3400673,3400466,3400868,3401021,3400136,3400673,3400786,3400988,3400136,3400673,3400136,3400673,3400144,3400673,3400144,3400673,3400144,3400144,3400144</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" s="0" t="n">
+        <v>715</v>
+      </c>
+      <c r="F176" s="0" t="inlineStr">
+        <is>
+          <t>L8 W11/20; N=25; EHP=3630.000000; normal:17x5,normal:18x5,fast:30x1,fast:58x1,medium:83x1,swarm:84x7,heavy:86x1,fast:98x1,medium:108x1,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" s="0" t="n">
+        <v>152</v>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t>3402136,3402673,3402242,3402091,3402668,3402253,3402136,3402673,3402466,3402107,3402868,3402693,3402136,3402673,3402786,3402115,3402988,3402136,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" s="0" t="n">
+        <v>700</v>
+      </c>
+      <c r="F177" s="0" t="inlineStr">
+        <is>
+          <t>L8 W12/20; N=26; EHP=4245.212400; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x1,heavy:31x1,fast:58x1,medium:83x1,swarm:84x7,heavy:86x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="0" t="n">
+        <v>153</v>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t>3404136,3404673,3404242,3404091,3404668,3404253,3404136,3404673,3404466,3404107,3404668,3404325,3404136,3404673,3404786,3404115,3404868,3404136,3404673,3404988,3404144,3404673,3404144,3404673,3404144,3404673,3404144</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" s="0" t="n">
+        <v>685</v>
+      </c>
+      <c r="F178" s="0" t="inlineStr">
+        <is>
+          <t>L8 W13/20; N=27; EHP=4931.863200; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,medium:83x2,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" s="0" t="n">
+        <v>154</v>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t>3406136,3406673,3406242,3406091,3406668,3406325,3406136,3406673,3406466,3406107,3406868,3407021,3406136,3406673,3406786,3406115,3406988,3406136,3406673,3406988,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406144</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" s="0" t="n">
+        <v>670</v>
+      </c>
+      <c r="F179" s="0" t="inlineStr">
+        <is>
+          <t>L8 W14/20; N=28; EHP=5693.872800; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x5,fast:30x1,heavy:40x1,fast:58x1,medium:83x1,swarm:84x7,fast:98x1,medium:108x1,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="0" t="n">
+        <v>155</v>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t>3408136,3408673,3408242,3408091,3408668,3408709,3409022,3408136,3408673,3408466,3408107,3408868,3409021,3408136,3408673,3408786,3408115,3408868,3408136,3408673,3408988,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" s="0" t="n">
+        <v>655</v>
+      </c>
+      <c r="F180" s="0" t="inlineStr">
+        <is>
+          <t>L8 W15/20; N=29; EHP=7319.380992; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x1,fast:58x1,medium:83x1,swarm:84x8,heavy:88x1,fast:98x1,medium:108x2,medium:123x1,elite:127x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" s="0" t="n">
+        <v>156</v>
+      </c>
+      <c r="C181" s="0" t="inlineStr">
+        <is>
+          <t>3410136,3410673,3410242,3410668,3410645,3410136,3410673,3410466,3410668,3410693,3410136,3410673,3410786,3410868,3410709,3410136,3410673,3410988,3410136,3410673,3410136,3410673,3410144,3410673,3410144,3410673,3410144,3410144,3410144,3410144</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" s="0" t="n">
+        <v>640</v>
+      </c>
+      <c r="F181" s="0" t="inlineStr">
+        <is>
+          <t>L8 W16/20; N=30; EHP=7613.000000; normal:17x6,normal:18x6,fast:30x1,fast:58x1,heavy:80x1,medium:83x2,swarm:84x8,heavy:86x1,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" s="0" t="n">
+        <v>157</v>
+      </c>
+      <c r="C182" s="0" t="inlineStr">
+        <is>
+          <t>3412136,3412673,3412242,3412091,3412668,3412253,3412136,3412673,3412466,3412107,3412868,3412645,3412136,3412673,3412786,3412115,3412988,3412693,3412136,3412673,3412988,3412136,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412144</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" s="0" t="n">
+        <v>625</v>
+      </c>
+      <c r="F182" s="0" t="inlineStr">
+        <is>
+          <t>L8 W17/20; N=31; EHP=8471.258400; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x5,fast:30x1,heavy:31x1,fast:58x1,heavy:80x1,medium:83x1,swarm:84x8,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" s="0" t="n">
+        <v>158</v>
+      </c>
+      <c r="C183" s="0" t="inlineStr">
+        <is>
+          <t>3414136,3414673,3414242,3414091,3414668,3414253,3414136,3414673,3414466,3414107,3414868,3414325,3414136,3414673,3414786,3414115,3414868,3414693,3414136,3414673,3414988,3414136,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414144,3414144</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" s="0" t="n">
+        <v>610</v>
+      </c>
+      <c r="F183" s="0" t="inlineStr">
+        <is>
+          <t>L8 W18/20; N=32; EHP=9573.907200; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x6,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,medium:83x1,swarm:84x8,heavy:86x1,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" s="0" t="n">
+        <v>159</v>
+      </c>
+      <c r="C184" s="0" t="inlineStr">
+        <is>
+          <t>3416136,3416673,3416242,3416091,3416668,3416253,3416136,3416673,3416466,3416107,3416668,3416325,3416136,3416673,3416786,3416115,3416868,3417021,3416136,3416673,3416988,3416136,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416144</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" s="0" t="n">
+        <v>595</v>
+      </c>
+      <c r="F184" s="0" t="inlineStr">
+        <is>
+          <t>L8 W19/20; N=33; EHP=10771.516800; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x6,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x1,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="C185" s="0" t="inlineStr">
+        <is>
+          <t>3418136,3418673,3418242,3418091,3418668,3418325,3418990,3418136,3418673,3418466,3418107,3418868,3418709,3418136,3418673,3418786,3418115,3418868,3419021,3418136,3418673,3418786,3418115,3418988,3418144,3418673,3418988,3418144,3418673,3418144,3418673,3418144,3418673,3418673</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" s="0" t="n">
+        <v>580</v>
+      </c>
+      <c r="F185" s="0" t="inlineStr">
+        <is>
+          <t>L8 W20/20; N=34; EHP=15085.009500; air:11x1,air:13x1,air:14x2,normal:17x4,normal:18x4,fast:30x1,heavy:40x1,fast:58x1,medium:83x1,swarm:84x9,heavy:88x1,fast:98x2,medium:108x2,elite:123x1,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" s="0" t="n">
+        <v>161</v>
+      </c>
+      <c r="C186" s="0" t="inlineStr">
+        <is>
+          <t>3420136,3420136,3420136,3420136,3420136,3420136,3420136,3420136,3420144,3420144,3420144,3420144,3420144,3420144,3420144,3420144</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" s="0" t="n">
+        <v>860</v>
+      </c>
+      <c r="F186" s="0" t="inlineStr">
+        <is>
+          <t>L9 W1/20; N=16; EHP=595.200000; normal:17x8,normal:18x8</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" s="0" t="n">
+        <v>162</v>
+      </c>
+      <c r="C187" s="0" t="inlineStr">
+        <is>
+          <t>3422136,3422136,3422136,3422136,3422136,3422136,3422136,3422136,3422136,3422144,3422144,3422144,3422144,3422144,3422144,3422144,3422144</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" s="0" t="n">
+        <v>845</v>
+      </c>
+      <c r="F187" s="0" t="inlineStr">
+        <is>
+          <t>L9 W2/20; N=17; EHP=719.671200; normal:17x9,normal:18x8</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" s="0" t="n">
+        <v>163</v>
+      </c>
+      <c r="C188" s="0" t="inlineStr">
+        <is>
+          <t>3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424136,3424144,3424144,3424144,3424144,3424144,3424144</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" s="0" t="n">
+        <v>830</v>
+      </c>
+      <c r="F188" s="0" t="inlineStr">
+        <is>
+          <t>L9 W3/20; N=18; EHP=878.515200; normal:17x7,normal:18x6,swarm:84x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" s="0" t="n">
+        <v>164</v>
+      </c>
+      <c r="C189" s="0" t="inlineStr">
+        <is>
+          <t>3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426136,3426144,3426144,3426144,3426144,3426144,3426144,3426144</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" s="0" t="n">
+        <v>815</v>
+      </c>
+      <c r="F189" s="0" t="inlineStr">
+        <is>
+          <t>L9 W4/20; N=19; EHP=1075.749600; normal:17x7,normal:18x7,swarm:84x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="0" t="n">
+        <v>165</v>
+      </c>
+      <c r="C190" s="0" t="inlineStr">
+        <is>
+          <t>3428136,3428673,3428668,3428136,3428673,3428868,3428136,3428673,3428988,3428136,3428673,3428136,3428673,3428136,3428144,3428144,3428144,3428144,3428144,3428144</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="F190" s="0" t="inlineStr">
+        <is>
+          <t>L9 W5/20; N=20; EHP=1473.239040; normal:17x6,normal:18x6,medium:83x1,swarm:84x5,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" s="0" t="n">
+        <v>166</v>
+      </c>
+      <c r="C191" s="0" t="inlineStr">
+        <is>
+          <t>3430136,3430673,3430242,3430107,3430668,3430136,3430673,3430786,3430868,3430136,3430673,3430988,3430136,3430673,3430136,3430673,3430144,3430144,3430144,3430144,3430144</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" s="0" t="n">
+        <v>785</v>
+      </c>
+      <c r="F191" s="0" t="inlineStr">
+        <is>
+          <t>L9 W6/20; N=21; EHP=1601.460000; air:13x1,normal:17x5,normal:18x5,fast:30x1,medium:83x1,swarm:84x5,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" s="0" t="n">
+        <v>167</v>
+      </c>
+      <c r="C192" s="0" t="inlineStr">
+        <is>
+          <t>3432136,3432673,3432466,3432091,3432668,3432136,3432673,3432786,3432868,3432136,3432673,3432988,3432136,3432673,3432136,3432673,3432144,3432673,3432144,3432144,3432144,3432144</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" s="0" t="n">
+        <v>770</v>
+      </c>
+      <c r="F192" s="0" t="inlineStr">
+        <is>
+          <t>L9 W7/20; N=22; EHP=1937.971200; air:11x1,normal:17x5,normal:18x5,fast:58x1,medium:83x1,swarm:84x6,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" s="0" t="n">
+        <v>168</v>
+      </c>
+      <c r="C193" s="0" t="inlineStr">
+        <is>
+          <t>3434136,3434673,3434242,3434115,3434668,3434136,3434673,3434466,3434868,3434136,3434673,3434988,3434136,3434673,3434136,3434673,3434136,3434673,3434144,3434144,3434144,3434144,3434144</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" s="0" t="n">
+        <v>755</v>
+      </c>
+      <c r="F193" s="0" t="inlineStr">
+        <is>
+          <t>L9 W8/20; N=23; EHP=2328.943200; air:14x1,normal:17x6,normal:18x5,fast:30x1,fast:58x1,medium:83x1,swarm:84x6,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" s="0" t="n">
+        <v>169</v>
+      </c>
+      <c r="C194" s="0" t="inlineStr">
+        <is>
+          <t>3436136,3436673,3436242,3436107,3436668,3436136,3436673,3436786,3436868,3436136,3436673,3436988,3436136,3436673,3436136,3436673,3436136,3436673,3436144,3436144,3436144,3436144,3436144,3436144</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" s="0" t="n">
+        <v>740</v>
+      </c>
+      <c r="F194" s="0" t="inlineStr">
+        <is>
+          <t>L9 W9/20; N=24; EHP=2778.393600; air:13x1,normal:17x6,normal:18x6,fast:30x1,medium:83x1,swarm:84x6,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" s="0" t="n">
         <v>170</v>
       </c>
-      <c r="F100" s="0" t="inlineStr">
-        <is>
-          <t>第 75 波：33 只 / 目标血量 78878（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" t="n">
-        <v>76</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,132</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E101" t="n">
-        <v>170</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>第 76 波：33 只 / 目标血量 79509（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" t="n">
-        <v>77</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E102" t="n">
-        <v>170</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>第 77 波：33 只 / 目标血量 80145（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" t="n">
-        <v>78</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,132</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E103" t="n">
-        <v>170</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>第 78 波：34 只 / 目标血量 80786（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" t="n">
-        <v>79</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E104" t="n">
-        <v>170</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>第 79 波：33 只 / 目标血量 81432（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" t="n">
-        <v>80</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,132,130</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E105" t="n">
-        <v>170</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>第 80 波：36 只 / 目标血量 82084（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" t="n">
-        <v>81</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E106" t="n">
-        <v>170</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>第 81 波：34 只 / 目标血量 82740（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" t="n">
-        <v>82</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,132</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E107" t="n">
-        <v>170</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>第 82 波：34 只 / 目标血量 83402（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" t="n">
-        <v>83</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E108" t="n">
-        <v>170</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>第 83 波：34 只 / 目标血量 84070（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="B109" t="n">
-        <v>84</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,132</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E109" t="n">
-        <v>170</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>第 84 波：35 只 / 目标血量 84742（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="B110" t="n">
-        <v>85</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,131</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E110" t="n">
-        <v>170</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>第 85 波：35 只 / 目标血量 85420（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="B111" t="n">
-        <v>86</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,132</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E111" t="n">
-        <v>170</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>第 86 波：37 只 / 目标血量 86103（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" t="n">
-        <v>87</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E112" t="n">
-        <v>170</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>第 87 波：36 只 / 目标血量 86792（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="B113" t="n">
-        <v>88</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,132</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E113" t="n">
-        <v>170</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>第 88 波：37 只 / 目标血量 87487（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="B114" t="n">
-        <v>89</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E114" t="n">
-        <v>170</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>第 89 波：36 只 / 目标血量 88187（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" t="n">
-        <v>90</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,132,129</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E115" t="n">
-        <v>170</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>第 90 波：37 只 / 目标血量 88892（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="B116" t="n">
-        <v>91</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E116" t="n">
-        <v>170</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>第 91 波：35 只 / 目标血量 89603（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" t="n">
-        <v>92</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,132</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E117" t="n">
-        <v>170</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>第 92 波：38 只 / 目标血量 90320（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" t="n">
-        <v>93</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E118" t="n">
-        <v>170</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>第 93 波：36 只 / 目标血量 91043（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" t="n">
-        <v>94</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,132</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E119" t="n">
-        <v>170</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>第 94 波：38 只 / 目标血量 91771（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" t="n">
-        <v>95</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,130</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E120" t="n">
-        <v>170</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>第 95 波：38 只 / 目标血量 92505（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="B121" t="n">
-        <v>96</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,132</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E121" t="n">
-        <v>170</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>第 96 波：40 只 / 目标血量 93245（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="B122" t="n">
-        <v>97</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E122" t="n">
-        <v>170</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>第 97 波：38 只 / 目标血量 93991（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" t="n">
-        <v>98</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,132</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E123" t="n">
-        <v>170</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>第 98 波：41 只 / 目标血量 94743（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" t="n">
-        <v>99</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>34,76,66,74,40,36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E124" t="n">
-        <v>170</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>第 99 波：39 只 / 目标血量 95501（单怪间隔 0.17s）</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" t="n">
-        <v>100</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>36,31,69,110,3,33,71,72,10,6,35,67,61,63,39,9,68,41,75,32,70,65,58,38,37,73,47,34,76,66,74,40,36,31,69,110,3,33,71,72,132,131</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E125" t="n">
-        <v>170</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>第 100 波：42 只 / 目标血量 96265（单怪间隔 0.17s）</t>
+      <c r="C195" s="0" t="inlineStr">
+        <is>
+          <t>3438136,3438673,3438242,3438091,3438668,3438136,3438673,3438466,3438115,3438868,3438136,3438673,3438786,3438988,3438136,3438673,3438136,3438673,3438144,3438673,3438144,3438673,3438144,3438144,3438144</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" s="0" t="n">
+        <v>725</v>
+      </c>
+      <c r="F195" s="0" t="inlineStr">
+        <is>
+          <t>L9 W10/20; N=25; EHP=3685.180800; air:11x1,air:14x1,normal:17x5,normal:18x5,fast:30x1,fast:58x1,medium:83x1,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" s="0" t="n">
+        <v>171</v>
+      </c>
+      <c r="C196" s="0" t="inlineStr">
+        <is>
+          <t>3440136,3440673,3440466,3440668,3440253,3440136,3440673,3440514,3440868,3440693,3440136,3440673,3440786,3440988,3440136,3440673,3440136,3440673,3440136,3440673,3440144,3440673,3440144,3440144,3440144,3440144</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" s="0" t="n">
+        <v>710</v>
+      </c>
+      <c r="F196" s="0" t="inlineStr">
+        <is>
+          <t>L9 W11/20; N=26; EHP=3868.800000; normal:17x6,normal:18x5,heavy:31x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x7,heavy:86x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" s="0" t="n">
+        <v>172</v>
+      </c>
+      <c r="C197" s="0" t="inlineStr">
+        <is>
+          <t>3442136,3442673,3442466,3442091,3442668,3442253,3442136,3442673,3442514,3442107,3442668,3442325,3442136,3442673,3442786,3442115,3442868,3442136,3442673,3442988,3442144,3442673,3442144,3442673,3442144,3442673,3442144</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" s="0" t="n">
+        <v>695</v>
+      </c>
+      <c r="F197" s="0" t="inlineStr">
+        <is>
+          <t>L9 W12/20; N=27; EHP=4517.791200; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x2,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" s="0" t="n">
+        <v>173</v>
+      </c>
+      <c r="C198" s="0" t="inlineStr">
+        <is>
+          <t>3444136,3444673,3444242,3444091,3444668,3444325,3444136,3444673,3444466,3444107,3444868,3445021,3444136,3444673,3444514,3444115,3444988,3444136,3444673,3444988,3444136,3444673,3444144,3444673,3444144,3444673,3444144,3444144</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" s="0" t="n">
+        <v>680</v>
+      </c>
+      <c r="F198" s="0" t="inlineStr">
+        <is>
+          <t>L9 W13/20; N=28; EHP=5241.331200; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x4,fast:30x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x7,medium:108x1,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" s="0" t="n">
+        <v>174</v>
+      </c>
+      <c r="C199" s="0" t="inlineStr">
+        <is>
+          <t>3446136,3446673,3446242,3446091,3446668,3446709,3446136,3446673,3446514,3446107,3446868,3447021,3446136,3446673,3446786,3446115,3446868,3446136,3446673,3446988,3446136,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" s="0" t="n">
+        <v>665</v>
+      </c>
+      <c r="F199" s="0" t="inlineStr">
+        <is>
+          <t>L9 W14/20; N=29; EHP=6043.437600; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x4,fast:30x1,fast:64x1,medium:83x1,swarm:84x8,heavy:88x1,fast:98x1,medium:108x2,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="C200" s="0" t="inlineStr">
+        <is>
+          <t>3448136,3448673,3448242,3448091,3448668,3448645,3449022,3448136,3448673,3448466,3448107,3448668,3448693,3448136,3448673,3448786,3448115,3448868,3448709,3448136,3448673,3448988,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" s="0" t="n">
+        <v>650</v>
+      </c>
+      <c r="F200" s="0" t="inlineStr">
+        <is>
+          <t>L9 W15/20; N=30; EHP=7759.503360; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x4,fast:30x1,fast:58x1,heavy:80x1,medium:83x2,swarm:84x8,heavy:86x1,heavy:88x1,fast:98x1,medium:108x1,medium:123x1,elite:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" s="0" t="n">
+        <v>176</v>
+      </c>
+      <c r="C201" s="0" t="inlineStr">
+        <is>
+          <t>3450136,3450673,3450466,3450668,3450253,3450136,3450673,3450514,3450868,3450645,3450136,3450673,3450786,3450988,3450693,3450136,3450673,3450988,3450136,3450673,3450136,3450673,3450136,3450673,3450144,3450673,3450144,3450144,3450144,3450144,3450144</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" s="0" t="n">
+        <v>635</v>
+      </c>
+      <c r="F201" s="0" t="inlineStr">
+        <is>
+          <t>L9 W16/20; N=31; EHP=8070.000000; normal:17x7,normal:18x6,heavy:31x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x1,swarm:84x8,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" s="0" t="n">
+        <v>177</v>
+      </c>
+      <c r="C202" s="0" t="inlineStr">
+        <is>
+          <t>3452136,3452673,3452242,3452091,3452668,3452253,3452136,3452673,3452466,3452107,3452868,3452325,3452136,3452673,3452514,3452115,3452868,3452693,3452136,3452673,3452988,3452136,3452673,3452136,3452673,3452144,3452673,3452144,3452673,3452144,3452144,3452144</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" s="0" t="n">
+        <v>620</v>
+      </c>
+      <c r="F202" s="0" t="inlineStr">
+        <is>
+          <t>L9 W17/20; N=32; EHP=8961.331200; air:11x1,air:13x1,air:14x1,normal:17x6,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,heavy:86x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" s="0" t="n">
+        <v>178</v>
+      </c>
+      <c r="C203" s="0" t="inlineStr">
+        <is>
+          <t>3454136,3454673,3454242,3454091,3454668,3454253,3454136,3454673,3454514,3454107,3454668,3454325,3454136,3454673,3454786,3454115,3454868,3455021,3454136,3454673,3454988,3454136,3454673,3454136,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454144</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" s="0" t="n">
+        <v>605</v>
+      </c>
+      <c r="F203" s="0" t="inlineStr">
+        <is>
+          <t>L9 W18/20; N=33; EHP=10117.879200; air:11x1,air:13x1,air:14x1,normal:17x6,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:64x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x1,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" s="0" t="n">
+        <v>179</v>
+      </c>
+      <c r="C204" s="0" t="inlineStr">
+        <is>
+          <t>3456136,3456673,3456242,3456091,3456668,3456325,3456136,3456673,3456466,3456091,3456868,3456709,3456136,3456673,3456514,3456107,3456868,3457021,3456136,3456673,3456786,3456115,3456988,3456136,3456673,3456988,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" s="0" t="n">
+        <v>590</v>
+      </c>
+      <c r="F204" s="0" t="inlineStr">
+        <is>
+          <t>L9 W19/20; N=34; EHP=11373.081600; air:11x2,air:13x1,air:14x1,normal:17x5,normal:18x4,fast:30x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x9,heavy:88x1,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="C205" s="0" t="inlineStr">
+        <is>
+          <t>3458136,3458673,3458242,3458091,3458668,3458645,3458990,3458136,3458673,3458466,3458107,3458668,3458709,3458136,3458673,3458514,3458115,3458868,3459021,3458136,3458673,3458786,3458115,3458868,3458136,3458673,3458988,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" s="0" t="n">
+        <v>575</v>
+      </c>
+      <c r="F205" s="0" t="inlineStr">
+        <is>
+          <t>L9 W20/20; N=35; EHP=15913.695000; air:11x1,air:13x1,air:14x2,normal:17x5,normal:18x4,fast:30x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x9,heavy:88x1,fast:98x1,medium:108x2,elite:123x1,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" s="0" t="n">
+        <v>181</v>
+      </c>
+      <c r="C206" s="0" t="inlineStr">
+        <is>
+          <t>3460136,3460136,3460136,3460136,3460136,3460136,3460136,3460136,3460144,3460144,3460144,3460144,3460144,3460144,3460144,3460144,3460144</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" s="0" t="n">
+        <v>855</v>
+      </c>
+      <c r="F206" s="0" t="inlineStr">
+        <is>
+          <t>L10 W1/20; N=17; EHP=647.700000; normal:17x8,normal:18x9</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" s="0" t="n">
+        <v>182</v>
+      </c>
+      <c r="C207" s="0" t="inlineStr">
+        <is>
+          <t>3462136,3462136,3462136,3462136,3462136,3462136,3462136,3462136,3462136,3462144,3462144,3462144,3462144,3462144,3462144,3462144,3462144,3462144</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" s="0" t="n">
+        <v>840</v>
+      </c>
+      <c r="F207" s="0" t="inlineStr">
+        <is>
+          <t>L10 W2/20; N=18; EHP=780.440400; normal:17x9,normal:18x9</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" s="0" t="n">
+        <v>183</v>
+      </c>
+      <c r="C208" s="0" t="inlineStr">
+        <is>
+          <t>3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464136,3464144,3464144,3464144,3464144,3464144,3464144,3464144</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" s="0" t="n">
+        <v>825</v>
+      </c>
+      <c r="F208" s="0" t="inlineStr">
+        <is>
+          <t>L10 W3/20; N=19; EHP=949.756800; normal:17x7,normal:18x7,swarm:84x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" s="0" t="n">
+        <v>184</v>
+      </c>
+      <c r="C209" s="0" t="inlineStr">
+        <is>
+          <t>3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466136,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" s="0" t="n">
+        <v>810</v>
+      </c>
+      <c r="F209" s="0" t="inlineStr">
+        <is>
+          <t>L10 W4/20; N=20; EHP=1159.764000; normal:17x7,normal:18x8,swarm:84x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" s="0" t="n">
+        <v>185</v>
+      </c>
+      <c r="C210" s="0" t="inlineStr">
+        <is>
+          <t>3468136,3468673,3468668,3468136,3468673,3468868,3468136,3468673,3468988,3468136,3468673,3468136,3468673,3468136,3468144,3468144,3468144,3468144,3468144,3468144,3468144</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" s="0" t="n">
+        <v>795</v>
+      </c>
+      <c r="F210" s="0" t="inlineStr">
+        <is>
+          <t>L10 W5/20; N=21; EHP=1584.326016; normal:17x6,normal:18x7,medium:83x1,swarm:84x5,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" s="0" t="n">
+        <v>186</v>
+      </c>
+      <c r="C211" s="0" t="inlineStr">
+        <is>
+          <t>3470136,3470673,3470242,3470107,3470668,3470136,3470673,3470786,3470868,3470136,3470673,3470988,3470136,3470673,3470136,3470673,3470144,3470673,3470144,3470144,3470144,3470144</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" s="0" t="n">
+        <v>780</v>
+      </c>
+      <c r="F211" s="0" t="inlineStr">
+        <is>
+          <t>L10 W6/20; N=22; EHP=1718.310000; air:13x1,normal:17x5,normal:18x5,fast:30x1,medium:83x1,swarm:84x6,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" s="0" t="n">
+        <v>187</v>
+      </c>
+      <c r="C212" s="0" t="inlineStr">
+        <is>
+          <t>3472136,3472673,3472466,3472091,3472668,3472136,3472673,3472786,3472868,3472136,3472673,3472988,3472136,3472673,3472136,3472673,3472144,3472673,3472144,3472144,3472144,3472144,3472144</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" s="0" t="n">
+        <v>765</v>
+      </c>
+      <c r="F212" s="0" t="inlineStr">
+        <is>
+          <t>L10 W7/20; N=23; EHP=2075.078400; air:11x1,normal:17x5,normal:18x6,fast:58x1,medium:83x1,swarm:84x6,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" s="0" t="n">
+        <v>188</v>
+      </c>
+      <c r="C213" s="0" t="inlineStr">
+        <is>
+          <t>3474136,3474673,3474466,3474115,3474668,3474136,3474673,3474514,3474868,3474136,3474673,3474988,3474136,3474673,3474136,3474673,3474136,3474673,3474144,3474144,3474144,3474144,3474144,3474144</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" s="0" t="n">
+        <v>750</v>
+      </c>
+      <c r="F213" s="0" t="inlineStr">
+        <is>
+          <t>L10 W8/20; N=24; EHP=2488.996800; air:14x1,normal:17x6,normal:18x6,fast:58x1,fast:64x1,medium:83x1,swarm:84x6,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" s="0" t="n">
+        <v>189</v>
+      </c>
+      <c r="C214" s="0" t="inlineStr">
+        <is>
+          <t>3476136,3476673,3476242,3476091,3476668,3476136,3476673,3476514,3476107,3476868,3476136,3476673,3476786,3476988,3476136,3476673,3476136,3476673,3476144,3476673,3476144,3476673,3476144,3476144,3476144</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" s="0" t="n">
+        <v>735</v>
+      </c>
+      <c r="F214" s="0" t="inlineStr">
+        <is>
+          <t>L10 W9/20; N=25; EHP=2964.180000; air:11x1,air:13x1,normal:17x5,normal:18x5,fast:30x1,fast:64x1,medium:83x1,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" s="0" t="n">
+        <v>190</v>
+      </c>
+      <c r="C215" s="0" t="inlineStr">
+        <is>
+          <t>3478136,3478673,3478242,3478091,3478668,3478136,3478673,3478466,3478115,3478868,3478136,3478673,3478786,3478988,3478136,3478673,3478136,3478673,3478144,3478673,3478144,3478673,3478144,3478144,3478144,3478144</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" s="0" t="n">
+        <v>720</v>
+      </c>
+      <c r="F215" s="0" t="inlineStr">
+        <is>
+          <t>L10 W10/20; N=26; EHP=3925.311936; air:11x1,air:14x1,normal:17x5,normal:18x6,fast:30x1,fast:58x1,medium:83x1,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" s="0" t="n">
+        <v>191</v>
+      </c>
+      <c r="C216" s="0" t="inlineStr">
+        <is>
+          <t>3480136,3480673,3480466,3480668,3480565,3480136,3480673,3480514,3480668,3480645,3480136,3480673,3480786,3480868,3480136,3480673,3480988,3480136,3480673,3480144,3480673,3480144,3480673,3480144,3480144,3480144,3480144</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" s="0" t="n">
+        <v>705</v>
+      </c>
+      <c r="F216" s="0" t="inlineStr">
+        <is>
+          <t>L10 W11/20; N=27; EHP=4114.800000; normal:17x5,normal:18x6,fast:58x1,fast:64x1,heavy:70x1,heavy:80x1,medium:83x2,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" s="0" t="n">
+        <v>192</v>
+      </c>
+      <c r="C217" s="0" t="inlineStr">
+        <is>
+          <t>3482136,3482673,3482242,3482091,3482668,3482645,3482136,3482673,3482466,3482107,3482868,3482693,3482136,3482673,3482514,3482115,3482988,3482136,3482673,3482988,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482144</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" s="0" t="n">
+        <v>690</v>
+      </c>
+      <c r="F217" s="0" t="inlineStr">
+        <is>
+          <t>L10 W12/20; N=28; EHP=4798.466400; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x1,swarm:84x7,heavy:86x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" s="0" t="n">
+        <v>193</v>
+      </c>
+      <c r="C218" s="0" t="inlineStr">
+        <is>
+          <t>3484136,3484673,3484242,3484091,3484668,3484253,3484136,3484673,3484514,3484107,3484868,3484693,3484136,3484673,3484786,3484115,3484868,3484136,3484673,3484988,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" s="0" t="n">
+        <v>675</v>
+      </c>
+      <c r="F218" s="0" t="inlineStr">
+        <is>
+          <t>L10 W13/20; N=29; EHP=5559.856800; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x5,fast:30x1,heavy:31x1,fast:64x1,medium:83x1,swarm:84x8,heavy:86x1,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" s="0" t="n">
+        <v>194</v>
+      </c>
+      <c r="C219" s="0" t="inlineStr">
+        <is>
+          <t>3486136,3486673,3486242,3486091,3486668,3486253,3486136,3486673,3486466,3486107,3486668,3486325,3486136,3486673,3486786,3486115,3486868,3487021,3486136,3486673,3486988,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" s="0" t="n">
+        <v>660</v>
+      </c>
+      <c r="F219" s="0" t="inlineStr">
+        <is>
+          <t>L10 W14/20; N=30; EHP=6403.086000; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,medium:83x2,swarm:84x8,fast:98x1,medium:108x1,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" s="0" t="n">
+        <v>195</v>
+      </c>
+      <c r="C220" s="0" t="inlineStr">
+        <is>
+          <t>3488136,3488673,3488466,3488091,3488668,3488325,3488566,3488136,3488673,3488514,3488107,3488868,3488565,3488136,3488673,3488786,3488115,3488988,3489021,3488136,3488673,3488988,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" s="0" t="n">
+        <v>645</v>
+      </c>
+      <c r="F220" s="0" t="inlineStr">
+        <is>
+          <t>L10 W15/20; N=31; EHP=8212.141056; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x5,heavy:40x1,fast:58x1,fast:64x1,elite:70x1,heavy:70x1,medium:83x1,swarm:84x8,fast:98x1,medium:108x1,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" s="0" t="n">
+        <v>196</v>
+      </c>
+      <c r="C221" s="0" t="inlineStr">
+        <is>
+          <t>3490136,3490673,3490242,3490668,3490565,3490136,3490673,3490466,3490868,3490709,3490136,3490673,3490514,3490868,3491021,3490136,3490673,3490988,3490136,3490673,3490136,3490673,3490136,3490673,3490144,3490673,3490144,3490144,3490144,3490144,3490144,3490144</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" s="0" t="n">
+        <v>630</v>
+      </c>
+      <c r="F221" s="0" t="inlineStr">
+        <is>
+          <t>L10 W16/20; N=32; EHP=8541.000000; normal:17x7,normal:18x7,fast:30x1,fast:58x1,fast:64x1,heavy:70x1,medium:83x1,swarm:84x8,heavy:88x1,medium:108x2,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" s="0" t="n">
+        <v>197</v>
+      </c>
+      <c r="C222" s="0" t="inlineStr">
+        <is>
+          <t>3492136,3492673,3492242,3492091,3492668,3492565,3492136,3492673,3492514,3492107,3492668,3492645,3492136,3492673,3492786,3492115,3492868,3492709,3492136,3492673,3492988,3492136,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492144</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" s="0" t="n">
+        <v>615</v>
+      </c>
+      <c r="F222" s="0" t="inlineStr">
+        <is>
+          <t>L10 W17/20; N=33; EHP=9464.954400; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x6,fast:30x1,fast:64x1,heavy:70x1,heavy:80x1,medium:83x2,swarm:84x9,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" s="0" t="n">
+        <v>198</v>
+      </c>
+      <c r="C223" s="0" t="inlineStr">
+        <is>
+          <t>3494136,3494673,3494242,3494091,3494668,3494645,3494136,3494673,3494466,3494107,3494868,3494693,3494136,3494673,3494514,3494107,3494868,3494709,3494136,3494673,3494786,3494115,3494988,3494144,3494673,3494988,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="F223" s="0" t="inlineStr">
+        <is>
+          <t>L10 W18/20; N=34; EHP=10676.686800; air:11x1,air:13x2,air:14x1,normal:17x4,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x1,swarm:84x9,heavy:86x1,heavy:88x1,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" s="0" t="n">
+        <v>199</v>
+      </c>
+      <c r="C224" s="0" t="inlineStr">
+        <is>
+          <t>3496136,3496673,3496242,3496091,3496668,3496253,3496136,3496673,3496466,3496091,3496668,3496645,3496136,3496673,3496514,3496107,3496868,3496693,3496136,3496673,3496786,3496115,3496868,3496136,3496673,3496988,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" s="0" t="n">
+        <v>585</v>
+      </c>
+      <c r="F224" s="0" t="inlineStr">
+        <is>
+          <t>L10 W19/20; N=35; EHP=11990.832000; air:11x2,air:13x1,air:14x1,normal:17x5,normal:18x5,fast:30x1,heavy:31x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x9,heavy:86x1,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="C225" s="0" t="inlineStr">
+        <is>
+          <t>3498136,3498673,3498242,3498091,3498668,3498253,3498990,3498136,3498673,3498466,3498107,3498668,3498325,3498136,3498673,3498514,3498115,3498868,3498693,3498136,3498673,3498786,3498115,3498988,3498144,3498673,3498988,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498673</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" s="0" t="n">
+        <v>570</v>
+      </c>
+      <c r="F225" s="0" t="inlineStr">
+        <is>
+          <t>L10 W20/20; N=36; EHP=16764.381000; air:11x1,air:13x1,air:14x2,normal:17x4,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x2,swarm:84x10,heavy:86x1,fast:98x1,medium:108x1,elite:123x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" s="0" t="n">
+        <v>201</v>
+      </c>
+      <c r="C226" s="0" t="inlineStr">
+        <is>
+          <t>3500136,3500136,3500136,3500136,3500136,3500136,3500136,3500136,3500136,3500144,3500144,3500144,3500144,3500144,3500144,3500144,3500144,3500144</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" s="0" t="n">
+        <v>850</v>
+      </c>
+      <c r="F226" s="0" t="inlineStr">
+        <is>
+          <t>L11 W1/20; N=18; EHP=702.000000; normal:17x9,normal:18x9</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" s="0" t="n">
+        <v>202</v>
+      </c>
+      <c r="C227" s="0" t="inlineStr">
+        <is>
+          <t>3502136,3502136,3502136,3502136,3502136,3502136,3502136,3502136,3502136,3502136,3502144,3502144,3502144,3502144,3502144,3502144,3502144,3502144,3502144</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" s="0" t="n">
+        <v>835</v>
+      </c>
+      <c r="F227" s="0" t="inlineStr">
+        <is>
+          <t>L11 W2/20; N=19; EHP=843.258000; normal:17x10,normal:18x9</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" s="0" t="n">
+        <v>203</v>
+      </c>
+      <c r="C228" s="0" t="inlineStr">
+        <is>
+          <t>3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504673,3504136,3504136,3504136,3504144,3504144,3504144,3504144,3504144,3504144,3504144</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" s="0" t="n">
+        <v>820</v>
+      </c>
+      <c r="F228" s="0" t="inlineStr">
+        <is>
+          <t>L11 W3/20; N=20; EHP=1023.360000; normal:17x8,normal:18x7,swarm:84x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" s="0" t="n">
+        <v>204</v>
+      </c>
+      <c r="C229" s="0" t="inlineStr">
+        <is>
+          <t>3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506673,3506136,3506136,3506136,3506144,3506144,3506144,3506144,3506144,3506144,3506144,3506144</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" s="0" t="n">
+        <v>805</v>
+      </c>
+      <c r="F229" s="0" t="inlineStr">
+        <is>
+          <t>L11 W4/20; N=21; EHP=1246.518000; normal:17x8,normal:18x8,swarm:84x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" s="0" t="n">
+        <v>205</v>
+      </c>
+      <c r="C230" s="0" t="inlineStr">
+        <is>
+          <t>3508136,3508673,3508668,3508136,3508673,3508868,3508136,3508673,3508988,3508136,3508673,3508136,3508673,3508136,3508673,3508136,3508144,3508144,3508144,3508144,3508144,3508144</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" s="0" t="n">
+        <v>790</v>
+      </c>
+      <c r="F230" s="0" t="inlineStr">
+        <is>
+          <t>L11 W5/20; N=22; EHP=1698.977280; normal:17x7,normal:18x6,medium:83x1,swarm:84x6,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" s="0" t="n">
+        <v>206</v>
+      </c>
+      <c r="C231" s="0" t="inlineStr">
+        <is>
+          <t>3510136,3510673,3510466,3510107,3510668,3510136,3510673,3510786,3510868,3510136,3510673,3510988,3510136,3510673,3510136,3510673,3510136,3510673,3510144,3510144,3510144,3510144,3510144</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" s="0" t="n">
+        <v>775</v>
+      </c>
+      <c r="F231" s="0" t="inlineStr">
+        <is>
+          <t>L11 W6/20; N=23; EHP=1838.850000; air:13x1,normal:17x6,normal:18x5,fast:58x1,medium:83x1,swarm:84x6,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" s="0" t="n">
+        <v>207</v>
+      </c>
+      <c r="C232" s="0" t="inlineStr">
+        <is>
+          <t>3512136,3512673,3512466,3512091,3512668,3512136,3512673,3512514,3512868,3512136,3512673,3512988,3512136,3512673,3512136,3512673,3512136,3512673,3512144,3512144,3512144,3512144,3512144,3512144</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" s="0" t="n">
+        <v>760</v>
+      </c>
+      <c r="F232" s="0" t="inlineStr">
+        <is>
+          <t>L11 W7/20; N=24; EHP=2216.448000; air:11x1,normal:17x6,normal:18x6,fast:58x1,fast:64x1,medium:83x1,swarm:84x6,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" s="0" t="n">
+        <v>208</v>
+      </c>
+      <c r="C233" s="0" t="inlineStr">
+        <is>
+          <t>3514136,3514673,3514242,3514107,3514668,3514136,3514673,3514514,3514115,3514868,3514136,3514673,3514786,3514988,3514136,3514673,3514136,3514673,3514144,3514673,3514144,3514673,3514144,3514144,3514144</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" s="0" t="n">
+        <v>745</v>
+      </c>
+      <c r="F233" s="0" t="inlineStr">
+        <is>
+          <t>L11 W8/20; N=25; EHP=2653.950000; air:13x1,air:14x1,normal:17x5,normal:18x5,fast:30x1,fast:64x1,medium:83x1,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" s="0" t="n">
+        <v>209</v>
+      </c>
+      <c r="C234" s="0" t="inlineStr">
+        <is>
+          <t>3516136,3516673,3516242,3516091,3516668,3516136,3516673,3516466,3516107,3516868,3516136,3516673,3516786,3516988,3516136,3516673,3516136,3516673,3516136,3516673,3516144,3516673,3516144,3516144,3516144,3516144</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" s="0" t="n">
+        <v>730</v>
+      </c>
+      <c r="F234" s="0" t="inlineStr">
+        <is>
+          <t>L11 W9/20; N=26; EHP=3155.568000; air:11x1,air:13x1,normal:17x6,normal:18x5,fast:30x1,fast:58x1,medium:83x1,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" s="0" t="n">
+        <v>210</v>
+      </c>
+      <c r="C235" s="0" t="inlineStr">
+        <is>
+          <t>3518136,3518673,3518466,3518091,3518668,3518136,3518673,3518514,3518115,3518668,3518136,3518673,3518786,3518868,3518136,3518673,3518988,3518136,3518673,3518136,3518673,3518144,3518673,3518144,3518144,3518144,3518144</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" s="0" t="n">
+        <v>715</v>
+      </c>
+      <c r="F235" s="0" t="inlineStr">
+        <is>
+          <t>L11 W10/20; N=27; EHP=4172.575680; air:11x1,air:14x1,normal:17x6,normal:18x5,fast:58x1,fast:64x1,medium:83x2,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" s="0" t="n">
+        <v>211</v>
+      </c>
+      <c r="C236" s="0" t="inlineStr">
+        <is>
+          <t>3520136,3520673,3520242,3520668,3520541,3520136,3520673,3520466,3520868,3520565,3520136,3520673,3520514,3520988,3520136,3520673,3520988,3520136,3520673,3520136,3520673,3520144,3520673,3520144,3520144,3520144,3520144,3520144</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" s="0" t="n">
+        <v>700</v>
+      </c>
+      <c r="F236" s="0" t="inlineStr">
+        <is>
+          <t>L11 W11/20; N=28; EHP=4368.000000; normal:17x6,normal:18x6,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x1,swarm:84x7,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" s="0" t="n">
+        <v>212</v>
+      </c>
+      <c r="C237" s="0" t="inlineStr">
+        <is>
+          <t>3522136,3522673,3522242,3522091,3522668,3522541,3522136,3522673,3522514,3522107,3522868,3522709,3522136,3522673,3522786,3522115,3522868,3522136,3522673,3522988,3522136,3522673,3522144,3522673,3522144,3522673,3522144,3522673,3522144</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" s="0" t="n">
+        <v>685</v>
+      </c>
+      <c r="F237" s="0" t="inlineStr">
+        <is>
+          <t>L11 W12/20; N=29; EHP=5087.238000; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x4,fast:30x1,fast:64x1,heavy:67x1,medium:83x1,swarm:84x8,heavy:88x1,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" s="0" t="n">
+        <v>213</v>
+      </c>
+      <c r="C238" s="0" t="inlineStr">
+        <is>
+          <t>3524136,3524673,3524242,3524091,3524668,3524645,3524136,3524673,3524466,3524107,3524668,3524693,3524136,3524673,3524786,3524115,3524868,3524709,3524136,3524673,3524988,3524136,3524673,3524144,3524673,3524144,3524673,3524144,3524673,3524144</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" s="0" t="n">
+        <v>670</v>
+      </c>
+      <c r="F238" s="0" t="inlineStr">
+        <is>
+          <t>L11 W13/20; N=30; EHP=5887.440000; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x4,fast:30x1,fast:58x1,heavy:80x1,medium:83x2,swarm:84x8,heavy:86x1,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" s="0" t="n">
+        <v>214</v>
+      </c>
+      <c r="C239" s="0" t="inlineStr">
+        <is>
+          <t>3526136,3526673,3526466,3526091,3526668,3526253,3526136,3526673,3526514,3526107,3526868,3526645,3526136,3526673,3526786,3526115,3526988,3526693,3526136,3526673,3526988,3526136,3526673,3526144,3526673,3526144,3526673,3526144,3526673,3526144,3526144</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" s="0" t="n">
+        <v>655</v>
+      </c>
+      <c r="F239" s="0" t="inlineStr">
+        <is>
+          <t>L11 W14/20; N=31; EHP=6772.818000; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x5,heavy:31x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x1,swarm:84x8,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" s="0" t="n">
+        <v>215</v>
+      </c>
+      <c r="C240" s="0" t="inlineStr">
+        <is>
+          <t>3528136,3528673,3528242,3528091,3528668,3528253,3528542,3528136,3528673,3528466,3528107,3528868,3528325,3528136,3528673,3528514,3528115,3528868,3528693,3528136,3528673,3528988,3528136,3528673,3528144,3528673,3528144,3528673,3528144,3528673,3528144,3528144</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" s="0" t="n">
+        <v>640</v>
+      </c>
+      <c r="F240" s="0" t="inlineStr">
+        <is>
+          <t>L11 W15/20; N=32; EHP=8677.294080; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,elite:67x1,medium:83x1,swarm:84x8,heavy:86x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" s="0" t="n">
+        <v>216</v>
+      </c>
+      <c r="C241" s="0" t="inlineStr">
+        <is>
+          <t>3530136,3530673,3530242,3530668,3530253,3530136,3530673,3530514,3530668,3530325,3530136,3530673,3530786,3530868,3531021,3530136,3530673,3530988,3530136,3530673,3530136,3530673,3530136,3530673,3530144,3530673,3530144,3530673,3530144,3530144,3530144,3530144,3530144</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" s="0" t="n">
+        <v>625</v>
+      </c>
+      <c r="F241" s="0" t="inlineStr">
+        <is>
+          <t>L11 W16/20; N=33; EHP=9025.000000; normal:17x7,normal:18x7,fast:30x1,heavy:31x1,heavy:40x1,fast:64x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x1,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" s="0" t="n">
+        <v>217</v>
+      </c>
+      <c r="C242" s="0" t="inlineStr">
+        <is>
+          <t>3532136,3532673,3532242,3532091,3532668,3532325,3532136,3532673,3532466,3532107,3532868,3532565,3532136,3532673,3532514,3532115,3532868,3533021,3532136,3532673,3532786,3532115,3532988,3532136,3532673,3532988,3532144,3532673,3532144,3532673,3532144,3532673,3532144,3532673</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" s="0" t="n">
+        <v>610</v>
+      </c>
+      <c r="F242" s="0" t="inlineStr">
+        <is>
+          <t>L11 W17/20; N=34; EHP=9982.128000; air:11x1,air:13x1,air:14x2,normal:17x5,normal:18x4,fast:30x1,heavy:40x1,fast:58x1,fast:64x1,heavy:70x1,medium:83x1,swarm:84x9,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" s="0" t="n">
+        <v>218</v>
+      </c>
+      <c r="C243" s="0" t="inlineStr">
+        <is>
+          <t>3534136,3534673,3534242,3534091,3534668,3534541,3534136,3534673,3534466,3534107,3534668,3534565,3534136,3534673,3534514,3534107,3534868,3535021,3534136,3534673,3534786,3534115,3534868,3534136,3534673,3534988,3534144,3534673,3534144,3534673,3534144,3534673,3534144,3534673,3534144</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" s="0" t="n">
+        <v>595</v>
+      </c>
+      <c r="F243" s="0" t="inlineStr">
+        <is>
+          <t>L11 W18/20; N=35; EHP=11250.330000; air:11x1,air:13x2,air:14x1,normal:17x5,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x2,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" s="0" t="n">
+        <v>219</v>
+      </c>
+      <c r="C244" s="0" t="inlineStr">
+        <is>
+          <t>3536136,3536673,3536242,3536091,3536668,3536541,3536136,3536673,3536466,3536091,3536668,3536565,3536136,3536673,3536514,3536107,3536868,3536709,3536136,3536673,3536786,3536115,3536988,3536136,3536673,3536988,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673,3536144,3536673</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" s="0" t="n">
+        <v>580</v>
+      </c>
+      <c r="F244" s="0" t="inlineStr">
+        <is>
+          <t>L11 W19/20; N=36; EHP=12624.768000; air:11x2,air:13x1,air:14x1,normal:17x5,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x10,heavy:88x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" s="0" t="n">
+        <v>220</v>
+      </c>
+      <c r="C245" s="0" t="inlineStr">
+        <is>
+          <t>3538136,3538673,3538242,3538091,3538668,3538541,3538990,3538136,3538673,3538466,3538107,3538868,3538645,3538136,3538673,3538514,3538115,3538868,3538709,3538136,3538673,3538786,3538115,3538988,3538136,3538673,3538988,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673,3538144,3538673</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" s="0" t="n">
+        <v>565</v>
+      </c>
+      <c r="F245" s="0" t="inlineStr">
+        <is>
+          <t>L11 W20/20; N=37; EHP=17637.067500; air:11x1,air:13x1,air:14x2,normal:17x5,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:80x1,medium:83x1,swarm:84x10,heavy:88x1,fast:98x1,medium:108x2,elite:123x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" s="0" t="n">
+        <v>221</v>
+      </c>
+      <c r="C246" s="0" t="inlineStr">
+        <is>
+          <t>3540136,3540136,3540136,3540136,3540136,3540136,3540136,3540136,3540136,3540144,3540144,3540144,3540144,3540144,3540144,3540144,3540144,3540144,3540144</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" s="0" t="n">
+        <v>845</v>
+      </c>
+      <c r="F246" s="0" t="inlineStr">
+        <is>
+          <t>L12 W1/20; N=19; EHP=758.100000; normal:17x9,normal:18x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" s="0" t="n">
+        <v>222</v>
+      </c>
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t>3542136,3542136,3542136,3542136,3542136,3542136,3542136,3542136,3542136,3542136,3542144,3542144,3542144,3542144,3542144,3542144,3542144,3542144,3542144,3542144</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" s="0" t="n">
+        <v>830</v>
+      </c>
+      <c r="F247" s="0" t="inlineStr">
+        <is>
+          <t>L12 W2/20; N=20; EHP=908.124000; normal:17x10,normal:18x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" s="0" t="n">
+        <v>223</v>
+      </c>
+      <c r="C248" s="0" t="inlineStr">
+        <is>
+          <t>3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544136,3544136,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" s="0" t="n">
+        <v>815</v>
+      </c>
+      <c r="F248" s="0" t="inlineStr">
+        <is>
+          <t>L12 W3/20; N=21; EHP=1099.324800; normal:17x8,normal:18x8,swarm:84x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" s="0" t="n">
+        <v>224</v>
+      </c>
+      <c r="C249" s="0" t="inlineStr">
+        <is>
+          <t>3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546136,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="F249" s="0" t="inlineStr">
+        <is>
+          <t>L12 W4/20; N=22; EHP=1336.011600; normal:17x8,normal:18x8,swarm:84x6</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" s="0" t="n">
+        <v>225</v>
+      </c>
+      <c r="C250" s="0" t="inlineStr">
+        <is>
+          <t>3548136,3548673,3548668,3548136,3548673,3548868,3548136,3548673,3548988,3548136,3548673,3548136,3548673,3548136,3548673,3548136,3548144,3548144,3548144,3548144,3548144,3548144,3548144</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" s="0" t="n">
+        <v>785</v>
+      </c>
+      <c r="F250" s="0" t="inlineStr">
+        <is>
+          <t>L12 W5/20; N=23; EHP=1817.192832; normal:17x7,normal:18x7,medium:83x1,swarm:84x6,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" s="0" t="n">
+        <v>226</v>
+      </c>
+      <c r="C251" s="0" t="inlineStr">
+        <is>
+          <t>3550136,3550673,3550466,3550107,3550668,3550136,3550673,3550514,3550868,3550136,3550673,3550988,3550136,3550673,3550136,3550673,3550136,3550673,3550144,3550144,3550144,3550144,3550144,3550144</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" s="0" t="n">
+        <v>770</v>
+      </c>
+      <c r="F251" s="0" t="inlineStr">
+        <is>
+          <t>L12 W6/20; N=24; EHP=1963.080000; air:13x1,normal:17x6,normal:18x6,fast:58x1,fast:64x1,medium:83x1,swarm:84x6,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" s="0" t="n">
+        <v>227</v>
+      </c>
+      <c r="C252" s="0" t="inlineStr">
+        <is>
+          <t>3552136,3552673,3552242,3552091,3552668,3552136,3552673,3552514,3552115,3552868,3552136,3552673,3552786,3552988,3552136,3552673,3552136,3552673,3552144,3552673,3552144,3552673,3552144,3552144,3552144</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" s="0" t="n">
+        <v>755</v>
+      </c>
+      <c r="F252" s="0" t="inlineStr">
+        <is>
+          <t>L12 W7/20; N=25; EHP=2362.080000; air:11x1,air:14x1,normal:17x5,normal:18x5,fast:30x1,fast:64x1,medium:83x1,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" s="0" t="n">
+        <v>228</v>
+      </c>
+      <c r="C253" s="0" t="inlineStr">
+        <is>
+          <t>3554136,3554673,3554242,3554107,3554668,3554136,3554673,3554466,3554115,3554868,3554136,3554673,3554786,3554988,3554136,3554673,3554136,3554673,3554144,3554673,3554144,3554673,3554144,3554144,3554144,3554144</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" s="0" t="n">
+        <v>740</v>
+      </c>
+      <c r="F253" s="0" t="inlineStr">
+        <is>
+          <t>L12 W8/20; N=26; EHP=2823.802800; air:13x1,air:14x1,normal:17x5,normal:18x6,fast:30x1,fast:58x1,medium:83x1,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" s="0" t="n">
+        <v>229</v>
+      </c>
+      <c r="C254" s="0" t="inlineStr">
+        <is>
+          <t>3556136,3556673,3556466,3556091,3556668,3556136,3556673,3556514,3556107,3556668,3556136,3556673,3556786,3556868,3556136,3556673,3556988,3556136,3556673,3556144,3556673,3556144,3556673,3556144,3556144,3556144,3556144</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" s="0" t="n">
+        <v>725</v>
+      </c>
+      <c r="F254" s="0" t="inlineStr">
+        <is>
+          <t>L12 W9/20; N=27; EHP=3352.557600; air:11x1,air:13x1,normal:17x5,normal:18x6,fast:58x1,fast:64x1,medium:83x2,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" s="0" t="n">
+        <v>230</v>
+      </c>
+      <c r="C255" s="0" t="inlineStr">
+        <is>
+          <t>3558136,3558673,3558242,3558091,3558668,3558136,3558673,3558466,3558115,3558868,3558136,3558673,3558514,3558988,3558136,3558673,3558988,3558136,3558673,3558136,3558673,3558144,3558673,3558144,3558144,3558144,3558144,3558144</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" s="0" t="n">
+        <v>710</v>
+      </c>
+      <c r="F255" s="0" t="inlineStr">
+        <is>
+          <t>L12 W10/20; N=28; EHP=4426.972032; air:11x1,air:14x1,normal:17x6,normal:18x6,fast:30x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x7,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" s="0" t="n">
+        <v>231</v>
+      </c>
+      <c r="C256" s="0" t="inlineStr">
+        <is>
+          <t>3560136,3560673,3560242,3560668,3560541,3560136,3560673,3560514,3560868,3560709,3560136,3560673,3560786,3560868,3560136,3560673,3560988,3560136,3560673,3560136,3560673,3560144,3560673,3560144,3560673,3560144,3560144,3560144,3560144</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" s="0" t="n">
+        <v>695</v>
+      </c>
+      <c r="F256" s="0" t="inlineStr">
+        <is>
+          <t>L12 W11/20; N=29; EHP=4628.400000; normal:17x6,normal:18x6,fast:30x1,fast:64x1,heavy:67x1,medium:83x1,swarm:84x8,heavy:88x1,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" s="0" t="n">
+        <v>232</v>
+      </c>
+      <c r="C257" s="0" t="inlineStr">
+        <is>
+          <t>3562136,3562673,3562242,3562091,3562668,3562645,3562136,3562673,3562466,3562107,3562668,3562693,3562136,3562673,3562786,3562115,3562868,3562709,3562136,3562673,3562988,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" s="0" t="n">
+        <v>680</v>
+      </c>
+      <c r="F257" s="0" t="inlineStr">
+        <is>
+          <t>L12 W12/20; N=30; EHP=5384.106000; air:11x1,air:13x1,air:14x1,normal:17x4,normal:18x5,fast:30x1,fast:58x1,heavy:80x1,medium:83x2,swarm:84x8,heavy:86x1,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" s="0" t="n">
+        <v>233</v>
+      </c>
+      <c r="C258" s="0" t="inlineStr">
+        <is>
+          <t>3564136,3564673,3564466,3564091,3564668,3564253,3564136,3564673,3564514,3564107,3564868,3564645,3564136,3564673,3564786,3564115,3564988,3564693,3564136,3564673,3564988,3564136,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564144</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" s="0" t="n">
+        <v>665</v>
+      </c>
+      <c r="F258" s="0" t="inlineStr">
+        <is>
+          <t>L12 W13/20; N=31; EHP=6224.080800; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x5,heavy:31x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x1,swarm:84x8,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" s="0" t="n">
+        <v>234</v>
+      </c>
+      <c r="C259" s="0" t="inlineStr">
+        <is>
+          <t>3566136,3566673,3566242,3566091,3566668,3566253,3566136,3566673,3566466,3566107,3566868,3566325,3566136,3566673,3566514,3566115,3566868,3566693,3566136,3566673,3566988,3566136,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566144,3566144</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" s="0" t="n">
+        <v>650</v>
+      </c>
+      <c r="F259" s="0" t="inlineStr">
+        <is>
+          <t>L12 W14/20; N=32; EHP=7152.633600; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x6,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,heavy:86x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" s="0" t="n">
+        <v>235</v>
+      </c>
+      <c r="C260" s="0" t="inlineStr">
+        <is>
+          <t>3568136,3568673,3568242,3568091,3568668,3568253,3568542,3568136,3568673,3568514,3568107,3568668,3568325,3568136,3568673,3568786,3568115,3568868,3569021,3568136,3568673,3568988,3568136,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" s="0" t="n">
+        <v>635</v>
+      </c>
+      <c r="F260" s="0" t="inlineStr">
+        <is>
+          <t>L12 W15/20; N=33; EHP=9154.962432; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:64x1,elite:67x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x1,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" s="0" t="n">
+        <v>236</v>
+      </c>
+      <c r="C261" s="0" t="inlineStr">
+        <is>
+          <t>3570136,3570673,3570242,3570668,3570325,3570136,3570673,3570466,3570868,3570565,3570136,3570673,3570514,3570868,3571021,3570136,3570673,3570786,3570988,3570136,3570673,3570988,3570136,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570144,3570144,3570144</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" s="0" t="n">
+        <v>620</v>
+      </c>
+      <c r="F261" s="0" t="inlineStr">
+        <is>
+          <t>L12 W16/20; N=34; EHP=9522.000000; normal:17x6,normal:18x7,fast:30x1,heavy:40x1,fast:58x1,fast:64x1,heavy:70x1,medium:83x1,swarm:84x9,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" s="0" t="n">
+        <v>237</v>
+      </c>
+      <c r="C262" s="0" t="inlineStr">
+        <is>
+          <t>3572136,3572673,3572242,3572091,3572668,3572541,3572136,3572673,3572466,3572107,3572668,3572565,3572136,3572673,3572514,3572115,3572868,3573021,3572136,3572673,3572786,3572115,3572868,3572136,3572673,3572988,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" s="0" t="n">
+        <v>605</v>
+      </c>
+      <c r="F262" s="0" t="inlineStr">
+        <is>
+          <t>L12 W17/20; N=35; EHP=10512.852000; air:11x1,air:13x1,air:14x2,normal:17x5,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x2,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" s="0" t="n">
+        <v>238</v>
+      </c>
+      <c r="C263" s="0" t="inlineStr">
+        <is>
+          <t>3574136,3574673,3574242,3574091,3574668,3574541,3574136,3574673,3574466,3574107,3574668,3574565,3574136,3574673,3574514,3574107,3574868,3574709,3574136,3574673,3574786,3574115,3574988,3574136,3574673,3574988,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" s="0" t="n">
+        <v>590</v>
+      </c>
+      <c r="F263" s="0" t="inlineStr">
+        <is>
+          <t>L12 W18/20; N=36; EHP=11838.808800; air:11x1,air:13x2,air:14x1,normal:17x5,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x10,heavy:88x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" s="0" t="n">
+        <v>239</v>
+      </c>
+      <c r="C264" s="0" t="inlineStr">
+        <is>
+          <t>3576136,3576673,3576242,3576091,3576668,3576541,3576136,3576673,3576466,3576091,3576868,3576645,3576136,3576673,3576514,3576107,3576868,3576709,3576136,3576673,3576786,3576115,3576988,3576136,3576673,3576988,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" s="0" t="n">
+        <v>575</v>
+      </c>
+      <c r="F264" s="0" t="inlineStr">
+        <is>
+          <t>L12 W19/20; N=37; EHP=13274.889600; air:11x2,air:13x1,air:14x1,normal:17x5,normal:18x6,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:80x1,medium:83x1,swarm:84x10,heavy:88x1,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" s="0" t="n">
+        <v>240</v>
+      </c>
+      <c r="C265" s="0" t="inlineStr">
+        <is>
+          <t>3578136,3578673,3578242,3578091,3578668,3578645,3579039,3578136,3578673,3578466,3578107,3578668,3578693,3578136,3578673,3578514,3578115,3578868,3578709,3578136,3578673,3578786,3578115,3578868,3578136,3578673,3578988,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" s="0" t="n">
+        <v>560</v>
+      </c>
+      <c r="F265" s="0" t="inlineStr">
+        <is>
+          <t>L12 W20/20; N=38; EHP=18531.754500; air:11x1,air:13x1,air:14x2,normal:17x5,normal:18x6,fast:30x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,heavy:88x1,fast:98x1,medium:108x2,medium:123x1,boss:129x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" s="0" t="n">
+        <v>241</v>
+      </c>
+      <c r="C266" s="0" t="inlineStr">
+        <is>
+          <t>3580136,3580136,3580136,3580136,3580136,3580136,3580136,3580136,3580136,3580136,3580144,3580144,3580144,3580144,3580144,3580144,3580144,3580144,3580144,3580144</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" s="0" t="n">
+        <v>840</v>
+      </c>
+      <c r="F266" s="0" t="inlineStr">
+        <is>
+          <t>L13 W1/20; N=20; EHP=816.000000; normal:17x10,normal:18x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" s="0" t="n">
+        <v>242</v>
+      </c>
+      <c r="C267" s="0" t="inlineStr">
+        <is>
+          <t>3582136,3582136,3582136,3582136,3582136,3582136,3582136,3582136,3582136,3582136,3582136,3582144,3582144,3582144,3582144,3582144,3582144,3582144,3582144,3582144,3582144</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" s="0" t="n">
+        <v>825</v>
+      </c>
+      <c r="F267" s="0" t="inlineStr">
+        <is>
+          <t>L13 W2/20; N=21; EHP=975.038400; normal:17x11,normal:18x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" s="0" t="n">
+        <v>243</v>
+      </c>
+      <c r="C268" s="0" t="inlineStr">
+        <is>
+          <t>3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584136,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" s="0" t="n">
+        <v>810</v>
+      </c>
+      <c r="F268" s="0" t="inlineStr">
+        <is>
+          <t>L13 W3/20; N=22; EHP=1177.651200; normal:17x8,normal:18x8,swarm:84x6</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" s="0" t="n">
+        <v>244</v>
+      </c>
+      <c r="C269" s="0" t="inlineStr">
+        <is>
+          <t>3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586136,3586136,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" s="0" t="n">
+        <v>795</v>
+      </c>
+      <c r="F269" s="0" t="inlineStr">
+        <is>
+          <t>L13 W4/20; N=23; EHP=1428.244800; normal:17x9,normal:18x8,swarm:84x6</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" s="0" t="n">
+        <v>245</v>
+      </c>
+      <c r="C270" s="0" t="inlineStr">
+        <is>
+          <t>3588136,3588673,3588668,3588136,3588673,3588868,3588136,3588673,3588988,3588136,3588673,3588136,3588673,3588136,3588673,3588136,3588136,3588144,3588144,3588144,3588144,3588144,3588144,3588144</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" s="0" t="n">
+        <v>780</v>
+      </c>
+      <c r="F270" s="0" t="inlineStr">
+        <is>
+          <t>L13 W5/20; N=24; EHP=1938.972672; normal:17x8,normal:18x7,medium:83x1,swarm:84x6,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" s="0" t="n">
+        <v>246</v>
+      </c>
+      <c r="C271" s="0" t="inlineStr">
+        <is>
+          <t>3590136,3590673,3590242,3590091,3590668,3590136,3590673,3590514,3590107,3590868,3590136,3590673,3590786,3590988,3590136,3590673,3590136,3590673,3590144,3590673,3590144,3590673,3590144,3590144,3590144</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" s="0" t="n">
+        <v>765</v>
+      </c>
+      <c r="F271" s="0" t="inlineStr">
+        <is>
+          <t>L13 W6/20; N=25; EHP=2091.000000; air:11x1,air:13x1,normal:17x5,normal:18x5,fast:30x1,fast:64x1,medium:83x1,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" s="0" t="n">
+        <v>247</v>
+      </c>
+      <c r="C272" s="0" t="inlineStr">
+        <is>
+          <t>3592136,3592673,3592242,3592091,3592668,3592136,3592673,3592466,3592115,3592868,3592136,3592673,3592786,3592988,3592136,3592673,3592136,3592673,3592136,3592673,3592144,3592673,3592144,3592144,3592144,3592144</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" s="0" t="n">
+        <v>750</v>
+      </c>
+      <c r="F272" s="0" t="inlineStr">
+        <is>
+          <t>L13 W7/20; N=26; EHP=2511.974400; air:11x1,air:14x1,normal:17x6,normal:18x5,fast:30x1,fast:58x1,medium:83x1,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" s="0" t="n">
+        <v>248</v>
+      </c>
+      <c r="C273" s="0" t="inlineStr">
+        <is>
+          <t>3594136,3594673,3594466,3594107,3594668,3594136,3594673,3594514,3594115,3594668,3594136,3594673,3594786,3594868,3594136,3594673,3594988,3594136,3594673,3594136,3594673,3594144,3594673,3594144,3594144,3594144,3594144</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" s="0" t="n">
+        <v>735</v>
+      </c>
+      <c r="F273" s="0" t="inlineStr">
+        <is>
+          <t>L13 W8/20; N=27; EHP=2998.555200; air:13x1,air:14x1,normal:17x6,normal:18x5,fast:58x1,fast:64x1,medium:83x2,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" s="0" t="n">
+        <v>249</v>
+      </c>
+      <c r="C274" s="0" t="inlineStr">
+        <is>
+          <t>3596136,3596673,3596242,3596091,3596668,3596136,3596673,3596466,3596107,3596868,3596136,3596673,3596514,3596988,3596136,3596673,3596988,3596136,3596673,3596136,3596673,3596144,3596673,3596144,3596144,3596144,3596144,3596144</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" s="0" t="n">
+        <v>720</v>
+      </c>
+      <c r="F274" s="0" t="inlineStr">
+        <is>
+          <t>L13 W9/20; N=28; EHP=3555.148800; air:11x1,air:13x1,normal:17x6,normal:18x6,fast:30x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x7,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="C275" s="0" t="inlineStr">
+        <is>
+          <t>3598136,3598673,3598242,3598091,3598668,3598136,3598673,3598514,3598115,3598868,3598136,3598673,3598786,3598868,3598136,3598673,3598988,3598136,3598673,3598136,3598673,3598144,3598673,3598144,3598673,3598144,3598144,3598144,3598144</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" s="0" t="n">
+        <v>705</v>
+      </c>
+      <c r="F275" s="0" t="inlineStr">
+        <is>
+          <t>L13 W10/20; N=29; EHP=4688.500992; air:11x1,air:14x1,normal:17x6,normal:18x6,fast:30x1,fast:64x1,medium:83x1,swarm:84x8,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" s="0" t="n">
+        <v>251</v>
+      </c>
+      <c r="C276" s="0" t="inlineStr">
+        <is>
+          <t>3600136,3600673,3600242,3600668,3600645,3600136,3600673,3600466,3600668,3600693,3600136,3600673,3600786,3600868,3600709,3600136,3600673,3600988,3600136,3600673,3600136,3600673,3600144,3600673,3600144,3600673,3600144,3600144,3600144,3600144</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" s="0" t="n">
+        <v>690</v>
+      </c>
+      <c r="F276" s="0" t="inlineStr">
+        <is>
+          <t>L13 W11/20; N=30; EHP=4896.000000; normal:17x6,normal:18x6,fast:30x1,fast:58x1,heavy:80x1,medium:83x2,swarm:84x8,heavy:86x1,heavy:88x1,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" s="0" t="n">
+        <v>252</v>
+      </c>
+      <c r="C277" s="0" t="inlineStr">
+        <is>
+          <t>3602136,3602673,3602466,3602091,3602668,3602253,3602136,3602673,3602514,3602107,3602868,3602645,3602136,3602673,3602786,3602115,3602988,3602693,3602136,3602673,3602988,3602136,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602144</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E277" s="0" t="n">
+        <v>675</v>
+      </c>
+      <c r="F277" s="0" t="inlineStr">
+        <is>
+          <t>L13 W12/20; N=31; EHP=5689.070400; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x5,heavy:31x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x1,swarm:84x8,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" s="0" t="n">
+        <v>253</v>
+      </c>
+      <c r="C278" s="0" t="inlineStr">
+        <is>
+          <t>3604136,3604673,3604242,3604091,3604668,3604253,3604136,3604673,3604466,3604107,3604868,3604325,3604136,3604673,3604514,3604115,3604868,3604693,3604136,3604673,3604988,3604136,3604673,3604136,3604673,3604144,3604673,3604144,3604673,3604144,3604144,3604144</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" s="0" t="n">
+        <v>660</v>
+      </c>
+      <c r="F278" s="0" t="inlineStr">
+        <is>
+          <t>L13 W13/20; N=32; EHP=6569.779200; air:11x1,air:13x1,air:14x1,normal:17x6,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,heavy:86x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" s="0" t="n">
+        <v>254</v>
+      </c>
+      <c r="C279" s="0" t="inlineStr">
+        <is>
+          <t>3606136,3606673,3606242,3606091,3606668,3606253,3606136,3606673,3606514,3606107,3606668,3606325,3606136,3606673,3606786,3606115,3606868,3607021,3606136,3606673,3606988,3606136,3606673,3606136,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606144</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" s="0" t="n">
+        <v>645</v>
+      </c>
+      <c r="F279" s="0" t="inlineStr">
+        <is>
+          <t>L13 W14/20; N=33; EHP=7542.532800; air:11x1,air:13x1,air:14x1,normal:17x6,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:64x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x1,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" s="0" t="n">
+        <v>255</v>
+      </c>
+      <c r="C280" s="0" t="inlineStr">
+        <is>
+          <t>3608136,3608673,3608242,3608091,3608668,3608325,3608542,3608136,3608673,3608466,3608107,3608868,3608565,3608136,3608673,3608514,3608107,3608868,3609021,3608136,3608673,3608786,3608115,3608988,3608144,3608673,3608988,3608144,3608673,3608144,3608673,3608144,3608673,3608673</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" s="0" t="n">
+        <v>630</v>
+      </c>
+      <c r="F280" s="0" t="inlineStr">
+        <is>
+          <t>L13 W15/20; N=34; EHP=9645.146112; air:11x1,air:13x2,air:14x1,normal:17x4,normal:18x4,fast:30x1,heavy:40x1,fast:58x1,fast:64x1,elite:67x1,heavy:70x1,medium:83x1,swarm:84x9,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" s="0" t="n">
+        <v>256</v>
+      </c>
+      <c r="C281" s="0" t="inlineStr">
+        <is>
+          <t>3610136,3610673,3610242,3610668,3610541,3610136,3610673,3610466,3610668,3610565,3610136,3610673,3610514,3610868,3611021,3610136,3610673,3610786,3610868,3610136,3610673,3610988,3610136,3610673,3610136,3610673,3610144,3610673,3610144,3610673,3610144,3610144,3610144,3610144,3610144</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" s="0" t="n">
+        <v>615</v>
+      </c>
+      <c r="F281" s="0" t="inlineStr">
+        <is>
+          <t>L13 W16/20; N=35; EHP=10031.000000; normal:17x7,normal:18x7,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x2,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" s="0" t="n">
+        <v>257</v>
+      </c>
+      <c r="C282" s="0" t="inlineStr">
+        <is>
+          <t>3612136,3612673,3612242,3612091,3612668,3612541,3612136,3612673,3612466,3612107,3612668,3612565,3612136,3612673,3612514,3612115,3612868,3612709,3612136,3612673,3612786,3612115,3612988,3612136,3612673,3612988,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="F282" s="0" t="inlineStr">
+        <is>
+          <t>L13 W17/20; N=36; EHP=11057.126400; air:11x1,air:13x1,air:14x2,normal:17x5,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x10,heavy:88x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" s="0" t="n">
+        <v>258</v>
+      </c>
+      <c r="C283" s="0" t="inlineStr">
+        <is>
+          <t>3614136,3614673,3614242,3614091,3614668,3614541,3614136,3614673,3614466,3614107,3614868,3614645,3614136,3614673,3614514,3614107,3614868,3614709,3614136,3614673,3614786,3614115,3614988,3614136,3614673,3614988,3614136,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E283" s="0" t="n">
+        <v>585</v>
+      </c>
+      <c r="F283" s="0" t="inlineStr">
+        <is>
+          <t>L13 W18/20; N=37; EHP=12442.123200; air:11x1,air:13x2,air:14x1,normal:17x6,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:80x1,medium:83x1,swarm:84x10,heavy:88x1,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" s="0" t="n">
+        <v>259</v>
+      </c>
+      <c r="C284" s="0" t="inlineStr">
+        <is>
+          <t>3616136,3616673,3616242,3616091,3616668,3616645,3616136,3616673,3616466,3616091,3616668,3616693,3616136,3616673,3616514,3616107,3616868,3616709,3616136,3616673,3616786,3616115,3616868,3616136,3616673,3616988,3616136,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616144</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" s="0" t="n">
+        <v>570</v>
+      </c>
+      <c r="F284" s="0" t="inlineStr">
+        <is>
+          <t>L13 W19/20; N=38; EHP=13941.196800; air:11x2,air:13x1,air:14x1,normal:17x6,normal:18x6,fast:30x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,heavy:88x1,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" s="0" t="n">
+        <v>260</v>
+      </c>
+      <c r="C285" s="0" t="inlineStr">
+        <is>
+          <t>3618136,3618673,3618242,3618091,3618668,3618253,3619047,3618136,3618673,3618466,3618107,3618668,3618645,3618136,3618673,3618514,3618115,3618868,3618693,3618136,3618673,3618786,3618115,3618988,3618136,3618673,3618988,3618136,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618144</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" s="0" t="n">
+        <v>555</v>
+      </c>
+      <c r="F285" s="0" t="inlineStr">
+        <is>
+          <t>L13 W20/20; N=39; EHP=19448.442000; air:11x1,air:13x1,air:14x2,normal:17x6,normal:18x6,fast:30x1,heavy:31x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,fast:98x1,medium:108x1,medium:123x2,boss:130x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" s="0" t="n">
+        <v>261</v>
+      </c>
+      <c r="C286" s="0" t="inlineStr">
+        <is>
+          <t>3620136,3620136,3620136,3620136,3620136,3620136,3620136,3620136,3620136,3620136,3620144,3620144,3620144,3620144,3620144,3620144,3620144,3620144,3620144,3620144,3620144</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" s="0" t="n">
+        <v>835</v>
+      </c>
+      <c r="F286" s="0" t="inlineStr">
+        <is>
+          <t>L14 W1/20; N=21; EHP=875.700000; normal:17x10,normal:18x11</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" s="0" t="n">
+        <v>262</v>
+      </c>
+      <c r="C287" s="0" t="inlineStr">
+        <is>
+          <t>3622136,3622136,3622136,3622136,3622136,3622136,3622136,3622136,3622136,3622136,3622136,3622144,3622144,3622144,3622144,3622144,3622144,3622144,3622144,3622144,3622144,3622144</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" s="0" t="n">
+        <v>820</v>
+      </c>
+      <c r="F287" s="0" t="inlineStr">
+        <is>
+          <t>L14 W2/20; N=22; EHP=1044.001200; normal:17x11,normal:18x11</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" s="0" t="n">
+        <v>263</v>
+      </c>
+      <c r="C288" s="0" t="inlineStr">
+        <is>
+          <t>3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624136,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" s="0" t="n">
+        <v>805</v>
+      </c>
+      <c r="F288" s="0" t="inlineStr">
+        <is>
+          <t>L14 W3/20; N=23; EHP=1258.339200; normal:17x8,normal:18x9,swarm:84x6</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" s="0" t="n">
+        <v>264</v>
+      </c>
+      <c r="C289" s="0" t="inlineStr">
+        <is>
+          <t>3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626136,3626136,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" s="0" t="n">
+        <v>790</v>
+      </c>
+      <c r="F289" s="0" t="inlineStr">
+        <is>
+          <t>L14 W4/20; N=24; EHP=1523.217600; normal:17x9,normal:18x9,swarm:84x6</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" s="0" t="n">
+        <v>265</v>
+      </c>
+      <c r="C290" s="0" t="inlineStr">
+        <is>
+          <t>3628136,3628673,3628668,3628136,3628673,3628868,3628136,3628673,3628988,3628136,3628673,3628136,3628673,3628136,3628673,3628136,3628673,3628144,3628144,3628144,3628144,3628144,3628144,3628144,3628144</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E290" s="0" t="n">
+        <v>775</v>
+      </c>
+      <c r="F290" s="0" t="inlineStr">
+        <is>
+          <t>L14 W5/20; N=25; EHP=2064.316800; normal:17x7,normal:18x8,medium:83x1,swarm:84x7,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" s="0" t="n">
+        <v>266</v>
+      </c>
+      <c r="C291" s="0" t="inlineStr">
+        <is>
+          <t>3630136,3630673,3630242,3630091,3630668,3630136,3630673,3630466,3630107,3630868,3630136,3630673,3630786,3630988,3630136,3630673,3630136,3630673,3630144,3630673,3630144,3630673,3630144,3630144,3630144,3630144</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E291" s="0" t="n">
+        <v>760</v>
+      </c>
+      <c r="F291" s="0" t="inlineStr">
+        <is>
+          <t>L14 W6/20; N=26; EHP=2222.610000; air:11x1,air:13x1,normal:17x5,normal:18x6,fast:30x1,fast:58x1,medium:83x1,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" s="0" t="n">
+        <v>267</v>
+      </c>
+      <c r="C292" s="0" t="inlineStr">
+        <is>
+          <t>3632136,3632673,3632466,3632091,3632668,3632136,3632673,3632514,3632115,3632668,3632136,3632673,3632786,3632868,3632136,3632673,3632988,3632136,3632673,3632144,3632673,3632144,3632673,3632144,3632144,3632144,3632144</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" s="0" t="n">
+        <v>745</v>
+      </c>
+      <c r="F292" s="0" t="inlineStr">
+        <is>
+          <t>L14 W7/20; N=27; EHP=2666.131200; air:11x1,air:14x1,normal:17x5,normal:18x6,fast:58x1,fast:64x1,medium:83x2,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" s="0" t="n">
+        <v>268</v>
+      </c>
+      <c r="C293" s="0" t="inlineStr">
+        <is>
+          <t>3634136,3634673,3634242,3634107,3634668,3634136,3634673,3634466,3634115,3634868,3634136,3634673,3634514,3634988,3634136,3634673,3634988,3634136,3634673,3634136,3634673,3634144,3634673,3634144,3634144,3634144,3634144,3634144</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E293" s="0" t="n">
+        <v>730</v>
+      </c>
+      <c r="F293" s="0" t="inlineStr">
+        <is>
+          <t>L14 W8/20; N=28; EHP=3178.207200; air:13x1,air:14x1,normal:17x6,normal:18x6,fast:30x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x7,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" s="0" t="n">
+        <v>269</v>
+      </c>
+      <c r="C294" s="0" t="inlineStr">
+        <is>
+          <t>3636136,3636673,3636242,3636091,3636668,3636136,3636673,3636514,3636107,3636868,3636136,3636673,3636786,3636868,3636136,3636673,3636988,3636136,3636673,3636136,3636673,3636144,3636673,3636144,3636673,3636144,3636144,3636144,3636144</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E294" s="0" t="n">
+        <v>715</v>
+      </c>
+      <c r="F294" s="0" t="inlineStr">
+        <is>
+          <t>L14 W9/20; N=29; EHP=3763.341600; air:11x1,air:13x1,normal:17x6,normal:18x6,fast:30x1,fast:64x1,medium:83x1,swarm:84x8,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" s="0" t="n">
+        <v>270</v>
+      </c>
+      <c r="C295" s="0" t="inlineStr">
+        <is>
+          <t>3638136,3638673,3638242,3638091,3638668,3638136,3638673,3638466,3638115,3638668,3638136,3638673,3638786,3638868,3638136,3638673,3638988,3638136,3638673,3638136,3638673,3638144,3638673,3638144,3638673,3638144,3638144,3638144,3638144,3638144</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" s="0" t="n">
+        <v>700</v>
+      </c>
+      <c r="F295" s="0" t="inlineStr">
+        <is>
+          <t>L14 W10/20; N=30; EHP=4957.162560; air:11x1,air:14x1,normal:17x6,normal:18x7,fast:30x1,fast:58x1,medium:83x2,swarm:84x8,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" s="0" t="n">
+        <v>271</v>
+      </c>
+      <c r="C296" s="0" t="inlineStr">
+        <is>
+          <t>3640136,3640673,3640466,3640668,3640253,3640136,3640673,3640514,3640868,3640645,3640136,3640673,3640786,3640988,3640693,3640136,3640673,3640988,3640136,3640673,3640136,3640673,3640144,3640673,3640144,3640673,3640144,3640144,3640144,3640144,3640144</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" s="0" t="n">
+        <v>685</v>
+      </c>
+      <c r="F296" s="0" t="inlineStr">
+        <is>
+          <t>L14 W11/20; N=31; EHP=5170.800000; normal:17x6,normal:18x7,heavy:31x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x1,swarm:84x8,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" s="0" t="n">
+        <v>272</v>
+      </c>
+      <c r="C297" s="0" t="inlineStr">
+        <is>
+          <t>3642136,3642673,3642242,3642091,3642668,3642253,3642136,3642673,3642466,3642107,3642868,3642325,3642136,3642673,3642514,3642115,3642868,3642693,3642136,3642673,3642988,3642136,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642144,3642144</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E297" s="0" t="n">
+        <v>670</v>
+      </c>
+      <c r="F297" s="0" t="inlineStr">
+        <is>
+          <t>L14 W12/20; N=32; EHP=6002.131200; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x6,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,heavy:86x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" s="0" t="n">
+        <v>273</v>
+      </c>
+      <c r="C298" s="0" t="inlineStr">
+        <is>
+          <t>3644136,3644673,3644242,3644091,3644668,3644253,3644136,3644673,3644514,3644107,3644668,3644325,3644136,3644673,3644786,3644115,3644868,3645021,3644136,3644673,3644988,3644136,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644144</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E298" s="0" t="n">
+        <v>655</v>
+      </c>
+      <c r="F298" s="0" t="inlineStr">
+        <is>
+          <t>L14 W13/20; N=33; EHP=6924.535200; air:11x1,air:13x1,air:14x1,normal:17x5,normal:18x6,fast:30x1,heavy:31x1,heavy:40x1,fast:64x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x1,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" s="0" t="n">
+        <v>274</v>
+      </c>
+      <c r="C299" s="0" t="inlineStr">
+        <is>
+          <t>3646136,3646673,3646242,3646091,3646668,3646325,3646136,3646673,3646466,3646107,3646868,3646565,3646136,3646673,3646514,3646115,3646868,3647021,3646136,3646673,3646786,3646115,3646988,3646144,3646673,3646988,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" s="0" t="n">
+        <v>640</v>
+      </c>
+      <c r="F299" s="0" t="inlineStr">
+        <is>
+          <t>L14 W14/20; N=34; EHP=7942.515600; air:11x1,air:13x1,air:14x2,normal:17x4,normal:18x5,fast:30x1,heavy:40x1,fast:58x1,fast:64x1,heavy:70x1,medium:83x1,swarm:84x9,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" s="0" t="n">
+        <v>275</v>
+      </c>
+      <c r="C300" s="0" t="inlineStr">
+        <is>
+          <t>3648136,3648673,3648242,3648091,3648668,3648541,3648542,3648136,3648673,3648466,3648107,3648668,3648565,3648136,3648673,3648514,3648107,3648868,3649021,3648136,3648673,3648786,3648115,3648868,3648144,3648673,3648988,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" s="0" t="n">
+        <v>625</v>
+      </c>
+      <c r="F300" s="0" t="inlineStr">
+        <is>
+          <t>L14 W15/20; N=35; EHP=10147.845120; air:11x1,air:13x2,air:14x1,normal:17x4,normal:18x5,fast:30x1,fast:58x1,fast:64x1,elite:67x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x2,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" s="0" t="n">
+        <v>276</v>
+      </c>
+      <c r="C301" s="0" t="inlineStr">
+        <is>
+          <t>3650136,3650673,3650242,3650668,3650541,3650136,3650673,3650466,3650668,3650565,3650136,3650673,3650514,3650868,3650709,3650136,3650673,3650786,3650988,3650136,3650673,3650988,3650136,3650673,3650136,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650144,3650144,3650144</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" s="0" t="n">
+        <v>610</v>
+      </c>
+      <c r="F301" s="0" t="inlineStr">
+        <is>
+          <t>L14 W16/20; N=36; EHP=10554.000000; normal:17x7,normal:18x7,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x10,heavy:88x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" s="0" t="n">
+        <v>277</v>
+      </c>
+      <c r="C302" s="0" t="inlineStr">
+        <is>
+          <t>3652136,3652673,3652242,3652091,3652668,3652541,3652136,3652673,3652466,3652107,3652868,3652645,3652136,3652673,3652514,3652115,3652868,3652709,3652136,3652673,3652786,3652115,3652988,3652136,3652673,3652988,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" s="0" t="n">
+        <v>595</v>
+      </c>
+      <c r="F302" s="0" t="inlineStr">
+        <is>
+          <t>L14 W17/20; N=37; EHP=11614.951200; air:11x1,air:13x1,air:14x2,normal:17x5,normal:18x6,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:80x1,medium:83x1,swarm:84x10,heavy:88x1,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" s="0" t="n">
+        <v>278</v>
+      </c>
+      <c r="C303" s="0" t="inlineStr">
+        <is>
+          <t>3654136,3654673,3654242,3654091,3654668,3654645,3654136,3654673,3654466,3654107,3654668,3654693,3654136,3654673,3654514,3654107,3654868,3654709,3654136,3654673,3654786,3654115,3654868,3654136,3654673,3654988,3654136,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654144</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" s="0" t="n">
+        <v>580</v>
+      </c>
+      <c r="F303" s="0" t="inlineStr">
+        <is>
+          <t>L14 W18/20; N=38; EHP=13060.273200; air:11x1,air:13x2,air:14x1,normal:17x6,normal:18x6,fast:30x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,heavy:88x1,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" s="0" t="n">
+        <v>279</v>
+      </c>
+      <c r="C304" s="0" t="inlineStr">
+        <is>
+          <t>3656136,3656673,3656242,3656091,3656668,3656253,3656136,3656673,3656466,3656091,3656668,3656645,3656136,3656673,3656514,3656107,3656868,3656693,3656136,3656673,3656786,3656115,3656988,3656136,3656673,3656988,3656136,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656144,3656144</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" s="0" t="n">
+        <v>565</v>
+      </c>
+      <c r="F304" s="0" t="inlineStr">
+        <is>
+          <t>L14 W19/20; N=39; EHP=14623.689600; air:11x2,air:13x1,air:14x1,normal:17x6,normal:18x7,fast:30x1,heavy:31x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" s="0" t="n">
+        <v>280</v>
+      </c>
+      <c r="C305" s="0" t="inlineStr">
+        <is>
+          <t>3658136,3658673,3658242,3658091,3658668,3658253,3659055,3658136,3658673,3658466,3658107,3658668,3658325,3658136,3658673,3658514,3658115,3658868,3658693,3658136,3658673,3658786,3658115,3658868,3659021,3658136,3658673,3658988,3658144,3658673,3658988,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658673</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E305" s="0" t="n">
+        <v>550</v>
+      </c>
+      <c r="F305" s="0" t="inlineStr">
+        <is>
+          <t>L14 W20/20; N=40; EHP=20387.130000; air:11x1,air:13x1,air:14x2,normal:17x5,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x2,swarm:84x11,heavy:86x1,fast:98x1,medium:108x2,medium:123x2,heavy:127x1,boss:131x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" s="0" t="n">
+        <v>281</v>
+      </c>
+      <c r="C306" s="0" t="inlineStr">
+        <is>
+          <t>3660136,3660136,3660136,3660136,3660136,3660136,3660136,3660136,3660136,3660136,3660136,3660144,3660144,3660144,3660144,3660144,3660144,3660144,3660144,3660144,3660144,3660144</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" s="0" t="n">
+        <v>830</v>
+      </c>
+      <c r="F306" s="0" t="inlineStr">
+        <is>
+          <t>L15 W1/20; N=22; EHP=937.200000; normal:17x11,normal:18x11</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" s="0" t="n">
+        <v>282</v>
+      </c>
+      <c r="C307" s="0" t="inlineStr">
+        <is>
+          <t>3662136,3662136,3662136,3662136,3662136,3662136,3662136,3662136,3662136,3662136,3662136,3662136,3662144,3662144,3662144,3662144,3662144,3662144,3662144,3662144,3662144,3662144,3662144</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E307" s="0" t="n">
+        <v>815</v>
+      </c>
+      <c r="F307" s="0" t="inlineStr">
+        <is>
+          <t>L15 W2/20; N=23; EHP=1115.012400; normal:17x12,normal:18x11</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" s="0" t="n">
+        <v>283</v>
+      </c>
+      <c r="C308" s="0" t="inlineStr">
+        <is>
+          <t>3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664136,3664136,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E308" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="F308" s="0" t="inlineStr">
+        <is>
+          <t>L15 W3/20; N=24; EHP=1341.388800; normal:17x9,normal:18x9,swarm:84x6</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" s="0" t="n">
+        <v>284</v>
+      </c>
+      <c r="C309" s="0" t="inlineStr">
+        <is>
+          <t>3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666136,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" s="0" t="n">
+        <v>785</v>
+      </c>
+      <c r="F309" s="0" t="inlineStr">
+        <is>
+          <t>L15 W4/20; N=25; EHP=1620.930000; normal:17x9,normal:18x9,swarm:84x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" s="0" t="n">
+        <v>285</v>
+      </c>
+      <c r="C310" s="0" t="inlineStr">
+        <is>
+          <t>3668136,3668673,3668668,3668136,3668673,3668868,3668136,3668673,3668988,3668136,3668673,3668136,3668673,3668136,3668673,3668136,3668673,3668136,3668144,3668144,3668144,3668144,3668144,3668144,3668144,3668144</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" s="0" t="n">
+        <v>770</v>
+      </c>
+      <c r="F310" s="0" t="inlineStr">
+        <is>
+          <t>L15 W5/20; N=26; EHP=2193.225216; normal:17x8,normal:18x8,medium:83x1,swarm:84x7,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" s="0" t="n">
+        <v>286</v>
+      </c>
+      <c r="C311" s="0" t="inlineStr">
+        <is>
+          <t>3670136,3670673,3670466,3670091,3670668,3670136,3670673,3670514,3670107,3670668,3670136,3670673,3670786,3670868,3670136,3670673,3670988,3670136,3670673,3670136,3670673,3670144,3670673,3670144,3670144,3670144,3670144</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" s="0" t="n">
+        <v>755</v>
+      </c>
+      <c r="F311" s="0" t="inlineStr">
+        <is>
+          <t>L15 W6/20; N=27; EHP=2357.910000; air:11x1,air:13x1,normal:17x6,normal:18x5,fast:58x1,fast:64x1,medium:83x2,swarm:84x7,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" s="0" t="n">
+        <v>287</v>
+      </c>
+      <c r="C312" s="0" t="inlineStr">
+        <is>
+          <t>3672136,3672673,3672242,3672091,3672668,3672136,3672673,3672466,3672115,3672868,3672136,3672673,3672514,3672988,3672136,3672673,3672988,3672136,3672673,3672136,3672673,3672144,3672673,3672144,3672144,3672144,3672144,3672144</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E312" s="0" t="n">
+        <v>740</v>
+      </c>
+      <c r="F312" s="0" t="inlineStr">
+        <is>
+          <t>L15 W7/20; N=28; EHP=2824.550400; air:11x1,air:14x1,normal:17x6,normal:18x6,fast:30x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x7,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" s="0" t="n">
+        <v>288</v>
+      </c>
+      <c r="C313" s="0" t="inlineStr">
+        <is>
+          <t>3674136,3674673,3674242,3674107,3674668,3674136,3674673,3674514,3674115,3674868,3674136,3674673,3674786,3674868,3674136,3674673,3674988,3674136,3674673,3674136,3674673,3674144,3674673,3674144,3674673,3674144,3674144,3674144,3674144</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" s="0" t="n">
+        <v>725</v>
+      </c>
+      <c r="F313" s="0" t="inlineStr">
+        <is>
+          <t>L15 W8/20; N=29; EHP=3362.758800; air:13x1,air:14x1,normal:17x6,normal:18x6,fast:30x1,fast:64x1,medium:83x1,swarm:84x8,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" s="0" t="n">
+        <v>289</v>
+      </c>
+      <c r="C314" s="0" t="inlineStr">
+        <is>
+          <t>3676136,3676673,3676242,3676091,3676668,3676136,3676673,3676466,3676107,3676668,3676136,3676673,3676786,3676868,3676136,3676673,3676988,3676136,3676673,3676136,3676673,3676136,3676673,3676144,3676673,3676144,3676144,3676144,3676144,3676144</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" s="0" t="n">
+        <v>710</v>
+      </c>
+      <c r="F314" s="0" t="inlineStr">
+        <is>
+          <t>L15 W9/20; N=30; EHP=3977.136000; air:11x1,air:13x1,normal:17x7,normal:18x6,fast:30x1,fast:58x1,medium:83x2,swarm:84x8,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" s="0" t="n">
+        <v>290</v>
+      </c>
+      <c r="C315" s="0" t="inlineStr">
+        <is>
+          <t>3678136,3678673,3678466,3678091,3678668,3678136,3678673,3678514,3678115,3678868,3678136,3678673,3678786,3678988,3678136,3678673,3678988,3678136,3678673,3678136,3678673,3678136,3678673,3678144,3678673,3678144,3678144,3678144,3678144,3678144,3678144</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E315" s="0" t="n">
+        <v>695</v>
+      </c>
+      <c r="F315" s="0" t="inlineStr">
+        <is>
+          <t>L15 W10/20; N=31; EHP=5232.956736; air:11x1,air:14x1,normal:17x7,normal:18x7,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" s="0" t="n">
+        <v>291</v>
+      </c>
+      <c r="C316" s="0" t="inlineStr">
+        <is>
+          <t>3680136,3680673,3680242,3680668,3680253,3680136,3680673,3680466,3680868,3680325,3680136,3680673,3680514,3680868,3680693,3680136,3680673,3680988,3680136,3680673,3680136,3680673,3680136,3680673,3680144,3680673,3680144,3680144,3680144,3680144,3680144,3680144</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E316" s="0" t="n">
+        <v>680</v>
+      </c>
+      <c r="F316" s="0" t="inlineStr">
+        <is>
+          <t>L15 W11/20; N=32; EHP=5452.800000; normal:17x7,normal:18x7,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,heavy:86x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" s="0" t="n">
+        <v>292</v>
+      </c>
+      <c r="C317" s="0" t="inlineStr">
+        <is>
+          <t>3682136,3682673,3682242,3682091,3682668,3682253,3682136,3682673,3682514,3682107,3682668,3682325,3682136,3682673,3682786,3682115,3682868,3683021,3682136,3682673,3682988,3682136,3682673,3682136,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682144</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" s="0" t="n">
+        <v>665</v>
+      </c>
+      <c r="F317" s="0" t="inlineStr">
+        <is>
+          <t>L15 W12/20; N=33; EHP=6323.288400; air:11x1,air:13x1,air:14x1,normal:17x6,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:64x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x1,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" s="0" t="n">
+        <v>293</v>
+      </c>
+      <c r="C318" s="0" t="inlineStr">
+        <is>
+          <t>3684136,3684673,3684242,3684091,3684668,3684325,3684136,3684673,3684466,3684091,3684868,3684565,3684136,3684673,3684514,3684107,3684868,3685021,3684136,3684673,3684786,3684115,3684988,3684136,3684673,3684988,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" s="0" t="n">
+        <v>650</v>
+      </c>
+      <c r="F318" s="0" t="inlineStr">
+        <is>
+          <t>L15 W13/20; N=34; EHP=7288.348800; air:11x2,air:13x1,air:14x1,normal:17x5,normal:18x4,fast:30x1,heavy:40x1,fast:58x1,fast:64x1,heavy:70x1,medium:83x1,swarm:84x9,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" s="0" t="n">
+        <v>294</v>
+      </c>
+      <c r="C319" s="0" t="inlineStr">
+        <is>
+          <t>3686136,3686673,3686242,3686091,3686668,3686541,3686136,3686673,3686466,3686107,3686668,3686565,3686136,3686673,3686514,3686115,3686868,3687021,3686136,3686673,3686786,3686115,3686868,3686136,3686673,3686988,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E319" s="0" t="n">
+        <v>635</v>
+      </c>
+      <c r="F319" s="0" t="inlineStr">
+        <is>
+          <t>L15 W14/20; N=35; EHP=8352.582000; air:11x1,air:13x1,air:14x2,normal:17x5,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x2,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" s="0" t="n">
+        <v>295</v>
+      </c>
+      <c r="C320" s="0" t="inlineStr">
+        <is>
+          <t>3688136,3688673,3688242,3688091,3688668,3688541,3688542,3688136,3688673,3688466,3688107,3688668,3688565,3688136,3688673,3688514,3688107,3688868,3688709,3688136,3688673,3688786,3688115,3688988,3688136,3688673,3688988,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688673</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" s="0" t="n">
+        <v>620</v>
+      </c>
+      <c r="F320" s="0" t="inlineStr">
+        <is>
+          <t>L15 W15/20; N=36; EHP=10663.059456; air:11x1,air:13x2,air:14x1,normal:17x5,normal:18x4,fast:30x1,fast:58x1,fast:64x1,elite:67x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x10,heavy:88x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" s="0" t="n">
+        <v>296</v>
+      </c>
+      <c r="C321" s="0" t="inlineStr">
+        <is>
+          <t>3690136,3690673,3690242,3690668,3690541,3690136,3690673,3690466,3690868,3690645,3690136,3690673,3690514,3690868,3690709,3690136,3690673,3690786,3690988,3690136,3690673,3690988,3690136,3690673,3690136,3690673,3690136,3690673,3690144,3690673,3690144,3690673,3690144,3690144,3690144,3690144,3690144</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" s="0" t="n">
+        <v>605</v>
+      </c>
+      <c r="F321" s="0" t="inlineStr">
+        <is>
+          <t>L15 W16/20; N=37; EHP=11090.000000; normal:17x8,normal:18x7,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:80x1,medium:83x1,swarm:84x10,heavy:88x1,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" s="0" t="n">
+        <v>297</v>
+      </c>
+      <c r="C322" s="0" t="inlineStr">
+        <is>
+          <t>3692136,3692673,3692242,3692091,3692668,3692645,3692136,3692673,3692466,3692107,3692668,3692693,3692136,3692673,3692514,3692115,3692868,3692709,3692136,3692673,3692786,3692115,3692868,3692136,3692673,3692988,3692136,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692144</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E322" s="0" t="n">
+        <v>590</v>
+      </c>
+      <c r="F322" s="0" t="inlineStr">
+        <is>
+          <t>L15 W17/20; N=38; EHP=12186.326400; air:11x1,air:13x1,air:14x2,normal:17x6,normal:18x6,fast:30x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,heavy:88x1,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" s="0" t="n">
+        <v>298</v>
+      </c>
+      <c r="C323" s="0" t="inlineStr">
+        <is>
+          <t>3694136,3694673,3694242,3694091,3694668,3694253,3694136,3694673,3694466,3694107,3694668,3694645,3694136,3694673,3694514,3694107,3694868,3694693,3694136,3694673,3694786,3694115,3694988,3694136,3694673,3694988,3694136,3694673,3694136,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694144,3694144</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" s="0" t="n">
+        <v>575</v>
+      </c>
+      <c r="F323" s="0" t="inlineStr">
+        <is>
+          <t>L15 W18/20; N=39; EHP=13693.258800; air:11x1,air:13x2,air:14x1,normal:17x7,normal:18x6,fast:30x1,heavy:31x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" s="0" t="n">
+        <v>299</v>
+      </c>
+      <c r="C324" s="0" t="inlineStr">
+        <is>
+          <t>3696136,3696673,3696242,3696091,3696668,3696253,3696136,3696673,3696466,3696091,3696668,3696325,3696136,3696673,3696514,3696107,3696868,3696693,3696136,3696673,3696786,3696115,3696868,3697021,3696136,3696673,3696988,3696136,3696673,3696988,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" s="0" t="n">
+        <v>560</v>
+      </c>
+      <c r="F324" s="0" t="inlineStr">
+        <is>
+          <t>L15 W19/20; N=40; EHP=15322.368000; air:11x2,air:13x1,air:14x1,normal:17x6,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x2,swarm:84x11,heavy:86x1,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="C325" s="0" t="inlineStr">
+        <is>
+          <t>3698136,3698673,3698242,3698091,3698668,3698253,3699063,3698136,3698673,3698466,3698107,3698668,3698325,3698136,3698673,3698514,3698115,3698868,3698565,3698136,3698673,3698786,3698115,3698868,3699021,3698136,3698673,3698988,3698136,3698673,3698988,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E325" s="0" t="n">
+        <v>545</v>
+      </c>
+      <c r="F325" s="0" t="inlineStr">
+        <is>
+          <t>L15 W20/20; N=41; EHP=21347.818500; air:11x1,air:13x1,air:14x2,normal:17x6,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,heavy:70x1,medium:83x2,swarm:84x11,fast:98x1,medium:108x2,medium:123x2,heavy:127x1,boss:132x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" s="0" t="n">
+        <v>301</v>
+      </c>
+      <c r="C326" s="0" t="inlineStr">
+        <is>
+          <t>3700136,3700136,3700136,3700136,3700136,3700136,3700136,3700136,3700136,3700136,3700136,3700144,3700144,3700144,3700144,3700144,3700144,3700144,3700144,3700144,3700144,3700144,3700144</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E326" s="0" t="n">
+        <v>825</v>
+      </c>
+      <c r="F326" s="0" t="inlineStr">
+        <is>
+          <t>L16 W1/20; N=23; EHP=1000.500000; normal:17x11,normal:18x12</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" s="0" t="n">
+        <v>302</v>
+      </c>
+      <c r="C327" s="0" t="inlineStr">
+        <is>
+          <t>3702136,3702136,3702136,3702136,3702136,3702136,3702136,3702136,3702136,3702136,3702136,3702136,3702144,3702144,3702144,3702144,3702144,3702144,3702144,3702144,3702144,3702144,3702144,3702144</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" s="0" t="n">
+        <v>810</v>
+      </c>
+      <c r="F327" s="0" t="inlineStr">
+        <is>
+          <t>L16 W2/20; N=24; EHP=1188.072000; normal:17x12,normal:18x12</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" s="0" t="n">
+        <v>303</v>
+      </c>
+      <c r="C328" s="0" t="inlineStr">
+        <is>
+          <t>3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704136,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E328" s="0" t="n">
+        <v>795</v>
+      </c>
+      <c r="F328" s="0" t="inlineStr">
+        <is>
+          <t>L16 W3/20; N=25; EHP=1426.800000; normal:17x9,normal:18x9,swarm:84x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" s="0" t="n">
+        <v>304</v>
+      </c>
+      <c r="C329" s="0" t="inlineStr">
+        <is>
+          <t>3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706136,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E329" s="0" t="n">
+        <v>780</v>
+      </c>
+      <c r="F329" s="0" t="inlineStr">
+        <is>
+          <t>L16 W4/20; N=26; EHP=1721.382000; normal:17x9,normal:18x10,swarm:84x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" s="0" t="n">
+        <v>305</v>
+      </c>
+      <c r="C330" s="0" t="inlineStr">
+        <is>
+          <t>3708136,3708673,3708668,3708136,3708673,3708668,3708136,3708673,3708868,3708136,3708673,3708988,3708136,3708673,3708136,3708673,3708136,3708673,3708136,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144</t>
+        </is>
+      </c>
+      <c r="D330" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E330" s="0" t="n">
+        <v>765</v>
+      </c>
+      <c r="F330" s="0" t="inlineStr">
+        <is>
+          <t>L16 W5/20; N=27; EHP=2325.697920; normal:17x8,normal:18x8,medium:83x2,swarm:84x7,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" s="0" t="n">
+        <v>306</v>
+      </c>
+      <c r="C331" s="0" t="inlineStr">
+        <is>
+          <t>3710136,3710673,3710242,3710091,3710668,3710136,3710673,3710466,3710107,3710868,3710136,3710673,3710514,3710988,3710136,3710673,3710988,3710136,3710673,3710136,3710673,3710144,3710673,3710144,3710144,3710144,3710144,3710144</t>
+        </is>
+      </c>
+      <c r="D331" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E331" s="0" t="n">
+        <v>750</v>
+      </c>
+      <c r="F331" s="0" t="inlineStr">
+        <is>
+          <t>L16 W6/20; N=28; EHP=2496.900000; air:11x1,air:13x1,normal:17x6,normal:18x6,fast:30x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x7,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" s="0" t="n">
+        <v>307</v>
+      </c>
+      <c r="C332" s="0" t="inlineStr">
+        <is>
+          <t>3712136,3712673,3712242,3712091,3712668,3712136,3712673,3712514,3712115,3712868,3712136,3712673,3712786,3712868,3712136,3712673,3712988,3712136,3712673,3712136,3712673,3712144,3712673,3712144,3712673,3712144,3712144,3712144,3712144</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E332" s="0" t="n">
+        <v>735</v>
+      </c>
+      <c r="F332" s="0" t="inlineStr">
+        <is>
+          <t>L16 W7/20; N=29; EHP=2987.232000; air:11x1,air:14x1,normal:17x6,normal:18x6,fast:30x1,fast:64x1,medium:83x1,swarm:84x8,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" s="0" t="n">
+        <v>308</v>
+      </c>
+      <c r="C333" s="0" t="inlineStr">
+        <is>
+          <t>3714136,3714673,3714242,3714107,3714668,3714136,3714673,3714466,3714115,3714668,3714136,3714673,3714786,3714868,3714136,3714673,3714988,3714136,3714673,3714136,3714673,3714144,3714673,3714144,3714673,3714144,3714144,3714144,3714144,3714144</t>
+        </is>
+      </c>
+      <c r="D333" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E333" s="0" t="n">
+        <v>720</v>
+      </c>
+      <c r="F333" s="0" t="inlineStr">
+        <is>
+          <t>L16 W8/20; N=30; EHP=3552.210000; air:13x1,air:14x1,normal:17x6,normal:18x7,fast:30x1,fast:58x1,medium:83x2,swarm:84x8,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" s="0" t="n">
+        <v>309</v>
+      </c>
+      <c r="C334" s="0" t="inlineStr">
+        <is>
+          <t>3716136,3716673,3716466,3716091,3716668,3716136,3716673,3716514,3716107,3716868,3716136,3716673,3716786,3716988,3716136,3716673,3716988,3716136,3716673,3716136,3716673,3716136,3716673,3716144,3716673,3716144,3716144,3716144,3716144,3716144,3716144</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" s="0" t="n">
+        <v>705</v>
+      </c>
+      <c r="F334" s="0" t="inlineStr">
+        <is>
+          <t>L16 W9/20; N=31; EHP=4196.532000; air:11x1,air:13x1,normal:17x7,normal:18x7,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" s="0" t="n">
+        <v>310</v>
+      </c>
+      <c r="C335" s="0" t="inlineStr">
+        <is>
+          <t>3718136,3718673,3718242,3718091,3718668,3718136,3718673,3718466,3718115,3718868,3718136,3718673,3718514,3718868,3718136,3718673,3718988,3718136,3718673,3718136,3718673,3718136,3718673,3718144,3718673,3718144,3718144,3718144,3718144,3718144,3718144,3718144</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E335" s="0" t="n">
+        <v>690</v>
+      </c>
+      <c r="F335" s="0" t="inlineStr">
+        <is>
+          <t>L16 W10/20; N=32; EHP=5515.883520; air:11x1,air:14x1,normal:17x7,normal:18x8,fast:30x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" s="0" t="n">
+        <v>311</v>
+      </c>
+      <c r="C336" s="0" t="inlineStr">
+        <is>
+          <t>3720136,3720673,3720242,3720668,3720253,3720136,3720673,3720514,3720668,3720325,3720136,3720673,3720786,3720868,3721021,3720136,3720673,3720988,3720136,3720673,3720136,3720673,3720136,3720673,3720144,3720673,3720144,3720673,3720144,3720144,3720144,3720144,3720144</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E336" s="0" t="n">
+        <v>675</v>
+      </c>
+      <c r="F336" s="0" t="inlineStr">
+        <is>
+          <t>L16 W11/20; N=33; EHP=5742.000000; normal:17x7,normal:18x7,fast:30x1,heavy:31x1,heavy:40x1,fast:64x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x1,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" s="0" t="n">
+        <v>312</v>
+      </c>
+      <c r="C337" s="0" t="inlineStr">
+        <is>
+          <t>3722136,3722673,3722242,3722091,3722668,3722325,3722136,3722673,3722466,3722107,3722868,3722565,3722136,3722673,3722514,3722107,3722868,3723021,3722136,3722673,3722786,3722115,3722988,3722144,3722673,3722988,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" s="0" t="n">
+        <v>660</v>
+      </c>
+      <c r="F337" s="0" t="inlineStr">
+        <is>
+          <t>L16 W12/20; N=34; EHP=6652.542000; air:11x1,air:13x2,air:14x1,normal:17x4,normal:18x5,fast:30x1,heavy:40x1,fast:58x1,fast:64x1,heavy:70x1,medium:83x1,swarm:84x9,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" s="0" t="n">
+        <v>313</v>
+      </c>
+      <c r="C338" s="0" t="inlineStr">
+        <is>
+          <t>3724136,3724673,3724242,3724091,3724668,3724541,3724136,3724673,3724466,3724091,3724668,3724565,3724136,3724673,3724514,3724107,3724868,3725021,3724136,3724673,3724786,3724115,3724868,3724136,3724673,3724988,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" s="0" t="n">
+        <v>645</v>
+      </c>
+      <c r="F338" s="0" t="inlineStr">
+        <is>
+          <t>L16 W13/20; N=35; EHP=7661.220000; air:11x2,air:13x1,air:14x1,normal:17x5,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x2,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" s="0" t="n">
+        <v>314</v>
+      </c>
+      <c r="C339" s="0" t="inlineStr">
+        <is>
+          <t>3726136,3726673,3726242,3726091,3726668,3726541,3726136,3726673,3726466,3726107,3726668,3726565,3726136,3726673,3726514,3726115,3726868,3726709,3726136,3726673,3726786,3726115,3726988,3726136,3726673,3726988,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E339" s="0" t="n">
+        <v>630</v>
+      </c>
+      <c r="F339" s="0" t="inlineStr">
+        <is>
+          <t>L16 W14/20; N=36; EHP=8772.732000; air:11x1,air:13x1,air:14x2,normal:17x5,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x10,heavy:88x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" s="0" t="n">
+        <v>315</v>
+      </c>
+      <c r="C340" s="0" t="inlineStr">
+        <is>
+          <t>3728136,3728673,3728242,3728091,3728668,3728541,3728542,3728136,3728673,3728466,3728107,3728868,3728645,3728136,3728673,3728514,3728107,3728868,3728709,3728136,3728673,3728786,3728115,3728988,3728136,3728673,3728988,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E340" s="0" t="n">
+        <v>615</v>
+      </c>
+      <c r="F340" s="0" t="inlineStr">
+        <is>
+          <t>L16 W15/20; N=37; EHP=11190.789120; air:11x1,air:13x2,air:14x1,normal:17x5,normal:18x5,fast:30x1,fast:58x1,fast:64x1,elite:67x1,heavy:67x1,heavy:80x1,medium:83x1,swarm:84x10,heavy:88x1,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" s="0" t="n">
+        <v>316</v>
+      </c>
+      <c r="C341" s="0" t="inlineStr">
+        <is>
+          <t>3730136,3730673,3730242,3730668,3730645,3730136,3730673,3730466,3730668,3730693,3730136,3730673,3730514,3730868,3730709,3730136,3730673,3730786,3730868,3730136,3730673,3730988,3730136,3730673,3730136,3730673,3730136,3730673,3730144,3730673,3730144,3730673,3730144,3730144,3730144,3730144,3730144,3730144</t>
+        </is>
+      </c>
+      <c r="D341" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="F341" s="0" t="inlineStr">
+        <is>
+          <t>L16 W16/20; N=38; EHP=11639.000000; normal:17x8,normal:18x8,fast:30x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,heavy:88x1,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" s="0" t="n">
+        <v>317</v>
+      </c>
+      <c r="C342" s="0" t="inlineStr">
+        <is>
+          <t>3732136,3732673,3732242,3732091,3732668,3732253,3732136,3732673,3732466,3732107,3732668,3732645,3732136,3732673,3732514,3732115,3732868,3732693,3732136,3732673,3732786,3732115,3732988,3732136,3732673,3732988,3732136,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732144,3732144</t>
+        </is>
+      </c>
+      <c r="D342" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" s="0" t="n">
+        <v>585</v>
+      </c>
+      <c r="F342" s="0" t="inlineStr">
+        <is>
+          <t>L16 W17/20; N=39; EHP=12771.252000; air:11x1,air:13x1,air:14x2,normal:17x6,normal:18x7,fast:30x1,heavy:31x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" s="0" t="n">
+        <v>318</v>
+      </c>
+      <c r="C343" s="0" t="inlineStr">
+        <is>
+          <t>3734136,3734673,3734242,3734091,3734668,3734253,3734136,3734673,3734466,3734107,3734668,3734325,3734136,3734673,3734514,3734107,3734868,3734693,3734136,3734673,3734786,3734115,3734868,3735021,3734136,3734673,3734988,3734144,3734673,3734988,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673</t>
+        </is>
+      </c>
+      <c r="D343" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" s="0" t="n">
+        <v>570</v>
+      </c>
+      <c r="F343" s="0" t="inlineStr">
+        <is>
+          <t>L16 W18/20; N=40; EHP=14341.080000; air:11x1,air:13x2,air:14x1,normal:17x5,normal:18x6,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x2,swarm:84x11,heavy:86x1,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" s="0" t="n">
+        <v>319</v>
+      </c>
+      <c r="C344" s="0" t="inlineStr">
+        <is>
+          <t>3736136,3736673,3736242,3736091,3736668,3736253,3736136,3736673,3736466,3736091,3736668,3736325,3736136,3736673,3736514,3736107,3736868,3736565,3736136,3736673,3736786,3736115,3736868,3737021,3736136,3736673,3736988,3736136,3736673,3736988,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" s="0" t="n">
+        <v>555</v>
+      </c>
+      <c r="F344" s="0" t="inlineStr">
+        <is>
+          <t>L16 W19/20; N=41; EHP=16037.232000; air:11x2,air:13x1,air:14x1,normal:17x6,normal:18x6,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,heavy:70x1,medium:83x2,swarm:84x11,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" s="0" t="n">
+        <v>320</v>
+      </c>
+      <c r="C345" s="0" t="inlineStr">
+        <is>
+          <t>3738136,3738673,3738242,3738091,3738668,3738325,3739063,3738136,3738673,3738242,3738107,3738668,3738541,3738136,3738673,3738466,3738107,3738868,3738565,3738136,3738673,3738514,3738115,3738868,3739021,3738136,3738673,3738786,3738115,3738988,3738144,3738673,3738988,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738673</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" s="0" t="n">
+        <v>540</v>
+      </c>
+      <c r="F345" s="0" t="inlineStr">
+        <is>
+          <t>L16 W20/20; N=42; EHP=22330.507500; air:11x1,air:13x2,air:14x2,normal:17x5,normal:18x5,fast:30x2,heavy:40x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x11,fast:98x1,medium:108x2,medium:123x2,heavy:127x1,boss:132x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" s="0" t="n">
+        <v>321</v>
+      </c>
+      <c r="C346" s="0" t="inlineStr">
+        <is>
+          <t>3740136,3740136,3740136,3740136,3740136,3740136,3740136,3740136,3740136,3740136,3740136,3740136,3740144,3740144,3740144,3740144,3740144,3740144,3740144,3740144,3740144,3740144,3740144,3740144</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E346" s="0" t="n">
+        <v>820</v>
+      </c>
+      <c r="F346" s="0" t="inlineStr">
+        <is>
+          <t>L17 W1/20; N=24; EHP=1065.600000; normal:17x12,normal:18x12</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" s="0" t="n">
+        <v>322</v>
+      </c>
+      <c r="C347" s="0" t="inlineStr">
+        <is>
+          <t>3742136,3742136,3742136,3742136,3742136,3742136,3742136,3742136,3742136,3742136,3742136,3742136,3742136,3742144,3742144,3742144,3742144,3742144,3742144,3742144,3742144,3742144,3742144,3742144,3742144</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E347" s="0" t="n">
+        <v>805</v>
+      </c>
+      <c r="F347" s="0" t="inlineStr">
+        <is>
+          <t>L17 W2/20; N=25; EHP=1263.180000; normal:17x13,normal:18x12</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" s="0" t="n">
+        <v>323</v>
+      </c>
+      <c r="C348" s="0" t="inlineStr">
+        <is>
+          <t>3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744136,3744136,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E348" s="0" t="n">
+        <v>790</v>
+      </c>
+      <c r="F348" s="0" t="inlineStr">
+        <is>
+          <t>L17 W3/20; N=26; EHP=1514.572800; normal:17x10,normal:18x9,swarm:84x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" s="0" t="n">
+        <v>324</v>
+      </c>
+      <c r="C349" s="0" t="inlineStr">
+        <is>
+          <t>3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746136,3746136,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144</t>
+        </is>
+      </c>
+      <c r="D349" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E349" s="0" t="n">
+        <v>775</v>
+      </c>
+      <c r="F349" s="0" t="inlineStr">
+        <is>
+          <t>L17 W4/20; N=27; EHP=1824.573600; normal:17x10,normal:18x10,swarm:84x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" s="0" t="n">
+        <v>325</v>
+      </c>
+      <c r="C350" s="0" t="inlineStr">
+        <is>
+          <t>3748136,3748673,3748668,3748136,3748673,3748868,3748136,3748673,3748988,3748136,3748673,3748988,3748136,3748673,3748136,3748673,3748136,3748673,3748136,3748136,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144</t>
+        </is>
+      </c>
+      <c r="D350" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" s="0" t="n">
+        <v>760</v>
+      </c>
+      <c r="F350" s="0" t="inlineStr">
+        <is>
+          <t>L17 W5/20; N=28; EHP=2461.734912; normal:17x9,normal:18x8,medium:83x1,swarm:84x7,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" s="0" t="n">
+        <v>326</v>
+      </c>
+      <c r="C351" s="0" t="inlineStr">
+        <is>
+          <t>3750136,3750673,3750242,3750091,3750668,3750136,3750673,3750514,3750107,3750868,3750136,3750673,3750786,3750868,3750136,3750673,3750988,3750136,3750673,3750136,3750673,3750144,3750673,3750144,3750673,3750144,3750144,3750144,3750144</t>
+        </is>
+      </c>
+      <c r="D351" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" s="0" t="n">
+        <v>745</v>
+      </c>
+      <c r="F351" s="0" t="inlineStr">
+        <is>
+          <t>L17 W6/20; N=29; EHP=2639.580000; air:11x1,air:13x1,normal:17x6,normal:18x6,fast:30x1,fast:64x1,medium:83x1,swarm:84x8,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" s="0" t="n">
+        <v>327</v>
+      </c>
+      <c r="C352" s="0" t="inlineStr">
+        <is>
+          <t>3752136,3752673,3752242,3752091,3752668,3752136,3752673,3752466,3752115,3752668,3752136,3752673,3752786,3752868,3752136,3752673,3752988,3752136,3752673,3752136,3752673,3752136,3752673,3752144,3752673,3752144,3752144,3752144,3752144,3752144</t>
+        </is>
+      </c>
+      <c r="D352" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" s="0" t="n">
+        <v>730</v>
+      </c>
+      <c r="F352" s="0" t="inlineStr">
+        <is>
+          <t>L17 W7/20; N=30; EHP=3154.176000; air:11x1,air:14x1,normal:17x7,normal:18x6,fast:30x1,fast:58x1,medium:83x2,swarm:84x8,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" s="0" t="n">
+        <v>328</v>
+      </c>
+      <c r="C353" s="0" t="inlineStr">
+        <is>
+          <t>3754136,3754673,3754466,3754107,3754668,3754136,3754673,3754514,3754115,3754868,3754136,3754673,3754786,3754988,3754136,3754673,3754988,3754136,3754673,3754136,3754673,3754136,3754673,3754144,3754673,3754144,3754144,3754144,3754144,3754144,3754144</t>
+        </is>
+      </c>
+      <c r="D353" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E353" s="0" t="n">
+        <v>715</v>
+      </c>
+      <c r="F353" s="0" t="inlineStr">
+        <is>
+          <t>L17 W8/20; N=31; EHP=3746.560800; air:13x1,air:14x1,normal:17x7,normal:18x7,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" s="0" t="n">
+        <v>329</v>
+      </c>
+      <c r="C354" s="0" t="inlineStr">
+        <is>
+          <t>3756136,3756673,3756242,3756091,3756668,3756136,3756673,3756466,3756107,3756868,3756136,3756673,3756514,3756868,3756136,3756673,3756988,3756136,3756673,3756136,3756673,3756136,3756673,3756136,3756673,3756144,3756144,3756144,3756144,3756144,3756144,3756144</t>
+        </is>
+      </c>
+      <c r="D354" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E354" s="0" t="n">
+        <v>700</v>
+      </c>
+      <c r="F354" s="0" t="inlineStr">
+        <is>
+          <t>L17 W9/20; N=32; EHP=4421.529600; air:11x1,air:13x1,normal:17x8,normal:18x7,fast:30x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" s="0" t="n">
+        <v>330</v>
+      </c>
+      <c r="C355" s="0" t="inlineStr">
+        <is>
+          <t>3758136,3758673,3758242,3758091,3758668,3758136,3758673,3758514,3758115,3758668,3758136,3758673,3758786,3758868,3758136,3758673,3758988,3758136,3758673,3758136,3758673,3758136,3758673,3758136,3758673,3758144,3758673,3758144,3758144,3758144,3758144,3758144,3758144</t>
+        </is>
+      </c>
+      <c r="D355" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" s="0" t="n">
+        <v>685</v>
+      </c>
+      <c r="F355" s="0" t="inlineStr">
+        <is>
+          <t>L17 W10/20; N=33; EHP=5805.942912; air:11x1,air:14x1,normal:17x8,normal:18x7,fast:30x1,fast:64x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" s="0" t="n">
+        <v>331</v>
+      </c>
+      <c r="C356" s="0" t="inlineStr">
+        <is>
+          <t>3760136,3760673,3760242,3760668,3760325,3760136,3760673,3760466,3760868,3760565,3760136,3760673,3760514,3760868,3761021,3760136,3760673,3760786,3760988,3760136,3760673,3760988,3760136,3760673,3760136,3760673,3760144,3760673,3760144,3760673,3760144,3760144,3760144,3760144</t>
+        </is>
+      </c>
+      <c r="D356" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" s="0" t="n">
+        <v>670</v>
+      </c>
+      <c r="F356" s="0" t="inlineStr">
+        <is>
+          <t>L17 W11/20; N=34; EHP=6039.000000; normal:17x7,normal:18x6,fast:30x1,heavy:40x1,fast:58x1,fast:64x1,heavy:70x1,medium:83x1,swarm:84x9,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" s="0" t="n">
+        <v>332</v>
+      </c>
+      <c r="C357" s="0" t="inlineStr">
+        <is>
+          <t>3762136,3762673,3762242,3762091,3762668,3762541,3762136,3762673,3762466,3762107,3762668,3762565,3762136,3762673,3762514,3762107,3762868,3763021,3762136,3762673,3762786,3762115,3762868,3762136,3762673,3762988,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144</t>
+        </is>
+      </c>
+      <c r="D357" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" s="0" t="n">
+        <v>655</v>
+      </c>
+      <c r="F357" s="0" t="inlineStr">
+        <is>
+          <t>L17 W12/20; N=35; EHP=6989.892000; air:11x1,air:13x2,air:14x1,normal:17x5,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x2,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" s="0" t="n">
+        <v>333</v>
+      </c>
+      <c r="C358" s="0" t="inlineStr">
+        <is>
+          <t>3764136,3764673,3764242,3764091,3764668,3764541,3764136,3764673,3764466,3764091,3764668,3764565,3764136,3764673,3764514,3764107,3764868,3764709,3764136,3764673,3764786,3764115,3764988,3764136,3764673,3764988,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673</t>
+        </is>
+      </c>
+      <c r="D358" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E358" s="0" t="n">
+        <v>640</v>
+      </c>
+      <c r="F358" s="0" t="inlineStr">
+        <is>
+          <t>L17 W13/20; N=36; EHP=8043.148800; air:11x2,air:13x1,air:14x1,normal:17x5,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x10,heavy:88x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" s="0" t="n">
+        <v>334</v>
+      </c>
+      <c r="C359" s="0" t="inlineStr">
+        <is>
+          <t>3766136,3766673,3766242,3766091,3766668,3766541,3766136,3766673,3766466,3766107,3766868,3766645,3766136,3766673,3766514,3766115,3766868,3766709,3766136,3766673,3766786,3766115,3766988,3766136,3766673,3766988,3766136,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144</t>
+        </is>
+      </c>
+      <c r="D359" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E359" s="0" t="n">
+        <v>625</v>
+      </c>
+      <c r="F359" s="0" t="inlineStr">
+        <is>
+          <t>L17 W14/20; N=37; EHP=9202.965600; air:11x1,air:13x1,air:14x2,normal:17x6,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:80x1,medium:83x1,swarm:84x10,heavy:88x1,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" s="0" t="n">
+        <v>335</v>
+      </c>
+      <c r="C360" s="0" t="inlineStr">
+        <is>
+          <t>3768136,3768673,3768242,3768091,3768668,3768645,3768542,3768136,3768673,3768466,3768107,3768668,3768693,3768136,3768673,3768514,3768107,3768868,3768709,3768136,3768673,3768786,3768115,3768868,3768136,3768673,3768988,3768136,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144</t>
+        </is>
+      </c>
+      <c r="D360" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E360" s="0" t="n">
+        <v>610</v>
+      </c>
+      <c r="F360" s="0" t="inlineStr">
+        <is>
+          <t>L17 W15/20; N=38; EHP=11731.034112; air:11x1,air:13x2,air:14x1,normal:17x6,normal:18x5,fast:30x1,fast:58x1,fast:64x1,elite:67x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,heavy:88x1,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" s="0" t="n">
+        <v>336</v>
+      </c>
+      <c r="C361" s="0" t="inlineStr">
+        <is>
+          <t>3770136,3770673,3770242,3770668,3770253,3770136,3770673,3770466,3770668,3770645,3770136,3770673,3770514,3770868,3770693,3770136,3770673,3770786,3770988,3770136,3770673,3770988,3770136,3770673,3770136,3770673,3770136,3770673,3770136,3770673,3770144,3770673,3770144,3770144,3770144,3770144,3770144,3770144,3770144</t>
+        </is>
+      </c>
+      <c r="D361" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E361" s="0" t="n">
+        <v>595</v>
+      </c>
+      <c r="F361" s="0" t="inlineStr">
+        <is>
+          <t>L17 W16/20; N=39; EHP=12201.000000; normal:17x9,normal:18x8,fast:30x1,heavy:31x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" s="0" t="n">
+        <v>337</v>
+      </c>
+      <c r="C362" s="0" t="inlineStr">
+        <is>
+          <t>3772136,3772673,3772242,3772091,3772668,3772253,3772136,3772673,3772466,3772107,3772668,3772325,3772136,3772673,3772514,3772115,3772868,3772693,3772136,3772673,3772786,3772115,3772868,3773021,3772136,3772673,3772988,3772136,3772673,3772988,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673</t>
+        </is>
+      </c>
+      <c r="D362" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E362" s="0" t="n">
+        <v>580</v>
+      </c>
+      <c r="F362" s="0" t="inlineStr">
+        <is>
+          <t>L17 W17/20; N=40; EHP=13369.728000; air:11x1,air:13x1,air:14x2,normal:17x6,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x2,swarm:84x11,heavy:86x1,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="C363" s="0" t="inlineStr">
+        <is>
+          <t>3774136,3774673,3774242,3774091,3774668,3774253,3774136,3774673,3774466,3774107,3774668,3774325,3774136,3774673,3774514,3774107,3774868,3774565,3774136,3774673,3774786,3774115,3774868,3775021,3774136,3774673,3774988,3774136,3774673,3774988,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144</t>
+        </is>
+      </c>
+      <c r="D363" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E363" s="0" t="n">
+        <v>565</v>
+      </c>
+      <c r="F363" s="0" t="inlineStr">
+        <is>
+          <t>L17 W18/20; N=41; EHP=15003.736800; air:11x1,air:13x2,air:14x1,normal:17x6,normal:18x6,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,heavy:70x1,medium:83x2,swarm:84x11,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" s="0" t="n">
+        <v>339</v>
+      </c>
+      <c r="C364" s="0" t="inlineStr">
+        <is>
+          <t>3776136,3776673,3776242,3776091,3776668,3776325,3776136,3776673,3776242,3776091,3776668,3776541,3776136,3776673,3776466,3776107,3776868,3776565,3776136,3776673,3776514,3776115,3776868,3777021,3776136,3776673,3776786,3776115,3776988,3776136,3776673,3776988,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673</t>
+        </is>
+      </c>
+      <c r="D364" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E364" s="0" t="n">
+        <v>550</v>
+      </c>
+      <c r="F364" s="0" t="inlineStr">
+        <is>
+          <t>L17 W19/20; N=42; EHP=16768.281600; air:11x2,air:13x1,air:14x2,normal:17x6,normal:18x5,fast:30x2,heavy:40x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x11,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" s="0" t="n">
+        <v>340</v>
+      </c>
+      <c r="C365" s="0" t="inlineStr">
+        <is>
+          <t>3778136,3778673,3778242,3778091,3778668,3778541,3779063,3778136,3778673,3778466,3778107,3778668,3778565,3778136,3778673,3778514,3778107,3778868,3778709,3778136,3778673,3778786,3778115,3778868,3779021,3778136,3778673,3778786,3778115,3778988,3778144,3778673,3778988,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778673,3778673</t>
+        </is>
+      </c>
+      <c r="D365" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E365" s="0" t="n">
+        <v>535</v>
+      </c>
+      <c r="F365" s="0" t="inlineStr">
+        <is>
+          <t>L17 W20/20; N=43; EHP=23335.197000; air:11x1,air:13x2,air:14x2,normal:17x5,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x12,heavy:88x1,fast:98x2,medium:108x2,medium:123x2,heavy:127x1,boss:132x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" s="0" t="n">
+        <v>341</v>
+      </c>
+      <c r="C366" s="0" t="inlineStr">
+        <is>
+          <t>3780136,3780136,3780136,3780136,3780136,3780136,3780136,3780136,3780136,3780136,3780136,3780136,3780144,3780144,3780144,3780144,3780144,3780144,3780144,3780144,3780144,3780144,3780144,3780144,3780144</t>
+        </is>
+      </c>
+      <c r="D366" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" s="0" t="n">
+        <v>815</v>
+      </c>
+      <c r="F366" s="0" t="inlineStr">
+        <is>
+          <t>L18 W1/20; N=25; EHP=1132.500000; normal:17x12,normal:18x13</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" s="0" t="n">
+        <v>342</v>
+      </c>
+      <c r="C367" s="0" t="inlineStr">
+        <is>
+          <t>3782136,3782136,3782136,3782136,3782136,3782136,3782136,3782136,3782136,3782136,3782136,3782136,3782136,3782144,3782144,3782144,3782144,3782144,3782144,3782144,3782144,3782144,3782144,3782144,3782144,3782144</t>
+        </is>
+      </c>
+      <c r="D367" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E367" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="F367" s="0" t="inlineStr">
+        <is>
+          <t>L18 W2/20; N=26; EHP=1340.336400; normal:17x13,normal:18x13</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" s="0" t="n">
+        <v>343</v>
+      </c>
+      <c r="C368" s="0" t="inlineStr">
+        <is>
+          <t>3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784673,3784136,3784136,3784136,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144,3784144</t>
+        </is>
+      </c>
+      <c r="D368" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E368" s="0" t="n">
+        <v>785</v>
+      </c>
+      <c r="F368" s="0" t="inlineStr">
+        <is>
+          <t>L18 W3/20; N=27; EHP=1604.707200; normal:17x10,normal:18x10,swarm:84x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" s="0" t="n">
+        <v>344</v>
+      </c>
+      <c r="C369" s="0" t="inlineStr">
+        <is>
+          <t>3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786673,3786136,3786136,3786136,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144,3786144</t>
+        </is>
+      </c>
+      <c r="D369" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E369" s="0" t="n">
+        <v>770</v>
+      </c>
+      <c r="F369" s="0" t="inlineStr">
+        <is>
+          <t>L18 W4/20; N=28; EHP=1930.504800; normal:17x10,normal:18x11,swarm:84x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" s="0" t="n">
+        <v>345</v>
+      </c>
+      <c r="C370" s="0" t="inlineStr">
+        <is>
+          <t>3788136,3788673,3788668,3788136,3788673,3788868,3788136,3788673,3788868,3788136,3788673,3788988,3788136,3788673,3788136,3788673,3788136,3788673,3788136,3788673,3788144,3788144,3788144,3788144,3788144,3788144,3788144,3788144,3788144</t>
+        </is>
+      </c>
+      <c r="D370" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E370" s="0" t="n">
+        <v>755</v>
+      </c>
+      <c r="F370" s="0" t="inlineStr">
+        <is>
+          <t>L18 W5/20; N=29; EHP=2601.336192; normal:17x8,normal:18x9,medium:83x1,swarm:84x8,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" s="0" t="n">
+        <v>346</v>
+      </c>
+      <c r="C371" s="0" t="inlineStr">
+        <is>
+          <t>3790136,3790673,3790242,3790091,3790668,3790136,3790673,3790466,3790107,3790668,3790136,3790673,3790786,3790868,3790136,3790673,3790988,3790136,3790673,3790136,3790673,3790144,3790673,3790144,3790673,3790144,3790144,3790144,3790144,3790144</t>
+        </is>
+      </c>
+      <c r="D371" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E371" s="0" t="n">
+        <v>740</v>
+      </c>
+      <c r="F371" s="0" t="inlineStr">
+        <is>
+          <t>L18 W6/20; N=30; EHP=2785.950000; air:11x1,air:13x1,normal:17x6,normal:18x7,fast:30x1,fast:58x1,medium:83x2,swarm:84x8,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" s="0" t="n">
+        <v>347</v>
+      </c>
+      <c r="C372" s="0" t="inlineStr">
+        <is>
+          <t>3792136,3792673,3792466,3792091,3792668,3792136,3792673,3792514,3792115,3792868,3792136,3792673,3792786,3792988,3792136,3792673,3792988,3792136,3792673,3792136,3792673,3792136,3792673,3792144,3792673,3792144,3792144,3792144,3792144,3792144,3792144</t>
+        </is>
+      </c>
+      <c r="D372" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E372" s="0" t="n">
+        <v>725</v>
+      </c>
+      <c r="F372" s="0" t="inlineStr">
+        <is>
+          <t>L18 W7/20; N=31; EHP=3325.382400; air:11x1,air:14x1,normal:17x7,normal:18x7,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" s="0" t="n">
+        <v>348</v>
+      </c>
+      <c r="C373" s="0" t="inlineStr">
+        <is>
+          <t>3794136,3794673,3794242,3794107,3794668,3794136,3794673,3794466,3794115,3794868,3794136,3794673,3794514,3794868,3794136,3794673,3794988,3794136,3794673,3794136,3794673,3794136,3794673,3794144,3794673,3794144,3794144,3794144,3794144,3794144,3794144,3794144</t>
+        </is>
+      </c>
+      <c r="D373" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E373" s="0" t="n">
+        <v>710</v>
+      </c>
+      <c r="F373" s="0" t="inlineStr">
+        <is>
+          <t>L18 W8/20; N=32; EHP=3945.811200; air:13x1,air:14x1,normal:17x7,normal:18x8,fast:30x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" s="0" t="n">
+        <v>349</v>
+      </c>
+      <c r="C374" s="0" t="inlineStr">
+        <is>
+          <t>3796136,3796673,3796242,3796091,3796668,3796136,3796673,3796514,3796107,3796668,3796136,3796673,3796786,3796868,3796136,3796673,3796988,3796136,3796673,3796136,3796673,3796136,3796673,3796144,3796673,3796144,3796673,3796144,3796144,3796144,3796144,3796144,3796144</t>
+        </is>
+      </c>
+      <c r="D374" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E374" s="0" t="n">
+        <v>695</v>
+      </c>
+      <c r="F374" s="0" t="inlineStr">
+        <is>
+          <t>L18 W9/20; N=33; EHP=4652.128800; air:11x1,air:13x1,normal:17x7,normal:18x8,fast:30x1,fast:64x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" s="0" t="n">
+        <v>350</v>
+      </c>
+      <c r="C375" s="0" t="inlineStr">
+        <is>
+          <t>3798136,3798673,3798242,3798091,3798668,3798136,3798673,3798466,3798115,3798868,3798136,3798673,3798514,3798868,3798136,3798673,3798786,3798988,3798136,3798673,3798988,3798136,3798673,3798136,3798673,3798144,3798673,3798144,3798673,3798144,3798144,3798144,3798144,3798144</t>
+        </is>
+      </c>
+      <c r="D375" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E375" s="0" t="n">
+        <v>680</v>
+      </c>
+      <c r="F375" s="0" t="inlineStr">
+        <is>
+          <t>L18 W10/20; N=34; EHP=6103.134912; air:11x1,air:14x1,normal:17x7,normal:18x7,fast:30x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x9,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" s="0" t="n">
+        <v>351</v>
+      </c>
+      <c r="C376" s="0" t="inlineStr">
+        <is>
+          <t>3800136,3800673,3800242,3800668,3800541,3800136,3800673,3800466,3800668,3800565,3800136,3800673,3800514,3800868,3801021,3800136,3800673,3800786,3800868,3800136,3800673,3800988,3800136,3800673,3800136,3800673,3800144,3800673,3800144,3800673,3800144,3800144,3800144,3800144,3800144</t>
+        </is>
+      </c>
+      <c r="D376" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E376" s="0" t="n">
+        <v>665</v>
+      </c>
+      <c r="F376" s="0" t="inlineStr">
+        <is>
+          <t>L18 W11/20; N=35; EHP=6348.000000; normal:17x7,normal:18x7,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x2,medium:123x1,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" s="0" t="n">
+        <v>352</v>
+      </c>
+      <c r="C377" s="0" t="inlineStr">
+        <is>
+          <t>3802136,3802673,3802242,3802091,3802668,3802541,3802136,3802673,3802466,3802107,3802668,3802565,3802136,3802673,3802514,3802107,3802868,3802709,3802136,3802673,3802786,3802115,3802988,3802136,3802673,3802988,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673,3802144,3802673</t>
+        </is>
+      </c>
+      <c r="D377" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E377" s="0" t="n">
+        <v>650</v>
+      </c>
+      <c r="F377" s="0" t="inlineStr">
+        <is>
+          <t>L18 W12/20; N=36; EHP=7335.338400; air:11x1,air:13x2,air:14x1,normal:17x5,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x10,heavy:88x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" s="0" t="n">
+        <v>353</v>
+      </c>
+      <c r="C378" s="0" t="inlineStr">
+        <is>
+          <t>3804136,3804673,3804242,3804091,3804668,3804541,3804136,3804673,3804466,3804091,3804868,3804645,3804136,3804673,3804514,3804107,3804868,3804709,3804136,3804673,3804786,3804115,3804988,3804136,3804673,3804988,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144,3804673,3804144</t>
+        </is>
+      </c>
+      <c r="D378" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E378" s="0" t="n">
+        <v>635</v>
+      </c>
+      <c r="F378" s="0" t="inlineStr">
+        <is>
+          <t>L18 W13/20; N=37; EHP=8434.135200; air:11x2,air:13x1,air:14x1,normal:17x5,normal:18x6,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:80x1,medium:83x1,swarm:84x10,heavy:88x1,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" s="0" t="n">
+        <v>354</v>
+      </c>
+      <c r="C379" s="0" t="inlineStr">
+        <is>
+          <t>3806136,3806673,3806242,3806091,3806668,3806645,3806136,3806673,3806466,3806107,3806668,3806693,3806136,3806673,3806514,3806115,3806868,3806709,3806136,3806673,3806786,3806115,3806868,3806136,3806673,3806988,3806136,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806673,3806144,3806144</t>
+        </is>
+      </c>
+      <c r="D379" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" s="0" t="n">
+        <v>620</v>
+      </c>
+      <c r="F379" s="0" t="inlineStr">
+        <is>
+          <t>L18 W14/20; N=38; EHP=9643.282800; air:11x1,air:13x1,air:14x2,normal:17x6,normal:18x6,fast:30x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,heavy:88x1,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="C380" s="0" t="inlineStr">
+        <is>
+          <t>3808136,3808673,3808242,3808091,3808668,3808253,3808542,3808136,3808673,3808466,3808107,3808668,3808645,3808136,3808673,3808514,3808107,3808868,3808693,3808136,3808673,3808786,3808115,3808988,3808136,3808673,3808988,3808136,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808673,3808144,3808144</t>
+        </is>
+      </c>
+      <c r="D380" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E380" s="0" t="n">
+        <v>605</v>
+      </c>
+      <c r="F380" s="0" t="inlineStr">
+        <is>
+          <t>L18 W15/20; N=39; EHP=12283.794432; air:11x1,air:13x2,air:14x1,normal:17x6,normal:18x6,fast:30x1,heavy:31x1,fast:58x1,fast:64x1,elite:67x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" s="0" t="n">
+        <v>356</v>
+      </c>
+      <c r="C381" s="0" t="inlineStr">
+        <is>
+          <t>3810136,3810673,3810242,3810668,3810253,3810136,3810673,3810466,3810668,3810325,3810136,3810673,3810514,3810868,3810693,3810136,3810673,3810786,3810868,3811021,3810136,3810673,3810988,3810136,3810673,3810988,3810136,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810673,3810144,3810144,3810144,3810144</t>
+        </is>
+      </c>
+      <c r="D381" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E381" s="0" t="n">
+        <v>590</v>
+      </c>
+      <c r="F381" s="0" t="inlineStr">
+        <is>
+          <t>L18 W16/20; N=40; EHP=12776.000000; normal:17x7,normal:18x8,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x2,swarm:84x11,heavy:86x1,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" s="0" t="n">
+        <v>357</v>
+      </c>
+      <c r="C382" s="0" t="inlineStr">
+        <is>
+          <t>3812136,3812673,3812242,3812091,3812668,3812253,3812136,3812673,3812466,3812107,3812668,3812325,3812136,3812673,3812514,3812115,3812868,3812565,3812136,3812673,3812786,3812115,3812868,3813021,3812136,3812673,3812988,3812136,3812673,3812988,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144,3812673,3812144</t>
+        </is>
+      </c>
+      <c r="D382" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E382" s="0" t="n">
+        <v>575</v>
+      </c>
+      <c r="F382" s="0" t="inlineStr">
+        <is>
+          <t>L18 W17/20; N=41; EHP=13981.754400; air:11x1,air:13x1,air:14x2,normal:17x6,normal:18x6,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,heavy:70x1,medium:83x2,swarm:84x11,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" s="0" t="n">
+        <v>358</v>
+      </c>
+      <c r="C383" s="0" t="inlineStr">
+        <is>
+          <t>3814136,3814673,3814242,3814091,3814668,3814325,3814136,3814673,3814242,3814091,3814668,3814541,3814136,3814673,3814466,3814107,3814868,3814565,3814136,3814673,3814514,3814107,3814868,3815021,3814136,3814673,3814786,3814115,3814988,3814144,3814673,3814988,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673,3814144,3814673</t>
+        </is>
+      </c>
+      <c r="D383" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E383" s="0" t="n">
+        <v>560</v>
+      </c>
+      <c r="F383" s="0" t="inlineStr">
+        <is>
+          <t>L18 W18/20; N=42; EHP=15681.229200; air:11x2,air:13x2,air:14x1,normal:17x5,normal:18x6,fast:30x2,heavy:40x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x11,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" s="0" t="n">
+        <v>359</v>
+      </c>
+      <c r="C384" s="0" t="inlineStr">
+        <is>
+          <t>3816136,3816673,3816242,3816091,3816668,3816541,3816136,3816673,3816466,3816091,3816668,3816565,3816136,3816673,3816514,3816107,3816868,3816709,3816136,3816673,3816786,3816115,3816868,3817021,3816136,3816673,3816786,3816115,3816988,3816144,3816673,3816988,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816144,3816673,3816673</t>
+        </is>
+      </c>
+      <c r="D384" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E384" s="0" t="n">
+        <v>545</v>
+      </c>
+      <c r="F384" s="0" t="inlineStr">
+        <is>
+          <t>L18 W19/20; N=43; EHP=17515.516800; air:11x2,air:13x1,air:14x2,normal:17x5,normal:18x6,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x12,heavy:88x1,fast:98x2,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" s="0" t="n">
+        <v>360</v>
+      </c>
+      <c r="C385" s="0" t="inlineStr">
+        <is>
+          <t>3818136,3818673,3818242,3818091,3818668,3818541,3819063,3818136,3818673,3818466,3818107,3818668,3818565,3818136,3818673,3818466,3818107,3818868,3818645,3818136,3818673,3818514,3818115,3818868,3818709,3818136,3818673,3818786,3818115,3818988,3818144,3818673,3818988,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818144,3818673,3818673</t>
+        </is>
+      </c>
+      <c r="D385" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E385" s="0" t="n">
+        <v>530</v>
+      </c>
+      <c r="F385" s="0" t="inlineStr">
+        <is>
+          <t>L18 W20/20; N=44; EHP=24361.887000; air:11x1,air:13x2,air:14x2,normal:17x5,normal:18x6,fast:30x1,fast:58x2,fast:64x1,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x2,swarm:84x12,heavy:88x1,fast:98x1,medium:108x2,medium:123x2,boss:132x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" s="0" t="n">
+        <v>361</v>
+      </c>
+      <c r="C386" s="0" t="inlineStr">
+        <is>
+          <t>3820136,3820136,3820136,3820136,3820136,3820136,3820136,3820136,3820136,3820136,3820136,3820136,3820136,3820144,3820144,3820144,3820144,3820144,3820144,3820144,3820144,3820144,3820144,3820144,3820144,3820144</t>
+        </is>
+      </c>
+      <c r="D386" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E386" s="0" t="n">
+        <v>810</v>
+      </c>
+      <c r="F386" s="0" t="inlineStr">
+        <is>
+          <t>L19 W1/20; N=26; EHP=1201.200000; normal:17x13,normal:18x13</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" s="0" t="n">
+        <v>362</v>
+      </c>
+      <c r="C387" s="0" t="inlineStr">
+        <is>
+          <t>3822136,3822136,3822136,3822136,3822136,3822136,3822136,3822136,3822136,3822136,3822136,3822136,3822136,3822136,3822144,3822144,3822144,3822144,3822144,3822144,3822144,3822144,3822144,3822144,3822144,3822144,3822144</t>
+        </is>
+      </c>
+      <c r="D387" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E387" s="0" t="n">
+        <v>795</v>
+      </c>
+      <c r="F387" s="0" t="inlineStr">
+        <is>
+          <t>L19 W2/20; N=27; EHP=1419.541200; normal:17x14,normal:18x13</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" s="0" t="n">
+        <v>363</v>
+      </c>
+      <c r="C388" s="0" t="inlineStr">
+        <is>
+          <t>3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824136,3824136,3824136,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144</t>
+        </is>
+      </c>
+      <c r="D388" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E388" s="0" t="n">
+        <v>780</v>
+      </c>
+      <c r="F388" s="0" t="inlineStr">
+        <is>
+          <t>L19 W3/20; N=28; EHP=1697.203200; normal:17x11,normal:18x10,swarm:84x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" s="0" t="n">
+        <v>364</v>
+      </c>
+      <c r="C389" s="0" t="inlineStr">
+        <is>
+          <t>3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826136,3826136,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144</t>
+        </is>
+      </c>
+      <c r="D389" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E389" s="0" t="n">
+        <v>765</v>
+      </c>
+      <c r="F389" s="0" t="inlineStr">
+        <is>
+          <t>L19 W4/20; N=29; EHP=2039.175600; normal:17x11,normal:18x10,swarm:84x8</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" s="0" t="n">
+        <v>365</v>
+      </c>
+      <c r="C390" s="0" t="inlineStr">
+        <is>
+          <t>3828136,3828673,3828668,3828136,3828673,3828668,3828136,3828673,3828868,3828136,3828673,3828988,3828136,3828673,3828136,3828673,3828136,3828673,3828136,3828673,3828136,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144</t>
+        </is>
+      </c>
+      <c r="D390" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E390" s="0" t="n">
+        <v>750</v>
+      </c>
+      <c r="F390" s="0" t="inlineStr">
+        <is>
+          <t>L19 W5/20; N=30; EHP=2744.501760; normal:17x9,normal:18x9,medium:83x2,swarm:84x8,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" s="0" t="n">
+        <v>366</v>
+      </c>
+      <c r="C391" s="0" t="inlineStr">
+        <is>
+          <t>3830136,3830673,3830466,3830091,3830668,3830136,3830673,3830514,3830107,3830868,3830136,3830673,3830786,3830988,3830136,3830673,3830988,3830136,3830673,3830136,3830673,3830136,3830673,3830144,3830673,3830144,3830144,3830144,3830144,3830144,3830144</t>
+        </is>
+      </c>
+      <c r="D391" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E391" s="0" t="n">
+        <v>735</v>
+      </c>
+      <c r="F391" s="0" t="inlineStr">
+        <is>
+          <t>L19 W6/20; N=31; EHP=2936.010000; air:11x1,air:13x1,normal:17x7,normal:18x7,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" s="0" t="n">
+        <v>367</v>
+      </c>
+      <c r="C392" s="0" t="inlineStr">
+        <is>
+          <t>3832136,3832673,3832242,3832091,3832668,3832136,3832673,3832466,3832115,3832868,3832136,3832673,3832514,3832868,3832136,3832673,3832988,3832136,3832673,3832136,3832673,3832136,3832673,3832136,3832673,3832144,3832144,3832144,3832144,3832144,3832144,3832144</t>
+        </is>
+      </c>
+      <c r="D392" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E392" s="0" t="n">
+        <v>720</v>
+      </c>
+      <c r="F392" s="0" t="inlineStr">
+        <is>
+          <t>L19 W7/20; N=32; EHP=3500.851200; air:11x1,air:14x1,normal:17x8,normal:18x7,fast:30x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" s="0" t="n">
+        <v>368</v>
+      </c>
+      <c r="C393" s="0" t="inlineStr">
+        <is>
+          <t>3834136,3834673,3834242,3834107,3834668,3834136,3834673,3834514,3834115,3834668,3834136,3834673,3834786,3834868,3834136,3834673,3834988,3834136,3834673,3834136,3834673,3834136,3834673,3834136,3834673,3834144,3834673,3834144,3834144,3834144,3834144,3834144,3834144</t>
+        </is>
+      </c>
+      <c r="D393" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E393" s="0" t="n">
+        <v>705</v>
+      </c>
+      <c r="F393" s="0" t="inlineStr">
+        <is>
+          <t>L19 W8/20; N=33; EHP=4149.961200; air:13x1,air:14x1,normal:17x8,normal:18x7,fast:30x1,fast:64x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" s="0" t="n">
+        <v>369</v>
+      </c>
+      <c r="C394" s="0" t="inlineStr">
+        <is>
+          <t>3836136,3836673,3836242,3836091,3836668,3836136,3836673,3836466,3836107,3836868,3836136,3836673,3836514,3836868,3836136,3836673,3836786,3836988,3836136,3836673,3836988,3836136,3836673,3836136,3836673,3836144,3836673,3836144,3836673,3836144,3836144,3836144,3836144,3836144</t>
+        </is>
+      </c>
+      <c r="D394" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E394" s="0" t="n">
+        <v>690</v>
+      </c>
+      <c r="F394" s="0" t="inlineStr">
+        <is>
+          <t>L19 W9/20; N=34; EHP=4888.329600; air:11x1,air:13x1,normal:17x7,normal:18x7,fast:30x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x9,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" s="0" t="n">
+        <v>370</v>
+      </c>
+      <c r="C395" s="0" t="inlineStr">
+        <is>
+          <t>3838136,3838673,3838242,3838091,3838668,3838136,3838673,3838466,3838115,3838668,3838136,3838673,3838514,3838868,3838136,3838673,3838786,3838868,3838136,3838673,3838988,3838136,3838673,3838136,3838673,3838136,3838673,3838144,3838673,3838144,3838144,3838144,3838144,3838144,3838144</t>
+        </is>
+      </c>
+      <c r="D395" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E395" s="0" t="n">
+        <v>675</v>
+      </c>
+      <c r="F395" s="0" t="inlineStr">
+        <is>
+          <t>L19 W10/20; N=35; EHP=6407.459520; air:11x1,air:14x1,normal:17x8,normal:18x7,fast:30x1,fast:58x1,fast:64x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" s="0" t="n">
+        <v>371</v>
+      </c>
+      <c r="C396" s="0" t="inlineStr">
+        <is>
+          <t>3840136,3840673,3840242,3840668,3840541,3840136,3840673,3840466,3840668,3840565,3840136,3840673,3840514,3840868,3840709,3840136,3840673,3840786,3840988,3840136,3840673,3840988,3840136,3840673,3840136,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840144,3840144,3840144</t>
+        </is>
+      </c>
+      <c r="D396" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E396" s="0" t="n">
+        <v>660</v>
+      </c>
+      <c r="F396" s="0" t="inlineStr">
+        <is>
+          <t>L19 W11/20; N=36; EHP=6664.000000; normal:17x7,normal:18x7,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x10,heavy:88x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" s="0" t="n">
+        <v>372</v>
+      </c>
+      <c r="C397" s="0" t="inlineStr">
+        <is>
+          <t>3842136,3842673,3842242,3842091,3842668,3842541,3842136,3842673,3842466,3842107,3842868,3842645,3842136,3842673,3842514,3842107,3842868,3842709,3842136,3842673,3842786,3842115,3842988,3842136,3842673,3842988,3842136,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144</t>
+        </is>
+      </c>
+      <c r="D397" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E397" s="0" t="n">
+        <v>645</v>
+      </c>
+      <c r="F397" s="0" t="inlineStr">
+        <is>
+          <t>L19 W12/20; N=37; EHP=7688.881200; air:11x1,air:13x2,air:14x1,normal:17x6,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:80x1,medium:83x1,swarm:84x10,heavy:88x1,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" s="0" t="n">
+        <v>373</v>
+      </c>
+      <c r="C398" s="0" t="inlineStr">
+        <is>
+          <t>3844136,3844673,3844242,3844091,3844668,3844645,3844136,3844673,3844466,3844091,3844668,3844693,3844136,3844673,3844514,3844107,3844868,3844709,3844136,3844673,3844786,3844115,3844868,3844136,3844673,3844988,3844136,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844144</t>
+        </is>
+      </c>
+      <c r="D398" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E398" s="0" t="n">
+        <v>630</v>
+      </c>
+      <c r="F398" s="0" t="inlineStr">
+        <is>
+          <t>L19 W13/20; N=38; EHP=8834.179200; air:11x2,air:13x1,air:14x1,normal:17x6,normal:18x6,fast:30x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,heavy:88x1,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" s="0" t="n">
+        <v>374</v>
+      </c>
+      <c r="C399" s="0" t="inlineStr">
+        <is>
+          <t>3846136,3846673,3846242,3846091,3846668,3846253,3846136,3846673,3846466,3846107,3846668,3846645,3846136,3846673,3846514,3846115,3846868,3846693,3846136,3846673,3846786,3846115,3846988,3846136,3846673,3846988,3846136,3846673,3846136,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846144,3846144</t>
+        </is>
+      </c>
+      <c r="D399" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E399" s="0" t="n">
+        <v>615</v>
+      </c>
+      <c r="F399" s="0" t="inlineStr">
+        <is>
+          <t>L19 W14/20; N=39; EHP=10093.683600; air:11x1,air:13x1,air:14x2,normal:17x7,normal:18x6,fast:30x1,heavy:31x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" s="0" t="n">
+        <v>375</v>
+      </c>
+      <c r="C400" s="0" t="inlineStr">
+        <is>
+          <t>3848136,3848673,3848242,3848091,3848668,3848253,3848542,3848136,3848673,3848466,3848107,3848668,3848325,3848136,3848673,3848514,3848107,3848868,3848693,3848136,3848673,3848786,3848115,3848868,3849021,3848136,3848673,3848988,3848144,3848673,3848988,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848673</t>
+        </is>
+      </c>
+      <c r="D400" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E400" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="F400" s="0" t="inlineStr">
+        <is>
+          <t>L19 W15/20; N=40; EHP=12849.070080; air:11x1,air:13x2,air:14x1,normal:17x5,normal:18x5,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,elite:67x1,medium:83x2,swarm:84x11,heavy:86x1,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" s="0" t="n">
+        <v>376</v>
+      </c>
+      <c r="C401" s="0" t="inlineStr">
+        <is>
+          <t>3850136,3850673,3850242,3850668,3850253,3850136,3850673,3850466,3850668,3850325,3850136,3850673,3850514,3850868,3850565,3850136,3850673,3850786,3850868,3851021,3850136,3850673,3850988,3850136,3850673,3850988,3850136,3850673,3850136,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850144,3850144,3850144,3850144</t>
+        </is>
+      </c>
+      <c r="D401" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E401" s="0" t="n">
+        <v>585</v>
+      </c>
+      <c r="F401" s="0" t="inlineStr">
+        <is>
+          <t>L19 W16/20; N=41; EHP=13364.000000; normal:17x8,normal:18x8,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,heavy:70x1,medium:83x2,swarm:84x11,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" s="0" t="n">
+        <v>377</v>
+      </c>
+      <c r="C402" s="0" t="inlineStr">
+        <is>
+          <t>3852136,3852673,3852242,3852091,3852668,3852325,3852136,3852673,3852242,3852107,3852668,3852541,3852136,3852673,3852466,3852107,3852868,3852565,3852136,3852673,3852514,3852115,3852868,3853021,3852136,3852673,3852786,3852115,3852988,3852136,3852673,3852988,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673</t>
+        </is>
+      </c>
+      <c r="D402" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E402" s="0" t="n">
+        <v>570</v>
+      </c>
+      <c r="F402" s="0" t="inlineStr">
+        <is>
+          <t>L19 W17/20; N=42; EHP=14607.331200; air:11x1,air:13x2,air:14x2,normal:17x6,normal:18x5,fast:30x2,heavy:40x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x11,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" s="0" t="n">
+        <v>378</v>
+      </c>
+      <c r="C403" s="0" t="inlineStr">
+        <is>
+          <t>3854136,3854673,3854242,3854091,3854668,3854541,3854136,3854673,3854466,3854091,3854668,3854565,3854136,3854673,3854514,3854107,3854868,3854709,3854136,3854673,3854786,3854107,3854868,3855021,3854136,3854673,3854786,3854115,3854988,3854136,3854673,3854988,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854673</t>
+        </is>
+      </c>
+      <c r="D403" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E403" s="0" t="n">
+        <v>555</v>
+      </c>
+      <c r="F403" s="0" t="inlineStr">
+        <is>
+          <t>L19 W18/20; N=43; EHP=16373.557200; air:11x2,air:13x2,air:14x1,normal:17x6,normal:18x5,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x12,heavy:88x1,fast:98x2,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" s="0" t="n">
+        <v>379</v>
+      </c>
+      <c r="C404" s="0" t="inlineStr">
+        <is>
+          <t>3856136,3856673,3856242,3856091,3856668,3856541,3856136,3856673,3856466,3856091,3856668,3856565,3856136,3856673,3856466,3856107,3856868,3856645,3856136,3856673,3856514,3856115,3856868,3856709,3856136,3856673,3856786,3856115,3856988,3856136,3856673,3856988,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673</t>
+        </is>
+      </c>
+      <c r="D404" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E404" s="0" t="n">
+        <v>540</v>
+      </c>
+      <c r="F404" s="0" t="inlineStr">
+        <is>
+          <t>L19 W19/20; N=44; EHP=18278.937600; air:11x2,air:13x1,air:14x2,normal:17x6,normal:18x6,fast:30x1,fast:58x2,fast:64x1,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x2,swarm:84x12,heavy:88x1,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" s="0" t="n">
+        <v>380</v>
+      </c>
+      <c r="C405" s="0" t="inlineStr">
+        <is>
+          <t>3858136,3858673,3858242,3858091,3858668,3858541,3859063,3858136,3858673,3858466,3858107,3858668,3858645,3858136,3858673,3858514,3858107,3858868,3858693,3858136,3858673,3858514,3858115,3858868,3858709,3858136,3858673,3858786,3858115,3858988,3858136,3858673,3858988,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673</t>
+        </is>
+      </c>
+      <c r="D405" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E405" s="0" t="n">
+        <v>525</v>
+      </c>
+      <c r="F405" s="0" t="inlineStr">
+        <is>
+          <t>L19 W20/20; N=45; EHP=25410.577500; air:11x1,air:13x2,air:14x2,normal:17x6,normal:18x6,fast:30x1,fast:58x1,fast:64x2,heavy:67x1,heavy:80x1,medium:83x2,swarm:84x12,heavy:86x1,heavy:88x1,fast:98x1,medium:108x2,medium:123x2,boss:132x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" s="0" t="n">
+        <v>381</v>
+      </c>
+      <c r="C406" s="0" t="inlineStr">
+        <is>
+          <t>3860136,3860136,3860136,3860136,3860136,3860136,3860136,3860136,3860136,3860136,3860136,3860136,3860136,3860144,3860144,3860144,3860144,3860144,3860144,3860144,3860144,3860144,3860144,3860144,3860144,3860144,3860144</t>
+        </is>
+      </c>
+      <c r="D406" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E406" s="0" t="n">
+        <v>805</v>
+      </c>
+      <c r="F406" s="0" t="inlineStr">
+        <is>
+          <t>L20 W1/20; N=27; EHP=1271.700000; normal:17x13,normal:18x14</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" s="0" t="n">
+        <v>382</v>
+      </c>
+      <c r="C407" s="0" t="inlineStr">
+        <is>
+          <t>3862136,3862136,3862136,3862136,3862136,3862136,3862136,3862136,3862136,3862136,3862136,3862136,3862136,3862136,3862144,3862144,3862144,3862144,3862144,3862144,3862144,3862144,3862144,3862144,3862144,3862144,3862144,3862144</t>
+        </is>
+      </c>
+      <c r="D407" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E407" s="0" t="n">
+        <v>790</v>
+      </c>
+      <c r="F407" s="0" t="inlineStr">
+        <is>
+          <t>L20 W2/20; N=28; EHP=1500.794400; normal:17x14,normal:18x14</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" s="0" t="n">
+        <v>383</v>
+      </c>
+      <c r="C408" s="0" t="inlineStr">
+        <is>
+          <t>3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864136,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144</t>
+        </is>
+      </c>
+      <c r="D408" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E408" s="0" t="n">
+        <v>775</v>
+      </c>
+      <c r="F408" s="0" t="inlineStr">
+        <is>
+          <t>L20 W3/20; N=29; EHP=1792.060800; normal:17x10,normal:18x11,swarm:84x8</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" s="0" t="n">
+        <v>384</v>
+      </c>
+      <c r="C409" s="0" t="inlineStr">
+        <is>
+          <t>3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866136,3866136,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144</t>
+        </is>
+      </c>
+      <c r="D409" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E409" s="0" t="n">
+        <v>760</v>
+      </c>
+      <c r="F409" s="0" t="inlineStr">
+        <is>
+          <t>L20 W4/20; N=30; EHP=2150.586000; normal:17x11,normal:18x11,swarm:84x8</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" s="0" t="n">
+        <v>385</v>
+      </c>
+      <c r="C410" s="0" t="inlineStr">
+        <is>
+          <t>3868136,3868673,3868668,3868136,3868673,3868868,3868136,3868673,3868988,3868136,3868673,3868988,3868136,3868673,3868136,3868673,3868136,3868673,3868136,3868673,3868136,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144</t>
+        </is>
+      </c>
+      <c r="D410" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E410" s="0" t="n">
+        <v>745</v>
+      </c>
+      <c r="F410" s="0" t="inlineStr">
+        <is>
+          <t>L20 W5/20; N=31; EHP=2891.231616; normal:17x9,normal:18x10,medium:83x1,swarm:84x8,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" s="0" t="n">
+        <v>386</v>
+      </c>
+      <c r="C411" s="0" t="inlineStr">
+        <is>
+          <t>3870136,3870673,3870242,3870091,3870668,3870136,3870673,3870466,3870107,3870868,3870136,3870673,3870514,3870868,3870136,3870673,3870988,3870136,3870673,3870136,3870673,3870136,3870673,3870144,3870673,3870144,3870144,3870144,3870144,3870144,3870144,3870144</t>
+        </is>
+      </c>
+      <c r="D411" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E411" s="0" t="n">
+        <v>730</v>
+      </c>
+      <c r="F411" s="0" t="inlineStr">
+        <is>
+          <t>L20 W6/20; N=32; EHP=3089.760000; air:11x1,air:13x1,normal:17x7,normal:18x8,fast:30x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x8,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" s="0" t="n">
+        <v>387</v>
+      </c>
+      <c r="C412" s="0" t="inlineStr">
+        <is>
+          <t>3872136,3872673,3872242,3872091,3872668,3872136,3872673,3872514,3872115,3872668,3872136,3872673,3872786,3872868,3872136,3872673,3872988,3872136,3872673,3872136,3872673,3872136,3872673,3872144,3872673,3872144,3872673,3872144,3872144,3872144,3872144,3872144,3872144</t>
+        </is>
+      </c>
+      <c r="D412" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E412" s="0" t="n">
+        <v>715</v>
+      </c>
+      <c r="F412" s="0" t="inlineStr">
+        <is>
+          <t>L20 W7/20; N=33; EHP=3680.582400; air:11x1,air:14x1,normal:17x7,normal:18x8,fast:30x1,fast:64x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x1,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" s="0" t="n">
+        <v>388</v>
+      </c>
+      <c r="C413" s="0" t="inlineStr">
+        <is>
+          <t>3874136,3874673,3874242,3874107,3874668,3874136,3874673,3874466,3874115,3874868,3874136,3874673,3874514,3874868,3874136,3874673,3874786,3874988,3874136,3874673,3874988,3874136,3874673,3874136,3874673,3874144,3874673,3874144,3874673,3874144,3874144,3874144,3874144,3874144</t>
+        </is>
+      </c>
+      <c r="D413" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E413" s="0" t="n">
+        <v>700</v>
+      </c>
+      <c r="F413" s="0" t="inlineStr">
+        <is>
+          <t>L20 W8/20; N=34; EHP=4359.010800; air:13x1,air:14x1,normal:17x7,normal:18x7,fast:30x1,fast:58x1,fast:64x1,medium:83x1,swarm:84x9,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" s="0" t="n">
+        <v>389</v>
+      </c>
+      <c r="C414" s="0" t="inlineStr">
+        <is>
+          <t>3876136,3876673,3876242,3876091,3876668,3876136,3876673,3876466,3876107,3876668,3876136,3876673,3876514,3876868,3876136,3876673,3876786,3876868,3876136,3876673,3876988,3876136,3876673,3876136,3876673,3876144,3876673,3876144,3876673,3876144,3876144,3876144,3876144,3876144,3876144</t>
+        </is>
+      </c>
+      <c r="D414" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E414" s="0" t="n">
+        <v>685</v>
+      </c>
+      <c r="F414" s="0" t="inlineStr">
+        <is>
+          <t>L20 W9/20; N=35; EHP=5130.132000; air:11x1,air:13x1,normal:17x7,normal:18x8,fast:30x1,fast:58x1,fast:64x1,medium:83x2,swarm:84x9,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" s="0" t="n">
+        <v>390</v>
+      </c>
+      <c r="C415" s="0" t="inlineStr">
+        <is>
+          <t>3878136,3878673,3878242,3878091,3878668,3878136,3878673,3878466,3878115,3878668,3878136,3878673,3878514,3878868,3878136,3878673,3878786,3878988,3878136,3878673,3878988,3878136,3878673,3878136,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878144,3878144,3878144,3878144</t>
+        </is>
+      </c>
+      <c r="D415" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E415" s="0" t="n">
+        <v>670</v>
+      </c>
+      <c r="F415" s="0" t="inlineStr">
+        <is>
+          <t>L20 W10/20; N=36; EHP=6718.916736; air:11x1,air:14x1,normal:17x7,normal:18x8,fast:30x1,fast:58x1,fast:64x1,medium:83x2,swarm:84x10,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" s="0" t="n">
+        <v>391</v>
+      </c>
+      <c r="C416" s="0" t="inlineStr">
+        <is>
+          <t>3880136,3880673,3880242,3880668,3880541,3880136,3880673,3880466,3880868,3880645,3880136,3880673,3880514,3880868,3880709,3880136,3880673,3880786,3880988,3880136,3880673,3880988,3880136,3880673,3880136,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880144,3880144,3880144,3880144</t>
+        </is>
+      </c>
+      <c r="D416" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E416" s="0" t="n">
+        <v>655</v>
+      </c>
+      <c r="F416" s="0" t="inlineStr">
+        <is>
+          <t>L20 W11/20; N=37; EHP=6988.000000; normal:17x7,normal:18x8,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:80x1,medium:83x1,swarm:84x10,heavy:88x1,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" s="0" t="n">
+        <v>392</v>
+      </c>
+      <c r="C417" s="0" t="inlineStr">
+        <is>
+          <t>3882136,3882673,3882242,3882091,3882668,3882645,3882136,3882673,3882466,3882107,3882668,3882693,3882136,3882673,3882514,3882107,3882868,3882709,3882136,3882673,3882786,3882115,3882868,3882136,3882673,3882988,3882136,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882144</t>
+        </is>
+      </c>
+      <c r="D417" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E417" s="0" t="n">
+        <v>640</v>
+      </c>
+      <c r="F417" s="0" t="inlineStr">
+        <is>
+          <t>L20 W12/20; N=38; EHP=8050.520400; air:11x1,air:13x2,air:14x1,normal:17x6,normal:18x6,fast:30x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,heavy:88x1,fast:98x1,medium:108x2,medium:123x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" s="0" t="n">
+        <v>393</v>
+      </c>
+      <c r="C418" s="0" t="inlineStr">
+        <is>
+          <t>3884136,3884673,3884242,3884091,3884668,3884253,3884136,3884673,3884466,3884091,3884668,3884645,3884136,3884673,3884514,3884107,3884868,3884693,3884136,3884673,3884786,3884115,3884988,3884136,3884673,3884988,3884136,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884144,3884144</t>
+        </is>
+      </c>
+      <c r="D418" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E418" s="0" t="n">
+        <v>625</v>
+      </c>
+      <c r="F418" s="0" t="inlineStr">
+        <is>
+          <t>L20 W13/20; N=39; EHP=9243.280800; air:11x2,air:13x1,air:14x1,normal:17x6,normal:18x7,fast:30x1,heavy:31x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x10,heavy:86x1,fast:98x1,medium:108x1,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" s="0" t="n">
+        <v>394</v>
+      </c>
+      <c r="C419" s="0" t="inlineStr">
+        <is>
+          <t>3886136,3886673,3886242,3886091,3886668,3886253,3886136,3886673,3886466,3886107,3886668,3886325,3886136,3886673,3886514,3886115,3886868,3886693,3886136,3886673,3886786,3886115,3886868,3887021,3886136,3886673,3886988,3886144,3886673,3886988,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673</t>
+        </is>
+      </c>
+      <c r="D419" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E419" s="0" t="n">
+        <v>610</v>
+      </c>
+      <c r="F419" s="0" t="inlineStr">
+        <is>
+          <t>L20 W14/20; N=40; EHP=10554.168000; air:11x1,air:13x1,air:14x2,normal:17x5,normal:18x6,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,medium:83x2,swarm:84x11,heavy:86x1,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" s="0" t="n">
+        <v>395</v>
+      </c>
+      <c r="C420" s="0" t="inlineStr">
+        <is>
+          <t>3888136,3888673,3888242,3888091,3888668,3888253,3888542,3888136,3888673,3888466,3888107,3888668,3888325,3888136,3888673,3888514,3888107,3888868,3888565,3888136,3888673,3888786,3888115,3888868,3889021,3888136,3888673,3888988,3888144,3888673,3888988,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673</t>
+        </is>
+      </c>
+      <c r="D420" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E420" s="0" t="n">
+        <v>595</v>
+      </c>
+      <c r="F420" s="0" t="inlineStr">
+        <is>
+          <t>L20 W15/20; N=41; EHP=13426.861056; air:11x1,air:13x2,air:14x1,normal:17x5,normal:18x6,fast:30x1,heavy:31x1,heavy:40x1,fast:58x1,fast:64x1,elite:67x1,heavy:70x1,medium:83x2,swarm:84x11,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" s="0" t="n">
+        <v>396</v>
+      </c>
+      <c r="C421" s="0" t="inlineStr">
+        <is>
+          <t>3890136,3890673,3890242,3890668,3890325,3890136,3890673,3890242,3890668,3890541,3890136,3890673,3890466,3890868,3890565,3890136,3890673,3890514,3890868,3891021,3890136,3890673,3890786,3890988,3890136,3890673,3890988,3890136,3890673,3890136,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890144,3890144,3890144,3890144</t>
+        </is>
+      </c>
+      <c r="D421" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E421" s="0" t="n">
+        <v>580</v>
+      </c>
+      <c r="F421" s="0" t="inlineStr">
+        <is>
+          <t>L20 W16/20; N=42; EHP=13964.000000; normal:17x8,normal:18x8,fast:30x2,heavy:40x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x11,fast:98x1,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" s="0" t="n">
+        <v>397</v>
+      </c>
+      <c r="C422" s="0" t="inlineStr">
+        <is>
+          <t>3892136,3892673,3892242,3892091,3892668,3892541,3892136,3892673,3892466,3892107,3892668,3892565,3892136,3892673,3892514,3892107,3892868,3892709,3892136,3892673,3892786,3892115,3892868,3893021,3892136,3892673,3892786,3892115,3892988,3892144,3892673,3892988,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892673</t>
+        </is>
+      </c>
+      <c r="D422" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E422" s="0" t="n">
+        <v>565</v>
+      </c>
+      <c r="F422" s="0" t="inlineStr">
+        <is>
+          <t>L20 W17/20; N=43; EHP=15246.458400; air:11x1,air:13x2,air:14x2,normal:17x5,normal:18x6,fast:30x1,fast:58x1,fast:64x1,heavy:67x1,heavy:70x1,medium:83x2,swarm:84x12,heavy:88x1,fast:98x2,medium:108x2,medium:123x2,heavy:127x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" s="0" t="n">
+        <v>398</v>
+      </c>
+      <c r="C423" s="0" t="inlineStr">
+        <is>
+          <t>3894136,3894673,3894242,3894091,3894668,3894541,3894136,3894673,3894466,3894091,3894668,3894565,3894136,3894673,3894466,3894107,3894868,3894645,3894136,3894673,3894514,3894107,3894868,3894709,3894136,3894673,3894786,3894115,3894988,3894136,3894673,3894988,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673</t>
+        </is>
+      </c>
+      <c r="D423" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E423" s="0" t="n">
+        <v>550</v>
+      </c>
+      <c r="F423" s="0" t="inlineStr">
+        <is>
+          <t>L20 W18/20; N=44; EHP=17080.720800; air:11x2,air:13x2,air:14x1,normal:17x6,normal:18x6,fast:30x1,fast:58x2,fast:64x1,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x2,swarm:84x12,heavy:88x1,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" s="0" t="n">
+        <v>399</v>
+      </c>
+      <c r="C424" s="0" t="inlineStr">
+        <is>
+          <t>3896136,3896673,3896242,3896091,3896668,3896541,3896136,3896673,3896466,3896091,3896668,3896645,3896136,3896673,3896514,3896107,3896868,3896693,3896136,3896673,3896514,3896115,3896868,3896709,3896136,3896673,3896786,3896115,3896988,3896136,3896673,3896988,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144</t>
+        </is>
+      </c>
+      <c r="D424" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E424" s="0" t="n">
+        <v>535</v>
+      </c>
+      <c r="F424" s="0" t="inlineStr">
+        <is>
+          <t>L20 W19/20; N=45; EHP=19058.544000; air:11x2,air:13x1,air:14x2,normal:17x6,normal:18x7,fast:30x1,fast:58x1,fast:64x2,heavy:67x1,heavy:80x1,medium:83x2,swarm:84x12,heavy:86x1,heavy:88x1,fast:98x1,medium:108x2,medium:123x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="C425" s="0" t="inlineStr">
+        <is>
+          <t>3898136,3898673,3898242,3898091,3898668,3898253,3899063,3898136,3898673,3898242,3898107,3898668,3898645,3898136,3898673,3898466,3898107,3898868,3898693,3898136,3898673,3898514,3898115,3898868,3898709,3898136,3898673,3898786,3898115,3898988,3898136,3898673,3898988,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144</t>
+        </is>
+      </c>
+      <c r="D425" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E425" s="0" t="n">
+        <v>520</v>
+      </c>
+      <c r="F425" s="0" t="inlineStr">
+        <is>
+          <t>L20 W20/20; N=46; EHP=26481.268500; air:11x1,air:13x2,air:14x2,normal:17x6,normal:18x7,fast:30x2,heavy:31x1,fast:58x1,fast:64x1,heavy:80x1,medium:83x2,swarm:84x12,heavy:86x1,heavy:88x1,fast:98x1,medium:108x2,medium:123x2,boss:132x1</t>
         </is>
       </c>
     </row>
